--- a/tanki_financial_model_v5.xlsx
+++ b/tanki_financial_model_v5.xlsx
@@ -20,6 +20,7 @@
     <sheet name="تكلفة المحطات" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="التحصيل من الامتياز" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="التوقعات السنوية" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="الاقتصاد الموسّع" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -49,7 +50,7 @@
     <numFmt numFmtId="181" formatCode="#,##0&quot; نقطة&quot;"/>
     <numFmt numFmtId="182" formatCode="0.00&quot; م&quot;"/>
   </numFmts>
-  <fonts count="99">
+  <fonts count="103">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -823,8 +824,22 @@
       <color rgb="FFE65100"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFD54A"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFE8EEFC"/>
+    </font>
+    <font>
+      <color rgb="FFE8EEFC"/>
+    </font>
   </fonts>
-  <fills count="29">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -993,6 +1008,16 @@
         <bgColor rgb="FF9C5700"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D26B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16223C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1101,7 +1126,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="521">
+  <cellXfs count="529">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2049,6 +2074,11 @@
     <xf numFmtId="0" fontId="41" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -2654,6 +2684,21 @@
     </xf>
     <xf numFmtId="0" fontId="87" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="4" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="10" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3697,15 +3742,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" s="260">
-      <c r="A1" s="473" t="inlineStr">
+      <c r="A1" s="476" t="inlineStr">
         <is>
           <t xml:space="preserve">  درب · المستويات الثلاثة</t>
         </is>
       </c>
-      <c r="F1" s="481" t="n"/>
-      <c r="G1" s="481" t="n"/>
-      <c r="H1" s="481" t="n"/>
-      <c r="I1" s="481" t="n"/>
+      <c r="F1" s="484" t="n"/>
+      <c r="G1" s="484" t="n"/>
+      <c r="H1" s="484" t="n"/>
+      <c r="I1" s="484" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1" s="260">
       <c r="A2" s="262" t="inlineStr">
@@ -3713,10 +3758,10 @@
           <t xml:space="preserve">  هيكل المستويات + الكسب + المنافع</t>
         </is>
       </c>
-      <c r="F2" s="482" t="n"/>
-      <c r="G2" s="482" t="n"/>
-      <c r="H2" s="482" t="n"/>
-      <c r="I2" s="482" t="n"/>
+      <c r="F2" s="485" t="n"/>
+      <c r="G2" s="485" t="n"/>
+      <c r="H2" s="485" t="n"/>
+      <c r="I2" s="485" t="n"/>
     </row>
     <row r="3" ht="9.75" customHeight="1" s="260"/>
     <row r="4" ht="30" customHeight="1" s="260">
@@ -3725,100 +3770,100 @@
           <t>🎯 هيكل المستويات</t>
         </is>
       </c>
-      <c r="F4" s="481" t="n"/>
-      <c r="G4" s="481" t="n"/>
-      <c r="H4" s="481" t="n"/>
-      <c r="I4" s="481" t="n"/>
+      <c r="F4" s="484" t="n"/>
+      <c r="G4" s="484" t="n"/>
+      <c r="H4" s="484" t="n"/>
+      <c r="I4" s="484" t="n"/>
     </row>
     <row r="5" ht="31.5" customHeight="1" s="260">
-      <c r="A5" s="327" t="inlineStr">
+      <c r="A5" s="330" t="inlineStr">
         <is>
           <t>المستوى</t>
         </is>
       </c>
-      <c r="B5" s="327" t="inlineStr">
+      <c r="B5" s="330" t="inlineStr">
         <is>
           <t>معدل الكسب</t>
         </is>
       </c>
-      <c r="C5" s="327" t="inlineStr">
+      <c r="C5" s="330" t="inlineStr">
         <is>
           <t>الحد الأدنى</t>
         </is>
       </c>
-      <c r="D5" s="327" t="inlineStr">
+      <c r="D5" s="330" t="inlineStr">
         <is>
           <t>الكاش باك</t>
         </is>
       </c>
-      <c r="E5" s="327" t="inlineStr">
+      <c r="E5" s="330" t="inlineStr">
         <is>
           <t>هدية الترحيب</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" s="260">
-      <c r="A6" s="483" t="inlineStr">
+      <c r="A6" s="486" t="inlineStr">
         <is>
           <t>🤍 المستوى الأبيض</t>
         </is>
       </c>
-      <c r="B6" s="484">
+      <c r="B6" s="487">
         <f>السيناريوهات!C7</f>
         <v/>
       </c>
-      <c r="C6" s="485" t="n">
+      <c r="C6" s="488" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="486">
+      <c r="D6" s="489">
         <f>السيناريوهات!C7/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="E6" s="487" t="n">
+      <c r="E6" s="490" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" s="260">
-      <c r="A7" s="488" t="inlineStr">
+      <c r="A7" s="491" t="inlineStr">
         <is>
           <t>🩶 المستوى الفضي</t>
         </is>
       </c>
-      <c r="B7" s="484">
+      <c r="B7" s="487">
         <f>السيناريوهات!C8</f>
         <v/>
       </c>
-      <c r="C7" s="485">
+      <c r="C7" s="488">
         <f>السيناريوهات!C16</f>
         <v/>
       </c>
-      <c r="D7" s="486">
+      <c r="D7" s="489">
         <f>السيناريوهات!C8/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="E7" s="487" t="n">
+      <c r="E7" s="490" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" s="260">
-      <c r="A8" s="489" t="inlineStr">
+      <c r="A8" s="492" t="inlineStr">
         <is>
           <t>🟠 المستوى البرتقالي</t>
         </is>
       </c>
-      <c r="B8" s="484">
+      <c r="B8" s="487">
         <f>السيناريوهات!C9</f>
         <v/>
       </c>
-      <c r="C8" s="485">
+      <c r="C8" s="488">
         <f>السيناريوهات!C17+1</f>
         <v/>
       </c>
-      <c r="D8" s="486">
+      <c r="D8" s="489">
         <f>السيناريوهات!C9/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="E8" s="487" t="n">
+      <c r="E8" s="490" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -3829,13 +3874,13 @@
           <t>🎁 المنافع الإضافية</t>
         </is>
       </c>
-      <c r="F10" s="481" t="n"/>
-      <c r="G10" s="481" t="n"/>
-      <c r="H10" s="481" t="n"/>
-      <c r="I10" s="481" t="n"/>
+      <c r="F10" s="484" t="n"/>
+      <c r="G10" s="484" t="n"/>
+      <c r="H10" s="484" t="n"/>
+      <c r="I10" s="484" t="n"/>
     </row>
     <row r="11" ht="31.5" customHeight="1" s="260">
-      <c r="A11" s="327" t="inlineStr">
+      <c r="A11" s="330" t="inlineStr">
         <is>
           <t>الميزة</t>
         </is>
@@ -3855,7 +3900,7 @@
           <t>🟠 البرتقالي</t>
         </is>
       </c>
-      <c r="E11" s="327" t="inlineStr">
+      <c r="E11" s="330" t="inlineStr">
         <is>
           <t>ملاحظة</t>
         </is>
@@ -3882,7 +3927,7 @@
           <t>🎯 2×</t>
         </is>
       </c>
-      <c r="E12" s="490" t="inlineStr">
+      <c r="E12" s="493" t="inlineStr">
         <is>
           <t>تحفيز للمناسبات</t>
         </is>
@@ -3909,7 +3954,7 @@
           <t>✅✅ VIP</t>
         </is>
       </c>
-      <c r="E13" s="490" t="inlineStr">
+      <c r="E13" s="493" t="inlineStr">
         <is>
           <t>تجربة حصرية</t>
         </is>
@@ -3936,7 +3981,7 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="E14" s="490" t="inlineStr">
+      <c r="E14" s="493" t="inlineStr">
         <is>
           <t>قيمة إضافية</t>
         </is>
@@ -3963,7 +4008,7 @@
           <t>فوري</t>
         </is>
       </c>
-      <c r="E15" s="490" t="inlineStr">
+      <c r="E15" s="493" t="inlineStr">
         <is>
           <t>خدمة العملاء</t>
         </is>
@@ -3990,7 +4035,7 @@
           <t>✅ بلا حدود</t>
         </is>
       </c>
-      <c r="E16" s="490" t="inlineStr">
+      <c r="E16" s="493" t="inlineStr">
         <is>
           <t>مشاركة المنفعة</t>
         </is>
@@ -4017,7 +4062,7 @@
           <t>✅ مرة/سنة</t>
         </is>
       </c>
-      <c r="E17" s="490" t="inlineStr">
+      <c r="E17" s="493" t="inlineStr">
         <is>
           <t>مرونة في الإجازات</t>
         </is>
@@ -4025,18 +4070,18 @@
     </row>
     <row r="18" ht="12" customHeight="1" s="260"/>
     <row r="19" ht="30" customHeight="1" s="260">
-      <c r="A19" s="326" t="inlineStr">
+      <c r="A19" s="329" t="inlineStr">
         <is>
           <t>⚙️ قواعد الترقية والتنزيل</t>
         </is>
       </c>
-      <c r="F19" s="491" t="n"/>
-      <c r="G19" s="491" t="n"/>
-      <c r="H19" s="491" t="n"/>
-      <c r="I19" s="491" t="n"/>
+      <c r="F19" s="494" t="n"/>
+      <c r="G19" s="494" t="n"/>
+      <c r="H19" s="494" t="n"/>
+      <c r="I19" s="494" t="n"/>
     </row>
     <row r="20" ht="25.5" customHeight="1" s="260">
-      <c r="A20" s="325" t="inlineStr">
+      <c r="A20" s="328" t="inlineStr">
         <is>
           <t>🔼 الترقية: تلقائية فور تجاوز الحد الأدنى للمستوى التالي</t>
         </is>
@@ -4047,7 +4092,7 @@
       <c r="E20" s="287" t="n"/>
     </row>
     <row r="21" ht="25.5" customHeight="1" s="260">
-      <c r="A21" s="325" t="inlineStr">
+      <c r="A21" s="328" t="inlineStr">
         <is>
           <t>🔽 التنزيل: بعد 12 شهر من عدم الوصول للحد الأدنى</t>
         </is>
@@ -4058,7 +4103,7 @@
       <c r="E21" s="287" t="n"/>
     </row>
     <row r="22" ht="25.5" customHeight="1" s="260">
-      <c r="A22" s="325" t="inlineStr">
+      <c r="A22" s="328" t="inlineStr">
         <is>
           <t>📅 المراجعة: 31 ديسمبر من كل سنة · يحتسب آخر 12 شهر</t>
         </is>
@@ -4069,7 +4114,7 @@
       <c r="E22" s="287" t="n"/>
     </row>
     <row r="23" ht="25.5" customHeight="1" s="260">
-      <c r="A23" s="325" t="inlineStr">
+      <c r="A23" s="328" t="inlineStr">
         <is>
           <t>🎯 فترة سماح: 30 يوم بعد التنزيل لاستعادة المستوى</t>
         </is>
@@ -4080,7 +4125,7 @@
       <c r="E23" s="287" t="n"/>
     </row>
     <row r="24" ht="25.5" customHeight="1" s="260">
-      <c r="A24" s="325" t="inlineStr">
+      <c r="A24" s="328" t="inlineStr">
         <is>
           <t>💯 النقاط لا تنتهي · باقية حتى لو تغيّر المستوى</t>
         </is>
@@ -4126,7 +4171,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" s="260">
-      <c r="A1" s="473" t="inlineStr">
+      <c r="A1" s="476" t="inlineStr">
         <is>
           <t xml:space="preserve">  درب · تكلفة الولاء على كل نوع محطة</t>
         </is>
@@ -4190,21 +4235,21 @@
           <t>هامش/لتر (هللة)</t>
         </is>
       </c>
-      <c r="B6" s="492">
+      <c r="B6" s="495">
         <f>السيناريوهات!C26</f>
         <v/>
       </c>
-      <c r="C6" s="492">
+      <c r="C6" s="495">
         <f>السيناريوهات!C27</f>
         <v/>
       </c>
-      <c r="D6" s="492">
+      <c r="D6" s="495">
         <f>السيناريوهات!C28</f>
         <v/>
       </c>
-      <c r="E6" s="493" t="n"/>
-      <c r="F6" s="493" t="n"/>
-      <c r="G6" s="493" t="n"/>
+      <c r="E6" s="496" t="n"/>
+      <c r="F6" s="496" t="n"/>
+      <c r="G6" s="496" t="n"/>
     </row>
     <row r="7" ht="27.75" customHeight="1" s="260">
       <c r="A7" s="296" t="inlineStr">
@@ -4212,107 +4257,107 @@
           <t>هامش/ريال (هللة)</t>
         </is>
       </c>
-      <c r="B7" s="494">
+      <c r="B7" s="497">
         <f>B6/السيناريوهات!$C$11</f>
         <v/>
       </c>
-      <c r="C7" s="494">
+      <c r="C7" s="497">
         <f>C6/السيناريوهات!$C$11</f>
         <v/>
       </c>
-      <c r="D7" s="494">
+      <c r="D7" s="497">
         <f>D6/السيناريوهات!$C$11</f>
         <v/>
       </c>
-      <c r="E7" s="493" t="n"/>
-      <c r="F7" s="493" t="n"/>
-      <c r="G7" s="493" t="n"/>
+      <c r="E7" s="496" t="n"/>
+      <c r="F7" s="496" t="n"/>
+      <c r="G7" s="496" t="n"/>
     </row>
     <row r="8" ht="27.75" customHeight="1" s="260">
-      <c r="A8" s="495" t="inlineStr">
+      <c r="A8" s="498" t="inlineStr">
         <is>
           <t>تكلفة الولاء/ريال (هللة)</t>
         </is>
       </c>
-      <c r="B8" s="496">
+      <c r="B8" s="499">
         <f>السيناريوهات!$C$10</f>
         <v/>
       </c>
-      <c r="C8" s="496">
+      <c r="C8" s="499">
         <f>السيناريوهات!$C$10</f>
         <v/>
       </c>
-      <c r="D8" s="496">
+      <c r="D8" s="499">
         <f>السيناريوهات!$C$10</f>
         <v/>
       </c>
-      <c r="E8" s="493" t="n"/>
-      <c r="F8" s="493" t="n"/>
-      <c r="G8" s="493" t="n"/>
+      <c r="E8" s="496" t="n"/>
+      <c r="F8" s="496" t="n"/>
+      <c r="G8" s="496" t="n"/>
     </row>
     <row r="9" ht="27.75" customHeight="1" s="260">
-      <c r="A9" s="497" t="inlineStr">
+      <c r="A9" s="500" t="inlineStr">
         <is>
           <t>مساهمة درب %</t>
         </is>
       </c>
-      <c r="B9" s="498" t="n">
+      <c r="B9" s="501" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="498" t="n">
+      <c r="C9" s="501" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" s="498">
+      <c r="D9" s="501">
         <f>السيناريوهات!C29</f>
         <v/>
       </c>
-      <c r="E9" s="493" t="n"/>
-      <c r="F9" s="493" t="n"/>
-      <c r="G9" s="493" t="n"/>
+      <c r="E9" s="496" t="n"/>
+      <c r="F9" s="496" t="n"/>
+      <c r="G9" s="496" t="n"/>
     </row>
     <row r="10" ht="27.75" customHeight="1" s="260">
-      <c r="A10" s="499" t="inlineStr">
+      <c r="A10" s="502" t="inlineStr">
         <is>
           <t>تكلفة درب/ريال (هللة)</t>
         </is>
       </c>
-      <c r="B10" s="500">
+      <c r="B10" s="503">
         <f>B8*B9</f>
         <v/>
       </c>
-      <c r="C10" s="500">
+      <c r="C10" s="503">
         <f>C8*C9</f>
         <v/>
       </c>
-      <c r="D10" s="500">
+      <c r="D10" s="503">
         <f>D8*D9</f>
         <v/>
       </c>
-      <c r="E10" s="493" t="n"/>
-      <c r="F10" s="493" t="n"/>
-      <c r="G10" s="493" t="n"/>
+      <c r="E10" s="496" t="n"/>
+      <c r="F10" s="496" t="n"/>
+      <c r="G10" s="496" t="n"/>
     </row>
     <row r="11" ht="27.75" customHeight="1" s="260">
-      <c r="A11" s="501" t="inlineStr">
+      <c r="A11" s="504" t="inlineStr">
         <is>
           <t>صافي هامش المالك/ريال</t>
         </is>
       </c>
-      <c r="B11" s="502">
+      <c r="B11" s="505">
         <f>B7</f>
         <v/>
       </c>
-      <c r="C11" s="502">
+      <c r="C11" s="505">
         <f>C7-(C8*(1-C9))</f>
         <v/>
       </c>
-      <c r="D11" s="502">
+      <c r="D11" s="505">
         <f>D7-(D8*(1-D9))</f>
         <v/>
       </c>
-      <c r="E11" s="493" t="n"/>
-      <c r="F11" s="493" t="n"/>
-      <c r="G11" s="493" t="n"/>
+      <c r="E11" s="496" t="n"/>
+      <c r="F11" s="496" t="n"/>
+      <c r="G11" s="496" t="n"/>
     </row>
     <row r="12" ht="27.75" customHeight="1" s="260">
       <c r="A12" s="294" t="inlineStr">
@@ -4332,9 +4377,9 @@
         <f>IF(D11&gt;0.5,"✅ مربح",IF(D11&gt;0,"⚠️ هامش ضيق","🔴 خسارة"))</f>
         <v/>
       </c>
-      <c r="E12" s="493" t="n"/>
-      <c r="F12" s="493" t="n"/>
-      <c r="G12" s="493" t="n"/>
+      <c r="E12" s="496" t="n"/>
+      <c r="F12" s="496" t="n"/>
+      <c r="G12" s="496" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4364,7 +4409,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" s="260">
-      <c r="A1" s="473" t="inlineStr">
+      <c r="A1" s="476" t="inlineStr">
         <is>
           <t xml:space="preserve">  درب · آلية التحصيل من محطات الامتياز</t>
         </is>
@@ -4386,7 +4431,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="260">
-      <c r="A5" s="468" t="inlineStr">
+      <c r="A5" s="471" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4396,18 +4441,18 @@
           <t>نهاية كل شهر</t>
         </is>
       </c>
-      <c r="C5" s="325" t="inlineStr">
+      <c r="C5" s="328" t="inlineStr">
         <is>
           <t>النظام يحسب إجمالي اللترات لكل محطة</t>
         </is>
       </c>
-      <c r="D5" s="493" t="n"/>
-      <c r="E5" s="493" t="n"/>
-      <c r="F5" s="493" t="n"/>
-      <c r="G5" s="493" t="n"/>
+      <c r="D5" s="496" t="n"/>
+      <c r="E5" s="496" t="n"/>
+      <c r="F5" s="496" t="n"/>
+      <c r="G5" s="496" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1" s="260">
-      <c r="A6" s="468" t="inlineStr">
+      <c r="A6" s="471" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -4417,18 +4462,18 @@
           <t>حساب المساهمة</t>
         </is>
       </c>
-      <c r="C6" s="325" t="inlineStr">
+      <c r="C6" s="328" t="inlineStr">
         <is>
           <t>اللترات × سعر اللتر × 0.5 هللة = المستحق</t>
         </is>
       </c>
-      <c r="D6" s="493" t="n"/>
-      <c r="E6" s="493" t="n"/>
-      <c r="F6" s="493" t="n"/>
-      <c r="G6" s="493" t="n"/>
+      <c r="D6" s="496" t="n"/>
+      <c r="E6" s="496" t="n"/>
+      <c r="F6" s="496" t="n"/>
+      <c r="G6" s="496" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1" s="260">
-      <c r="A7" s="468" t="inlineStr">
+      <c r="A7" s="471" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4438,18 +4483,18 @@
           <t>إصدار الفاتورة</t>
         </is>
       </c>
-      <c r="C7" s="325" t="inlineStr">
+      <c r="C7" s="328" t="inlineStr">
         <is>
           <t>فاتورة إلكترونية تلقائية في اليوم 1</t>
         </is>
       </c>
-      <c r="D7" s="493" t="n"/>
-      <c r="E7" s="493" t="n"/>
-      <c r="F7" s="493" t="n"/>
-      <c r="G7" s="493" t="n"/>
+      <c r="D7" s="496" t="n"/>
+      <c r="E7" s="496" t="n"/>
+      <c r="F7" s="496" t="n"/>
+      <c r="G7" s="496" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1" s="260">
-      <c r="A8" s="468" t="inlineStr">
+      <c r="A8" s="471" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4459,18 +4504,18 @@
           <t>مهلة السداد</t>
         </is>
       </c>
-      <c r="C8" s="325" t="inlineStr">
+      <c r="C8" s="328" t="inlineStr">
         <is>
           <t>15 يوم من تاريخ الفاتورة</t>
         </is>
       </c>
-      <c r="D8" s="493" t="n"/>
-      <c r="E8" s="493" t="n"/>
-      <c r="F8" s="493" t="n"/>
-      <c r="G8" s="493" t="n"/>
+      <c r="D8" s="496" t="n"/>
+      <c r="E8" s="496" t="n"/>
+      <c r="F8" s="496" t="n"/>
+      <c r="G8" s="496" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1" s="260">
-      <c r="A9" s="468" t="inlineStr">
+      <c r="A9" s="471" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4480,19 +4525,19 @@
           <t>الغرامة</t>
         </is>
       </c>
-      <c r="C9" s="325" t="inlineStr">
+      <c r="C9" s="328" t="inlineStr">
         <is>
           <t>1% أسبوعياً + إيقاف بعد 30 يوم</t>
         </is>
       </c>
-      <c r="D9" s="493" t="n"/>
-      <c r="E9" s="493" t="n"/>
-      <c r="F9" s="493" t="n"/>
-      <c r="G9" s="493" t="n"/>
+      <c r="D9" s="496" t="n"/>
+      <c r="E9" s="496" t="n"/>
+      <c r="F9" s="496" t="n"/>
+      <c r="G9" s="496" t="n"/>
     </row>
     <row r="10" ht="9.75" customHeight="1" s="260"/>
     <row r="11" ht="30" customHeight="1" s="260">
-      <c r="A11" s="326" t="inlineStr">
+      <c r="A11" s="329" t="inlineStr">
         <is>
           <t>📋 محاكاة 10 محطات امتياز نموذجية</t>
         </is>
@@ -4539,20 +4584,20 @@
       <c r="A13" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="503" t="inlineStr">
+      <c r="B13" s="506" t="inlineStr">
         <is>
           <t>AMT-001</t>
         </is>
       </c>
-      <c r="C13" s="384" t="inlineStr">
+      <c r="C13" s="387" t="inlineStr">
         <is>
           <t>الرياض</t>
         </is>
       </c>
-      <c r="D13" s="504" t="n">
+      <c r="D13" s="507" t="n">
         <v>95000</v>
       </c>
-      <c r="E13" s="357">
+      <c r="E13" s="360">
         <f>D13*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4560,7 +4605,7 @@
         <f>E13*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G13" s="505">
+      <c r="G13" s="508">
         <f>E13*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4569,20 +4614,20 @@
       <c r="A14" s="303" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="503" t="inlineStr">
+      <c r="B14" s="506" t="inlineStr">
         <is>
           <t>AMT-002</t>
         </is>
       </c>
-      <c r="C14" s="384" t="inlineStr">
+      <c r="C14" s="387" t="inlineStr">
         <is>
           <t>جدة</t>
         </is>
       </c>
-      <c r="D14" s="504" t="n">
+      <c r="D14" s="507" t="n">
         <v>82000</v>
       </c>
-      <c r="E14" s="357">
+      <c r="E14" s="360">
         <f>D14*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4590,7 +4635,7 @@
         <f>E14*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G14" s="505">
+      <c r="G14" s="508">
         <f>E14*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4599,20 +4644,20 @@
       <c r="A15" s="303" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="503" t="inlineStr">
+      <c r="B15" s="506" t="inlineStr">
         <is>
           <t>AMT-003</t>
         </is>
       </c>
-      <c r="C15" s="384" t="inlineStr">
+      <c r="C15" s="387" t="inlineStr">
         <is>
           <t>مكة</t>
         </is>
       </c>
-      <c r="D15" s="504" t="n">
+      <c r="D15" s="507" t="n">
         <v>78000</v>
       </c>
-      <c r="E15" s="357">
+      <c r="E15" s="360">
         <f>D15*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4620,7 +4665,7 @@
         <f>E15*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G15" s="505">
+      <c r="G15" s="508">
         <f>E15*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4629,20 +4674,20 @@
       <c r="A16" s="303" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="503" t="inlineStr">
+      <c r="B16" s="506" t="inlineStr">
         <is>
           <t>AMT-004</t>
         </is>
       </c>
-      <c r="C16" s="384" t="inlineStr">
+      <c r="C16" s="387" t="inlineStr">
         <is>
           <t>الدمام</t>
         </is>
       </c>
-      <c r="D16" s="504" t="n">
+      <c r="D16" s="507" t="n">
         <v>88000</v>
       </c>
-      <c r="E16" s="357">
+      <c r="E16" s="360">
         <f>D16*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4650,7 +4695,7 @@
         <f>E16*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G16" s="505">
+      <c r="G16" s="508">
         <f>E16*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4659,20 +4704,20 @@
       <c r="A17" s="303" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="503" t="inlineStr">
+      <c r="B17" s="506" t="inlineStr">
         <is>
           <t>AMT-005</t>
         </is>
       </c>
-      <c r="C17" s="384" t="inlineStr">
+      <c r="C17" s="387" t="inlineStr">
         <is>
           <t>الطائف</t>
         </is>
       </c>
-      <c r="D17" s="504" t="n">
+      <c r="D17" s="507" t="n">
         <v>65000</v>
       </c>
-      <c r="E17" s="357">
+      <c r="E17" s="360">
         <f>D17*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4680,7 +4725,7 @@
         <f>E17*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G17" s="505">
+      <c r="G17" s="508">
         <f>E17*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4689,20 +4734,20 @@
       <c r="A18" s="303" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="503" t="inlineStr">
+      <c r="B18" s="506" t="inlineStr">
         <is>
           <t>AMT-006</t>
         </is>
       </c>
-      <c r="C18" s="384" t="inlineStr">
+      <c r="C18" s="387" t="inlineStr">
         <is>
           <t>تبوك</t>
         </is>
       </c>
-      <c r="D18" s="504" t="n">
+      <c r="D18" s="507" t="n">
         <v>58000</v>
       </c>
-      <c r="E18" s="357">
+      <c r="E18" s="360">
         <f>D18*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4710,7 +4755,7 @@
         <f>E18*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G18" s="505">
+      <c r="G18" s="508">
         <f>E18*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4719,20 +4764,20 @@
       <c r="A19" s="303" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="503" t="inlineStr">
+      <c r="B19" s="506" t="inlineStr">
         <is>
           <t>AMT-007</t>
         </is>
       </c>
-      <c r="C19" s="384" t="inlineStr">
+      <c r="C19" s="387" t="inlineStr">
         <is>
           <t>حائل</t>
         </is>
       </c>
-      <c r="D19" s="504" t="n">
+      <c r="D19" s="507" t="n">
         <v>52000</v>
       </c>
-      <c r="E19" s="357">
+      <c r="E19" s="360">
         <f>D19*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4740,7 +4785,7 @@
         <f>E19*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G19" s="505">
+      <c r="G19" s="508">
         <f>E19*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4749,20 +4794,20 @@
       <c r="A20" s="303" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="503" t="inlineStr">
+      <c r="B20" s="506" t="inlineStr">
         <is>
           <t>AMT-008</t>
         </is>
       </c>
-      <c r="C20" s="384" t="inlineStr">
+      <c r="C20" s="387" t="inlineStr">
         <is>
           <t>بريدة</t>
         </is>
       </c>
-      <c r="D20" s="504" t="n">
+      <c r="D20" s="507" t="n">
         <v>71000</v>
       </c>
-      <c r="E20" s="357">
+      <c r="E20" s="360">
         <f>D20*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4770,7 +4815,7 @@
         <f>E20*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G20" s="505">
+      <c r="G20" s="508">
         <f>E20*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4779,20 +4824,20 @@
       <c r="A21" s="303" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="503" t="inlineStr">
+      <c r="B21" s="506" t="inlineStr">
         <is>
           <t>AMT-009</t>
         </is>
       </c>
-      <c r="C21" s="384" t="inlineStr">
+      <c r="C21" s="387" t="inlineStr">
         <is>
           <t>أبها</t>
         </is>
       </c>
-      <c r="D21" s="504" t="n">
+      <c r="D21" s="507" t="n">
         <v>68000</v>
       </c>
-      <c r="E21" s="357">
+      <c r="E21" s="360">
         <f>D21*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4800,7 +4845,7 @@
         <f>E21*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G21" s="505">
+      <c r="G21" s="508">
         <f>E21*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
@@ -4809,20 +4854,20 @@
       <c r="A22" s="303" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="503" t="inlineStr">
+      <c r="B22" s="506" t="inlineStr">
         <is>
           <t>AMT-010</t>
         </is>
       </c>
-      <c r="C22" s="384" t="inlineStr">
+      <c r="C22" s="387" t="inlineStr">
         <is>
           <t>جازان</t>
         </is>
       </c>
-      <c r="D22" s="504" t="n">
+      <c r="D22" s="507" t="n">
         <v>49000</v>
       </c>
-      <c r="E22" s="357">
+      <c r="E22" s="360">
         <f>D22*السيناريوهات!$C$11</f>
         <v/>
       </c>
@@ -4830,57 +4875,57 @@
         <f>E22*السيناريوهات!$C$10*السيناريوهات!$C$30/100</f>
         <v/>
       </c>
-      <c r="G22" s="505">
+      <c r="G22" s="508">
         <f>E22*السيناريوهات!$C$10*السيناريوهات!$C$29/100</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="33.75" customHeight="1" s="260">
-      <c r="A23" s="445" t="inlineStr">
+      <c r="A23" s="448" t="inlineStr">
         <is>
           <t>📊 الإجمالي الشهري</t>
         </is>
       </c>
       <c r="B23" s="293" t="n"/>
       <c r="C23" s="287" t="n"/>
-      <c r="D23" s="506">
+      <c r="D23" s="509">
         <f>SUM(D13:D22)</f>
         <v/>
       </c>
-      <c r="E23" s="507">
+      <c r="E23" s="510">
         <f>SUM(E13:E22)</f>
         <v/>
       </c>
-      <c r="F23" s="507">
+      <c r="F23" s="510">
         <f>SUM(F13:F22)</f>
         <v/>
       </c>
-      <c r="G23" s="507">
+      <c r="G23" s="510">
         <f>SUM(G13:G22)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="33.75" customHeight="1" s="260">
-      <c r="A24" s="450" t="inlineStr">
+      <c r="A24" s="453" t="inlineStr">
         <is>
           <t>📅 الإجمالي السنوي</t>
         </is>
       </c>
       <c r="B24" s="293" t="n"/>
       <c r="C24" s="287" t="n"/>
-      <c r="D24" s="508">
+      <c r="D24" s="511">
         <f>D23*12</f>
         <v/>
       </c>
-      <c r="E24" s="509">
+      <c r="E24" s="512">
         <f>E23*12</f>
         <v/>
       </c>
-      <c r="F24" s="509">
+      <c r="F24" s="512">
         <f>F23*12</f>
         <v/>
       </c>
-      <c r="G24" s="509">
+      <c r="G24" s="512">
         <f>G23*12</f>
         <v/>
       </c>
@@ -4915,7 +4960,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" s="260">
-      <c r="A1" s="473" t="inlineStr">
+      <c r="A1" s="476" t="inlineStr">
         <is>
           <t xml:space="preserve">  درب · التوقعات المالية على 5 سنوات</t>
         </is>
@@ -4979,22 +5024,22 @@
           <t>🏢 تشغيل</t>
         </is>
       </c>
-      <c r="B6" s="510" t="n">
+      <c r="B6" s="513" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="510" t="n">
+      <c r="C6" s="513" t="n">
         <v>35</v>
       </c>
-      <c r="D6" s="510" t="n">
+      <c r="D6" s="513" t="n">
         <v>42</v>
       </c>
-      <c r="E6" s="510" t="n">
+      <c r="E6" s="513" t="n">
         <v>50</v>
       </c>
-      <c r="F6" s="510" t="n">
+      <c r="F6" s="513" t="n">
         <v>58</v>
       </c>
-      <c r="G6" s="511">
+      <c r="G6" s="514">
         <f>(F6-B6)/B6</f>
         <v/>
       </c>
@@ -5005,22 +5050,22 @@
           <t>💼 استثمار</t>
         </is>
       </c>
-      <c r="B7" s="510" t="n">
+      <c r="B7" s="513" t="n">
         <v>70</v>
       </c>
-      <c r="C7" s="510" t="n">
+      <c r="C7" s="513" t="n">
         <v>80</v>
       </c>
-      <c r="D7" s="510" t="n">
+      <c r="D7" s="513" t="n">
         <v>88</v>
       </c>
-      <c r="E7" s="510" t="n">
+      <c r="E7" s="513" t="n">
         <v>95</v>
       </c>
-      <c r="F7" s="510" t="n">
+      <c r="F7" s="513" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="511">
+      <c r="G7" s="514">
         <f>(F7-B7)/B7</f>
         <v/>
       </c>
@@ -5031,60 +5076,60 @@
           <t>🤝 امتياز</t>
         </is>
       </c>
-      <c r="B8" s="510" t="n">
+      <c r="B8" s="513" t="n">
         <v>73</v>
       </c>
-      <c r="C8" s="510" t="n">
+      <c r="C8" s="513" t="n">
         <v>90</v>
       </c>
-      <c r="D8" s="510" t="n">
+      <c r="D8" s="513" t="n">
         <v>105</v>
       </c>
-      <c r="E8" s="510" t="n">
+      <c r="E8" s="513" t="n">
         <v>120</v>
       </c>
-      <c r="F8" s="510" t="n">
+      <c r="F8" s="513" t="n">
         <v>135</v>
       </c>
-      <c r="G8" s="511">
+      <c r="G8" s="514">
         <f>(F8-B8)/B8</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" s="260">
-      <c r="A9" s="512" t="inlineStr">
+      <c r="A9" s="515" t="inlineStr">
         <is>
           <t>📊 الإجمالي</t>
         </is>
       </c>
-      <c r="B9" s="513">
+      <c r="B9" s="516">
         <f>SUM(B6:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="513">
+      <c r="C9" s="516">
         <f>SUM(C6:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="513">
+      <c r="D9" s="516">
         <f>SUM(D6:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="513">
+      <c r="E9" s="516">
         <f>SUM(E6:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="513">
+      <c r="F9" s="516">
         <f>SUM(F6:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="514">
+      <c r="G9" s="517">
         <f>(F9-B9)/B9</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="9.75" customHeight="1" s="260"/>
     <row r="11" ht="30" customHeight="1" s="260">
-      <c r="A11" s="326" t="inlineStr">
+      <c r="A11" s="329" t="inlineStr">
         <is>
           <t>💰 التكلفة السنوية على درب (مليون ريال)</t>
         </is>
@@ -5133,27 +5178,27 @@
           <t>تشغيل (100%)</t>
         </is>
       </c>
-      <c r="B13" s="515">
+      <c r="B13" s="518">
         <f>B6*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10/100/1000000</f>
         <v/>
       </c>
-      <c r="C13" s="515">
+      <c r="C13" s="518">
         <f>C6*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10/100/1000000</f>
         <v/>
       </c>
-      <c r="D13" s="515">
+      <c r="D13" s="518">
         <f>D6*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10/100/1000000</f>
         <v/>
       </c>
-      <c r="E13" s="515">
+      <c r="E13" s="518">
         <f>E6*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10/100/1000000</f>
         <v/>
       </c>
-      <c r="F13" s="515">
+      <c r="F13" s="518">
         <f>F6*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10/100/1000000</f>
         <v/>
       </c>
-      <c r="G13" s="516">
+      <c r="G13" s="519">
         <f>(F13-B13)/B13</f>
         <v/>
       </c>
@@ -5164,27 +5209,27 @@
           <t>استثمار (50%)</t>
         </is>
       </c>
-      <c r="B14" s="515">
+      <c r="B14" s="518">
         <f>B7*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*0.5/100/1000000</f>
         <v/>
       </c>
-      <c r="C14" s="515">
+      <c r="C14" s="518">
         <f>C7*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*0.5/100/1000000</f>
         <v/>
       </c>
-      <c r="D14" s="515">
+      <c r="D14" s="518">
         <f>D7*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*0.5/100/1000000</f>
         <v/>
       </c>
-      <c r="E14" s="515">
+      <c r="E14" s="518">
         <f>E7*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*0.5/100/1000000</f>
         <v/>
       </c>
-      <c r="F14" s="515">
+      <c r="F14" s="518">
         <f>F7*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*0.5/100/1000000</f>
         <v/>
       </c>
-      <c r="G14" s="516">
+      <c r="G14" s="519">
         <f>(F14-B14)/B14</f>
         <v/>
       </c>
@@ -5195,64 +5240,64 @@
           <t>امتياز (50%)</t>
         </is>
       </c>
-      <c r="B15" s="515">
+      <c r="B15" s="518">
         <f>B8*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*السيناريوهات!$C$29/100/1000000</f>
         <v/>
       </c>
-      <c r="C15" s="515">
+      <c r="C15" s="518">
         <f>C8*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*السيناريوهات!$C$29/100/1000000</f>
         <v/>
       </c>
-      <c r="D15" s="515">
+      <c r="D15" s="518">
         <f>D8*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*السيناريوهات!$C$29/100/1000000</f>
         <v/>
       </c>
-      <c r="E15" s="515">
+      <c r="E15" s="518">
         <f>E8*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*السيناريوهات!$C$29/100/1000000</f>
         <v/>
       </c>
-      <c r="F15" s="515">
+      <c r="F15" s="518">
         <f>F8*السيناريوهات!$C$31*12*السيناريوهات!$C$11*السيناريوهات!$C$10*السيناريوهات!$C$29/100/1000000</f>
         <v/>
       </c>
-      <c r="G15" s="516">
+      <c r="G15" s="519">
         <f>(F15-B15)/B15</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" s="260">
-      <c r="A16" s="517" t="inlineStr">
+      <c r="A16" s="520" t="inlineStr">
         <is>
           <t>📊 الإجمالي</t>
         </is>
       </c>
-      <c r="B16" s="518">
+      <c r="B16" s="521">
         <f>SUM(B13:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="518">
+      <c r="C16" s="521">
         <f>SUM(C13:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="518">
+      <c r="D16" s="521">
         <f>SUM(D13:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="518">
+      <c r="E16" s="521">
         <f>SUM(E13:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="518">
+      <c r="F16" s="521">
         <f>SUM(F13:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="519">
+      <c r="G16" s="522">
         <f>(F16-B16)/B16</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" s="260">
-      <c r="A17" s="520">
+      <c r="A17" s="523">
         <f>" 💎 إجمالي 5 سنوات على درب: "&amp;TEXT(SUM(B16:F16),"0.00")&amp;" مليون ريال"</f>
         <v/>
       </c>
@@ -5271,13 +5316,372 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" style="260" min="1" max="1"/>
+    <col width="16" customWidth="1" style="260" min="2" max="2"/>
+    <col width="16" customWidth="1" style="260" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="524" t="inlineStr">
+        <is>
+          <t>درب · محرك الاقتصاد الموسّع — الديزل والشركاء (معادلات حيّة)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="525" t="inlineStr">
+        <is>
+          <t>كل القيم أدناه معادلات تشير لخلايا ورقة السيناريوهات — غيّر هناك وتتحدث هنا</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="526" t="inlineStr">
+        <is>
+          <t>⛽ الديزل</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="524" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="B5" s="524" t="inlineStr">
+        <is>
+          <t>القيمة</t>
+        </is>
+      </c>
+      <c r="C5" s="524" t="inlineStr">
+        <is>
+          <t>الوحدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="525" t="inlineStr">
+        <is>
+          <t>هامش الديزل/لتر</t>
+        </is>
+      </c>
+      <c r="B6" s="527">
+        <f>السيناريوهات!C37</f>
+        <v/>
+      </c>
+      <c r="C6" s="525" t="inlineStr">
+        <is>
+          <t>هللة/لتر</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="525" t="inlineStr">
+        <is>
+          <t>هامش الديزل %</t>
+        </is>
+      </c>
+      <c r="B7" s="528">
+        <f>السيناريوهات!C37/(السيناريوهات!C36*100)</f>
+        <v/>
+      </c>
+      <c r="C7" s="525" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="525" t="inlineStr">
+        <is>
+          <t>كسب الديزل</t>
+        </is>
+      </c>
+      <c r="B8" s="527">
+        <f>السيناريوهات!C38</f>
+        <v/>
+      </c>
+      <c r="C8" s="525" t="inlineStr">
+        <is>
+          <t>نقطة/ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="525" t="inlineStr">
+        <is>
+          <t>كاش باك الديزل %</t>
+        </is>
+      </c>
+      <c r="B9" s="528">
+        <f>السيناريوهات!C38/السيناريوهات!C6</f>
+        <v/>
+      </c>
+      <c r="C9" s="525" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="525" t="inlineStr">
+        <is>
+          <t>تكلفة درب على الديزل</t>
+        </is>
+      </c>
+      <c r="B10" s="527">
+        <f>السيناريوهات!C38/السيناريوهات!C6*100</f>
+        <v/>
+      </c>
+      <c r="C10" s="525" t="inlineStr">
+        <is>
+          <t>هللة/ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="525" t="inlineStr">
+        <is>
+          <t>صافي هامش درب على الديزل</t>
+        </is>
+      </c>
+      <c r="B11" s="527">
+        <f>السيناريوهات!C37/السيناريوهات!C36-(السيناريوهات!C38/السيناريوهات!C6*100)</f>
+        <v/>
+      </c>
+      <c r="C11" s="525" t="inlineStr">
+        <is>
+          <t>هللة/ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="524" t="inlineStr">
+        <is>
+          <t>الجدوى</t>
+        </is>
+      </c>
+      <c r="B12" s="524">
+        <f>IF(B11&gt;0.5,"✅ مربح",IF(B11&gt;0,"⚠️ هامش ضيق","🔴 خسارة"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="526" t="inlineStr">
+        <is>
+          <t>☕ الشركاء (كافيه/مطعم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="524" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="B15" s="524" t="inlineStr">
+        <is>
+          <t>القيمة</t>
+        </is>
+      </c>
+      <c r="C15" s="524" t="inlineStr">
+        <is>
+          <t>الوحدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="525" t="inlineStr">
+        <is>
+          <t>كسب العميل عند الشريك</t>
+        </is>
+      </c>
+      <c r="B16" s="527">
+        <f>السيناريوهات!C39</f>
+        <v/>
+      </c>
+      <c r="C16" s="525" t="inlineStr">
+        <is>
+          <t>نقطة/ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="525" t="inlineStr">
+        <is>
+          <t>كاش باك العميل %</t>
+        </is>
+      </c>
+      <c r="B17" s="528">
+        <f>السيناريوهات!C39/السيناريوهات!C6</f>
+        <v/>
+      </c>
+      <c r="C17" s="525" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="525" t="inlineStr">
+        <is>
+          <t>تكلفة درب (الشريك يموّل)</t>
+        </is>
+      </c>
+      <c r="B18" s="527">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C18" s="525" t="inlineStr">
+        <is>
+          <t>هللة/ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="525" t="inlineStr">
+        <is>
+          <t>مساهمة الشريك لدرب</t>
+        </is>
+      </c>
+      <c r="B19" s="527">
+        <f>السيناريوهات!C40</f>
+        <v/>
+      </c>
+      <c r="C19" s="525" t="inlineStr">
+        <is>
+          <t>هللة/ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="525" t="inlineStr">
+        <is>
+          <t>صافي لدرب من الشريك</t>
+        </is>
+      </c>
+      <c r="B20" s="527">
+        <f>السيناريوهات!C40-B18</f>
+        <v/>
+      </c>
+      <c r="C20" s="525" t="inlineStr">
+        <is>
+          <t>هللة/ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="526" t="inlineStr">
+        <is>
+          <t>🔬 أثر الريال على درب: وقود مقابل شريك</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="524" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="B23" s="524" t="inlineStr">
+        <is>
+          <t>ريال بنزين</t>
+        </is>
+      </c>
+      <c r="C23" s="524" t="inlineStr">
+        <is>
+          <t>ريال شريك</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="525" t="inlineStr">
+        <is>
+          <t>دخل/ربح درب (هللة)</t>
+        </is>
+      </c>
+      <c r="B24" s="527">
+        <f>السيناريوهات!C26/السيناريوهات!C11</f>
+        <v/>
+      </c>
+      <c r="C24" s="527">
+        <f>السيناريوهات!C40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="525" t="inlineStr">
+        <is>
+          <t>تكلفة الولاء على درب (هللة)</t>
+        </is>
+      </c>
+      <c r="B25" s="527">
+        <f>السيناريوهات!C7/السيناريوهات!C6*100</f>
+        <v/>
+      </c>
+      <c r="C25" s="527">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="525" t="inlineStr">
+        <is>
+          <t>الصافي على درب (هللة/ريال)</t>
+        </is>
+      </c>
+      <c r="B26" s="527">
+        <f>B24-B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="527">
+        <f>C24-C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="524" t="inlineStr">
+        <is>
+          <t>الخلاصة</t>
+        </is>
+      </c>
+      <c r="B27" s="524">
+        <f>IF(B26&gt;0,"✅ تكلفة احتفاظ","🔴 خسارة")</f>
+        <v/>
+      </c>
+      <c r="C27" s="524">
+        <f>IF(C26&gt;0,"✅ ربح صافٍ","—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="525" t="inlineStr">
+        <is>
+          <t>💡 الوقود يجذب (هامش رفيع) والشركاء يموّلون ويربّحون — أولوية درب: توقيع الشركاء</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="259" min="1" max="1"/>
@@ -5767,7 +6171,7 @@
         </is>
       </c>
       <c r="C26" s="316" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D26" s="305" t="inlineStr">
         <is>
@@ -5791,7 +6195,7 @@
         </is>
       </c>
       <c r="C27" s="316" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D27" s="305" t="inlineStr">
         <is>
@@ -5918,9 +6322,9 @@
       <c r="G33" s="300" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>🆕 معدلات إضافية موصى بها (مرجعية)</t>
+      <c r="A35" s="319" t="inlineStr">
+        <is>
+          <t>🆕 الاقتصاد الموسّع — مدخلات</t>
         </is>
       </c>
     </row>
@@ -5930,17 +6334,17 @@
           <t>+</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>كسب الديزل (نقطة/ريال)</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>25</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>هامش الديزل 4 هللات (2.2%) فقط → كاش باك 0.25%</t>
+      <c r="B36" s="320" t="inlineStr">
+        <is>
+          <t>سعر لتر الديزل (ريال)</t>
+        </is>
+      </c>
+      <c r="C36" s="321" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D36" s="320" t="inlineStr">
+        <is>
+          <t>يناير 2026</t>
         </is>
       </c>
     </row>
@@ -5950,17 +6354,17 @@
           <t>+</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>كسب الشركاء كافيه/مطعم (نقطة/ريال)</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>400</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>3–5% · ممولة من الشريك لا من درب</t>
+      <c r="B37" s="320" t="inlineStr">
+        <is>
+          <t>هامش الديزل (هللة/لتر)</t>
+        </is>
+      </c>
+      <c r="C37" s="321" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="320" t="inlineStr">
+        <is>
+          <t>ضعيف جداً</t>
         </is>
       </c>
     </row>
@@ -5970,16 +6374,76 @@
           <t>+</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="320" t="inlineStr">
+        <is>
+          <t>كسب الديزل (نقطة/ريال)</t>
+        </is>
+      </c>
+      <c r="C38" s="321" t="n">
+        <v>25</v>
+      </c>
+      <c r="D38" s="320" t="inlineStr">
+        <is>
+          <t>كاش باك 0.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="B39" s="320" t="inlineStr">
+        <is>
+          <t>كسب الشركاء (نقطة/ريال)</t>
+        </is>
+      </c>
+      <c r="C39" s="321" t="n">
+        <v>400</v>
+      </c>
+      <c r="D39" s="320" t="inlineStr">
+        <is>
+          <t>~4% ممولة من الشريك</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="B40" s="320" t="inlineStr">
+        <is>
+          <t>مساهمة الشريك لدرب (هللة/ريال)</t>
+        </is>
+      </c>
+      <c r="C40" s="321" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="320" t="inlineStr">
+        <is>
+          <t>ما يدفعه الشريك مقابل عملاء درب</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="B41" s="320" t="inlineStr">
         <is>
           <t>هدية الترحيب الموصى بها (نقطة)</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C41" s="321" t="n">
         <v>50000</v>
       </c>
-      <c r="D38">
-        <f> 5 ريال تكلفة فعلية · إحساس ضخم</f>
+      <c r="D41" s="320">
+        <f> 5 ريال تكلفة فعلية</f>
         <v/>
       </c>
     </row>
@@ -6324,7 +6788,7 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="260">
-      <c r="A2" s="319" t="inlineStr">
+      <c r="A2" s="322" t="inlineStr">
         <is>
           <t xml:space="preserve">  الفكرة الأساسية · النقاط للاستبدال · الإنفاق للترقية · شيئان منفصلان تماماً</t>
         </is>
@@ -6339,33 +6803,33 @@
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" s="260">
-      <c r="A5" s="320" t="inlineStr">
+      <c r="A5" s="323" t="inlineStr">
         <is>
           <t>💎 النقاط (Points)</t>
         </is>
       </c>
-      <c r="E5" s="321" t="n"/>
-      <c r="F5" s="322" t="inlineStr">
+      <c r="E5" s="324" t="n"/>
+      <c r="F5" s="325" t="inlineStr">
         <is>
           <t>🎯 المستويات (Tiers)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" s="260">
-      <c r="A6" s="323" t="inlineStr">
+      <c r="A6" s="326" t="inlineStr">
         <is>
           <t>للاستبدال فقط</t>
         </is>
       </c>
-      <c r="E6" s="321" t="n"/>
-      <c r="F6" s="324" t="inlineStr">
+      <c r="E6" s="324" t="n"/>
+      <c r="F6" s="327" t="inlineStr">
         <is>
           <t>للحالة والمزايا</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" s="260">
-      <c r="A7" s="325" t="inlineStr">
+      <c r="A7" s="328" t="inlineStr">
         <is>
           <t>✅ تكتسبها مع كل عملية تعبئة</t>
         </is>
@@ -6373,8 +6837,8 @@
       <c r="B7" s="293" t="n"/>
       <c r="C7" s="293" t="n"/>
       <c r="D7" s="287" t="n"/>
-      <c r="E7" s="321" t="n"/>
-      <c r="F7" s="325" t="inlineStr">
+      <c r="E7" s="324" t="n"/>
+      <c r="F7" s="328" t="inlineStr">
         <is>
           <t>✅ تترقى بناءً على الإنفاق السنوي</t>
         </is>
@@ -6384,7 +6848,7 @@
       <c r="I7" s="287" t="n"/>
     </row>
     <row r="8" ht="25.5" customHeight="1" s="260">
-      <c r="A8" s="325" t="inlineStr">
+      <c r="A8" s="328" t="inlineStr">
         <is>
           <t>✅ تستبدلها بمكافآت من الشركاء</t>
         </is>
@@ -6392,8 +6856,8 @@
       <c r="B8" s="293" t="n"/>
       <c r="C8" s="293" t="n"/>
       <c r="D8" s="287" t="n"/>
-      <c r="E8" s="321" t="n"/>
-      <c r="F8" s="325" t="inlineStr">
+      <c r="E8" s="324" t="n"/>
+      <c r="F8" s="328" t="inlineStr">
         <is>
           <t>✅ تمنحك معدل كسب أعلى</t>
         </is>
@@ -6403,7 +6867,7 @@
       <c r="I8" s="287" t="n"/>
     </row>
     <row r="9" ht="25.5" customHeight="1" s="260">
-      <c r="A9" s="325" t="inlineStr">
+      <c r="A9" s="328" t="inlineStr">
         <is>
           <t>✅ يمكن إهداؤها للعائلة</t>
         </is>
@@ -6411,8 +6875,8 @@
       <c r="B9" s="293" t="n"/>
       <c r="C9" s="293" t="n"/>
       <c r="D9" s="287" t="n"/>
-      <c r="E9" s="321" t="n"/>
-      <c r="F9" s="325" t="inlineStr">
+      <c r="E9" s="324" t="n"/>
+      <c r="F9" s="328" t="inlineStr">
         <is>
           <t>✅ تمنحك مزايا حصرية</t>
         </is>
@@ -6422,7 +6886,7 @@
       <c r="I9" s="287" t="n"/>
     </row>
     <row r="10" ht="25.5" customHeight="1" s="260">
-      <c r="A10" s="325" t="inlineStr">
+      <c r="A10" s="328" t="inlineStr">
         <is>
           <t>❌ تنقص عند الاستبدال</t>
         </is>
@@ -6430,8 +6894,8 @@
       <c r="B10" s="293" t="n"/>
       <c r="C10" s="293" t="n"/>
       <c r="D10" s="287" t="n"/>
-      <c r="E10" s="321" t="n"/>
-      <c r="F10" s="325" t="inlineStr">
+      <c r="E10" s="324" t="n"/>
+      <c r="F10" s="328" t="inlineStr">
         <is>
           <t>✅ لا تتأثر باستبدال النقاط</t>
         </is>
@@ -6441,7 +6905,7 @@
       <c r="I10" s="287" t="n"/>
     </row>
     <row r="11" ht="25.5" customHeight="1" s="260">
-      <c r="A11" s="325" t="inlineStr">
+      <c r="A11" s="328" t="inlineStr">
         <is>
           <t>🎯 ربط مباشر بقيمة الإنفاق</t>
         </is>
@@ -6449,8 +6913,8 @@
       <c r="B11" s="293" t="n"/>
       <c r="C11" s="293" t="n"/>
       <c r="D11" s="287" t="n"/>
-      <c r="E11" s="321" t="n"/>
-      <c r="F11" s="325" t="inlineStr">
+      <c r="E11" s="324" t="n"/>
+      <c r="F11" s="328" t="inlineStr">
         <is>
           <t>🎯 الإنفاق يحدد مستواك</t>
         </is>
@@ -6461,21 +6925,21 @@
     </row>
     <row r="12" ht="13.5" customHeight="1" s="260"/>
     <row r="13" ht="30" customHeight="1" s="260">
-      <c r="A13" s="326" t="inlineStr">
+      <c r="A13" s="329" t="inlineStr">
         <is>
           <t>📊 الفرق بين العدّاديْن</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" s="260">
-      <c r="A14" s="327" t="inlineStr">
+      <c r="A14" s="330" t="inlineStr">
         <is>
           <t>المعيار</t>
         </is>
       </c>
       <c r="B14" s="293" t="n"/>
       <c r="C14" s="287" t="n"/>
-      <c r="D14" s="328" t="inlineStr">
+      <c r="D14" s="331" t="inlineStr">
         <is>
           <t>💎 رصيد النقاط</t>
         </is>
@@ -6498,14 +6962,14 @@
       </c>
       <c r="B15" s="293" t="n"/>
       <c r="C15" s="287" t="n"/>
-      <c r="D15" s="329" t="inlineStr">
+      <c r="D15" s="332" t="inlineStr">
         <is>
           <t>الاستبدال بمكافآت</t>
         </is>
       </c>
       <c r="E15" s="293" t="n"/>
       <c r="F15" s="287" t="n"/>
-      <c r="G15" s="330" t="inlineStr">
+      <c r="G15" s="333" t="inlineStr">
         <is>
           <t>تحديد المستوى</t>
         </is>
@@ -6521,14 +6985,14 @@
       </c>
       <c r="B16" s="293" t="n"/>
       <c r="C16" s="287" t="n"/>
-      <c r="D16" s="329" t="inlineStr">
+      <c r="D16" s="332" t="inlineStr">
         <is>
           <t>مع كل تعبئة</t>
         </is>
       </c>
       <c r="E16" s="293" t="n"/>
       <c r="F16" s="287" t="n"/>
-      <c r="G16" s="330" t="inlineStr">
+      <c r="G16" s="333" t="inlineStr">
         <is>
           <t>مع كل تعبئة (إنفاق)</t>
         </is>
@@ -6544,14 +7008,14 @@
       </c>
       <c r="B17" s="293" t="n"/>
       <c r="C17" s="287" t="n"/>
-      <c r="D17" s="329" t="inlineStr">
+      <c r="D17" s="332" t="inlineStr">
         <is>
           <t>عند استبدال نقاط</t>
         </is>
       </c>
       <c r="E17" s="293" t="n"/>
       <c r="F17" s="287" t="n"/>
-      <c r="G17" s="330" t="inlineStr">
+      <c r="G17" s="333" t="inlineStr">
         <is>
           <t>لا ينقص داخل السنة</t>
         </is>
@@ -6567,14 +7031,14 @@
       </c>
       <c r="B18" s="293" t="n"/>
       <c r="C18" s="287" t="n"/>
-      <c r="D18" s="329" t="inlineStr">
+      <c r="D18" s="332" t="inlineStr">
         <is>
           <t>لا · رصيد متراكم</t>
         </is>
       </c>
       <c r="E18" s="293" t="n"/>
       <c r="F18" s="287" t="n"/>
-      <c r="G18" s="330" t="inlineStr">
+      <c r="G18" s="333" t="inlineStr">
         <is>
           <t>نعم · كل 12 شهر</t>
         </is>
@@ -6590,14 +7054,14 @@
       </c>
       <c r="B19" s="293" t="n"/>
       <c r="C19" s="287" t="n"/>
-      <c r="D19" s="329" t="inlineStr">
+      <c r="D19" s="332" t="inlineStr">
         <is>
           <t>❌ لا</t>
         </is>
       </c>
       <c r="E19" s="293" t="n"/>
       <c r="F19" s="287" t="n"/>
-      <c r="G19" s="330" t="inlineStr">
+      <c r="G19" s="333" t="inlineStr">
         <is>
           <t>✅ نعم</t>
         </is>
@@ -6613,14 +7077,14 @@
       </c>
       <c r="B20" s="293" t="n"/>
       <c r="C20" s="287" t="n"/>
-      <c r="D20" s="329" t="inlineStr">
+      <c r="D20" s="332" t="inlineStr">
         <is>
           <t>500K نقطة = 50 ريال</t>
         </is>
       </c>
       <c r="E20" s="293" t="n"/>
       <c r="F20" s="287" t="n"/>
-      <c r="G20" s="330" t="inlineStr">
+      <c r="G20" s="333" t="inlineStr">
         <is>
           <t>7,200 ر = فضي</t>
         </is>
@@ -6637,19 +7101,19 @@
       </c>
     </row>
     <row r="23" ht="37.5" customHeight="1" s="260">
-      <c r="A23" s="327" t="inlineStr">
+      <c r="A23" s="330" t="inlineStr">
         <is>
           <t>الوقت</t>
         </is>
       </c>
       <c r="B23" s="287" t="n"/>
-      <c r="C23" s="327" t="inlineStr">
+      <c r="C23" s="330" t="inlineStr">
         <is>
           <t>النشاط</t>
         </is>
       </c>
       <c r="D23" s="287" t="n"/>
-      <c r="E23" s="328" t="inlineStr">
+      <c r="E23" s="331" t="inlineStr">
         <is>
           <t>💎 ما يحدث للنقاط</t>
         </is>
@@ -6670,20 +7134,20 @@
         </is>
       </c>
       <c r="B24" s="287" t="n"/>
-      <c r="C24" s="325" t="inlineStr">
+      <c r="C24" s="328" t="inlineStr">
         <is>
           <t>تنفق 600 ر هذا الشهر</t>
         </is>
       </c>
       <c r="D24" s="287" t="n"/>
-      <c r="E24" s="331" t="inlineStr">
+      <c r="E24" s="334" t="inlineStr">
         <is>
           <t>+60,000 نقطة → الرصيد 60K</t>
         </is>
       </c>
       <c r="F24" s="293" t="n"/>
       <c r="G24" s="287" t="n"/>
-      <c r="H24" s="332" t="inlineStr">
+      <c r="H24" s="335" t="inlineStr">
         <is>
           <t>+600 ر تقدم → 600/14,400</t>
         </is>
@@ -6697,20 +7161,20 @@
         </is>
       </c>
       <c r="B25" s="287" t="n"/>
-      <c r="C25" s="325" t="inlineStr">
+      <c r="C25" s="328" t="inlineStr">
         <is>
           <t>تستمر بنفس المعدل</t>
         </is>
       </c>
       <c r="D25" s="287" t="n"/>
-      <c r="E25" s="331" t="inlineStr">
+      <c r="E25" s="334" t="inlineStr">
         <is>
           <t>+360,000 نقطة (المجموع 420K)</t>
         </is>
       </c>
       <c r="F25" s="293" t="n"/>
       <c r="G25" s="287" t="n"/>
-      <c r="H25" s="332" t="inlineStr">
+      <c r="H25" s="335" t="inlineStr">
         <is>
           <t>التقدم 4,200 ر → 🩶 فضي ✅</t>
         </is>
@@ -6724,20 +7188,20 @@
         </is>
       </c>
       <c r="B26" s="287" t="n"/>
-      <c r="C26" s="325" t="inlineStr">
+      <c r="C26" s="328" t="inlineStr">
         <is>
           <t>تستبدل 400K نقطة بقهوة</t>
         </is>
       </c>
       <c r="D26" s="287" t="n"/>
-      <c r="E26" s="331" t="inlineStr">
+      <c r="E26" s="334" t="inlineStr">
         <is>
           <t>⬇️ الرصيد ينزل إلى 20K</t>
         </is>
       </c>
       <c r="F26" s="293" t="n"/>
       <c r="G26" s="287" t="n"/>
-      <c r="H26" s="332" t="inlineStr">
+      <c r="H26" s="335" t="inlineStr">
         <is>
           <t>التقدم 5,400 · لا يتأثر ✅</t>
         </is>
@@ -6751,20 +7215,20 @@
         </is>
       </c>
       <c r="B27" s="287" t="n"/>
-      <c r="C27" s="325" t="inlineStr">
+      <c r="C27" s="328" t="inlineStr">
         <is>
           <t>الإنفاق السنوي 7,200 ر</t>
         </is>
       </c>
       <c r="D27" s="287" t="n"/>
-      <c r="E27" s="331" t="inlineStr">
+      <c r="E27" s="334" t="inlineStr">
         <is>
           <t>كاش باك 1.5% (الفضي)</t>
         </is>
       </c>
       <c r="F27" s="293" t="n"/>
       <c r="G27" s="287" t="n"/>
-      <c r="H27" s="332" t="inlineStr">
+      <c r="H27" s="335" t="inlineStr">
         <is>
           <t>التقدم 7,200 → 🩶 فضي مستمر</t>
         </is>
@@ -6778,20 +7242,20 @@
         </is>
       </c>
       <c r="B28" s="287" t="n"/>
-      <c r="C28" s="325" t="inlineStr">
+      <c r="C28" s="328" t="inlineStr">
         <is>
           <t>بداية سنة جديدة</t>
         </is>
       </c>
       <c r="D28" s="287" t="n"/>
-      <c r="E28" s="331" t="inlineStr">
+      <c r="E28" s="334" t="inlineStr">
         <is>
           <t>الرصيد محفوظ · لا ينقص</t>
         </is>
       </c>
       <c r="F28" s="293" t="n"/>
       <c r="G28" s="287" t="n"/>
-      <c r="H28" s="332" t="inlineStr">
+      <c r="H28" s="335" t="inlineStr">
         <is>
           <t>العدّاد يبدأ من 0 · المستوى محفوظ</t>
         </is>
@@ -6800,14 +7264,14 @@
     </row>
     <row r="29" ht="13.5" customHeight="1" s="260"/>
     <row r="30" ht="30" customHeight="1" s="260">
-      <c r="A30" s="333" t="inlineStr">
+      <c r="A30" s="336" t="inlineStr">
         <is>
           <t>🌟 الرسائل المفتاحية للعميل</t>
         </is>
       </c>
     </row>
     <row r="31" ht="31.5" customHeight="1" s="260">
-      <c r="A31" s="334" t="inlineStr">
+      <c r="A31" s="337" t="inlineStr">
         <is>
           <t>💯 استبدل نقاطك متى تشاء · مستواك لن يتأثر أبداً</t>
         </is>
@@ -6822,7 +7286,7 @@
       <c r="I31" s="287" t="n"/>
     </row>
     <row r="32" ht="31.5" customHeight="1" s="260">
-      <c r="A32" s="334" t="inlineStr">
+      <c r="A32" s="337" t="inlineStr">
         <is>
           <t>📈 كلما أنفقت أكثر · ارتقيت أعلى · لا علاقة لذلك بنقاطك</t>
         </is>
@@ -6837,7 +7301,7 @@
       <c r="I32" s="287" t="n"/>
     </row>
     <row r="33" ht="31.5" customHeight="1" s="260">
-      <c r="A33" s="334" t="inlineStr">
+      <c r="A33" s="337" t="inlineStr">
         <is>
           <t>🎁 النقاط هي متعتك · المستوى هو إنجازك · شيئان منفصلان</t>
         </is>
@@ -6852,7 +7316,7 @@
       <c r="I33" s="287" t="n"/>
     </row>
     <row r="34" ht="31.5" customHeight="1" s="260">
-      <c r="A34" s="334" t="inlineStr">
+      <c r="A34" s="337" t="inlineStr">
         <is>
           <t>🔒 مستواك محفوظ لمدة 12 شهر بعد الترقية · حتى لو قل إنفاقك</t>
         </is>
@@ -6994,7 +7458,7 @@
       </c>
     </row>
     <row r="5" ht="55.5" customHeight="1" s="260">
-      <c r="A5" s="335" t="inlineStr">
+      <c r="A5" s="338" t="inlineStr">
         <is>
           <t>💰 الإنفاق الشهري على الوقود (ريال) →</t>
         </is>
@@ -7003,11 +7467,11 @@
       <c r="C5" s="293" t="n"/>
       <c r="D5" s="293" t="n"/>
       <c r="E5" s="287" t="n"/>
-      <c r="F5" s="336" t="n">
+      <c r="F5" s="339" t="n">
         <v>600</v>
       </c>
       <c r="G5" s="287" t="n"/>
-      <c r="H5" s="337" t="inlineStr">
+      <c r="H5" s="340" t="inlineStr">
         <is>
           <t>← غيّر القيمة هنا</t>
         </is>
@@ -7017,33 +7481,33 @@
     </row>
     <row r="6" ht="13.5" customHeight="1" s="260"/>
     <row r="7" ht="30" customHeight="1" s="260">
-      <c r="A7" s="326" t="inlineStr">
+      <c r="A7" s="329" t="inlineStr">
         <is>
           <t>🎯 الملخص الفوري</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="260">
-      <c r="A8" s="338" t="inlineStr">
+      <c r="A8" s="341" t="inlineStr">
         <is>
           <t>📅 الإنفاق السنوي</t>
         </is>
       </c>
       <c r="B8" s="287" t="n"/>
-      <c r="C8" s="339" t="inlineStr">
+      <c r="C8" s="342" t="inlineStr">
         <is>
           <t>🎯 المستوى الحالي</t>
         </is>
       </c>
       <c r="D8" s="287" t="n"/>
-      <c r="E8" s="340" t="inlineStr">
+      <c r="E8" s="343" t="inlineStr">
         <is>
           <t>💎 نقاط/سنة</t>
         </is>
       </c>
       <c r="F8" s="293" t="n"/>
       <c r="G8" s="287" t="n"/>
-      <c r="H8" s="341" t="inlineStr">
+      <c r="H8" s="344" t="inlineStr">
         <is>
           <t>💰 القيمة المالية</t>
         </is>
@@ -7052,23 +7516,23 @@
       <c r="J8" s="287" t="n"/>
     </row>
     <row r="9" ht="55.5" customHeight="1" s="260">
-      <c r="A9" s="342">
+      <c r="A9" s="345">
         <f>F5*12</f>
         <v/>
       </c>
       <c r="B9" s="287" t="n"/>
-      <c r="C9" s="343">
+      <c r="C9" s="346">
         <f>IF(F5*12&lt;السيناريوهات!C16,"🤍 الأبيض",IF(F5*12&lt;السيناريوهات!C17,"🩶 الفضي","🟠 البرتقالي"))</f>
         <v/>
       </c>
       <c r="D9" s="287" t="n"/>
-      <c r="E9" s="344">
+      <c r="E9" s="347">
         <f>F5*12*IF(C9="🤍 الأبيض",السيناريوهات!C7,IF(C9="🩶 الفضي",السيناريوهات!C8,السيناريوهات!C9))</f>
         <v/>
       </c>
       <c r="F9" s="293" t="n"/>
       <c r="G9" s="287" t="n"/>
-      <c r="H9" s="345">
+      <c r="H9" s="348">
         <f>E9/السيناريوهات!C6</f>
         <v/>
       </c>
@@ -7076,26 +7540,26 @@
       <c r="J9" s="287" t="n"/>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="260">
-      <c r="A10" s="346" t="inlineStr">
+      <c r="A10" s="349" t="inlineStr">
         <is>
           <t>إنفاق على الوقود</t>
         </is>
       </c>
       <c r="B10" s="287" t="n"/>
-      <c r="C10" s="347" t="inlineStr">
+      <c r="C10" s="350" t="inlineStr">
         <is>
           <t>مستواك بناء على الإنفاق</t>
         </is>
       </c>
       <c r="D10" s="287" t="n"/>
-      <c r="E10" s="348" t="inlineStr">
+      <c r="E10" s="351" t="inlineStr">
         <is>
           <t>للاستبدال بمكافآت</t>
         </is>
       </c>
       <c r="F10" s="293" t="n"/>
       <c r="G10" s="287" t="n"/>
-      <c r="H10" s="349" t="inlineStr">
+      <c r="H10" s="352" t="inlineStr">
         <is>
           <t>قيمة الكاش باك السنوي</t>
         </is>
@@ -7112,25 +7576,25 @@
       </c>
     </row>
     <row r="13" ht="39.75" customHeight="1" s="260">
-      <c r="A13" s="350" t="inlineStr">
+      <c r="A13" s="353" t="inlineStr">
         <is>
           <t>🎯 المستوى التالي →</t>
         </is>
       </c>
       <c r="B13" s="293" t="n"/>
       <c r="C13" s="287" t="n"/>
-      <c r="D13" s="351">
+      <c r="D13" s="354">
         <f>IF(C9="🤍 الأبيض","🩶 الفضي",IF(C9="🩶 الفضي","🟠 البرتقالي","✨ أعلى مستوى"))</f>
         <v/>
       </c>
       <c r="E13" s="287" t="n"/>
-      <c r="F13" s="350" t="inlineStr">
+      <c r="F13" s="353" t="inlineStr">
         <is>
           <t>💪 الإنفاق المتبقي →</t>
         </is>
       </c>
       <c r="G13" s="287" t="n"/>
-      <c r="H13" s="352">
+      <c r="H13" s="355">
         <f>IF(C9="🤍 الأبيض",MAX(0,السيناريوهات!C16-F5*12),IF(C9="🩶 الفضي",MAX(0,السيناريوهات!C17-F5*12),0))</f>
         <v/>
       </c>
@@ -7138,13 +7602,13 @@
       <c r="J13" s="287" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1" s="260">
-      <c r="A14" s="353" t="inlineStr">
+      <c r="A14" s="356" t="inlineStr">
         <is>
           <t>نسبة التقدم</t>
         </is>
       </c>
       <c r="B14" s="287" t="n"/>
-      <c r="C14" s="354">
+      <c r="C14" s="357">
         <f>IF(C9="🤍 الأبيض",F5*12/السيناريوهات!C16,IF(C9="🩶 الفضي",(F5*12-السيناريوهات!C16)/(السيناريوهات!C17-السيناريوهات!C16),1))</f>
         <v/>
       </c>
@@ -7165,13 +7629,13 @@
       </c>
     </row>
     <row r="17" ht="31.5" customHeight="1" s="260">
-      <c r="A17" s="327" t="inlineStr">
+      <c r="A17" s="330" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
       </c>
       <c r="B17" s="287" t="n"/>
-      <c r="C17" s="328" t="inlineStr">
+      <c r="C17" s="331" t="inlineStr">
         <is>
           <t>💎 النقاط (للاستبدال)</t>
         </is>
@@ -7195,14 +7659,14 @@
         </is>
       </c>
       <c r="B18" s="287" t="n"/>
-      <c r="C18" s="329">
+      <c r="C18" s="332">
         <f>TEXT(F5*IF(C9="🤍 الأبيض",السيناريوهات!C7,IF(C9="🩶 الفضي",السيناريوهات!C8,السيناريوهات!C9)),"#,##0")&amp;" نقطة تُضاف"</f>
         <v/>
       </c>
       <c r="D18" s="293" t="n"/>
       <c r="E18" s="293" t="n"/>
       <c r="F18" s="287" t="n"/>
-      <c r="G18" s="330">
+      <c r="G18" s="333">
         <f>TEXT(F5,"#,##0")&amp;" ر تضاف للعدّاد"</f>
         <v/>
       </c>
@@ -7217,14 +7681,14 @@
         </is>
       </c>
       <c r="B19" s="287" t="n"/>
-      <c r="C19" s="329">
+      <c r="C19" s="332">
         <f>TEXT(E9,"#,##0")&amp;" نقطة (= "&amp;TEXT(H9,"#,##0")&amp;" ر)"</f>
         <v/>
       </c>
       <c r="D19" s="293" t="n"/>
       <c r="E19" s="293" t="n"/>
       <c r="F19" s="287" t="n"/>
-      <c r="G19" s="330">
+      <c r="G19" s="333">
         <f>TEXT(F5*12,"#,##0")&amp;" ر إنفاق سنوي"</f>
         <v/>
       </c>
@@ -7239,7 +7703,7 @@
         </is>
       </c>
       <c r="B20" s="287" t="n"/>
-      <c r="C20" s="329" t="inlineStr">
+      <c r="C20" s="332" t="inlineStr">
         <is>
           <t>تنقص بحسب قيمة المكافأة</t>
         </is>
@@ -7247,7 +7711,7 @@
       <c r="D20" s="293" t="n"/>
       <c r="E20" s="293" t="n"/>
       <c r="F20" s="287" t="n"/>
-      <c r="G20" s="330" t="inlineStr">
+      <c r="G20" s="333" t="inlineStr">
         <is>
           <t>لا تتأثر · المستوى محفوظ</t>
         </is>
@@ -7263,7 +7727,7 @@
         </is>
       </c>
       <c r="B21" s="287" t="n"/>
-      <c r="C21" s="329" t="inlineStr">
+      <c r="C21" s="332" t="inlineStr">
         <is>
           <t>الرصيد يبقى كما هو</t>
         </is>
@@ -7271,7 +7735,7 @@
       <c r="D21" s="293" t="n"/>
       <c r="E21" s="293" t="n"/>
       <c r="F21" s="287" t="n"/>
-      <c r="G21" s="330" t="inlineStr">
+      <c r="G21" s="333" t="inlineStr">
         <is>
           <t>العدّاد يبدأ من 0 · المستوى محفوظ 12 شهر</t>
         </is>
@@ -7282,7 +7746,7 @@
     </row>
     <row r="22" ht="13.5" customHeight="1" s="260"/>
     <row r="23" ht="31.5" customHeight="1" s="260">
-      <c r="A23" s="355" t="inlineStr">
+      <c r="A23" s="358" t="inlineStr">
         <is>
           <t>💡 جرّب · غيّر الإنفاق في F5 وشوف كيف تتغير كل الأرقام · النقاط والمستوى منفصلان تماماً</t>
         </is>
@@ -7356,30 +7820,30 @@
         </is>
       </c>
       <c r="B27" s="287" t="n"/>
-      <c r="C27" s="356" t="n">
+      <c r="C27" s="359" t="n">
         <v>600</v>
       </c>
-      <c r="D27" s="357">
+      <c r="D27" s="360">
         <f>C27*12</f>
         <v/>
       </c>
-      <c r="E27" s="358">
+      <c r="E27" s="361">
         <f>IF(D27&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(D27&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="F27" s="359">
+      <c r="F27" s="362">
         <f>D27*IF(E27="🤍 أبيض",السيناريوهات!$C$7,IF(E27="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="G27" s="360">
+      <c r="G27" s="363">
         <f>F27/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="H27" s="361">
+      <c r="H27" s="364">
         <f>G27/D27</f>
         <v/>
       </c>
-      <c r="I27" s="362" t="inlineStr">
+      <c r="I27" s="365" t="inlineStr">
         <is>
           <t>حالتك! · سيارة كورولا أو سنتافي</t>
         </is>
@@ -7393,30 +7857,30 @@
         </is>
       </c>
       <c r="B28" s="287" t="n"/>
-      <c r="C28" s="356" t="n">
+      <c r="C28" s="359" t="n">
         <v>1000</v>
       </c>
-      <c r="D28" s="357">
+      <c r="D28" s="360">
         <f>C28*12</f>
         <v/>
       </c>
-      <c r="E28" s="358">
+      <c r="E28" s="361">
         <f>IF(D28&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(D28&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="F28" s="359">
+      <c r="F28" s="362">
         <f>D28*IF(E28="🤍 أبيض",السيناريوهات!$C$7,IF(E28="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="G28" s="360">
+      <c r="G28" s="363">
         <f>F28/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="H28" s="361">
+      <c r="H28" s="364">
         <f>G28/D28</f>
         <v/>
       </c>
-      <c r="I28" s="362" t="inlineStr">
+      <c r="I28" s="365" t="inlineStr">
         <is>
           <t>سيارة متوسطة · استخدام يومي</t>
         </is>
@@ -7430,30 +7894,30 @@
         </is>
       </c>
       <c r="B29" s="287" t="n"/>
-      <c r="C29" s="356" t="n">
+      <c r="C29" s="359" t="n">
         <v>1500</v>
       </c>
-      <c r="D29" s="357">
+      <c r="D29" s="360">
         <f>C29*12</f>
         <v/>
       </c>
-      <c r="E29" s="358">
+      <c r="E29" s="361">
         <f>IF(D29&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(D29&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="F29" s="359">
+      <c r="F29" s="362">
         <f>D29*IF(E29="🤍 أبيض",السيناريوهات!$C$7,IF(E29="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="G29" s="360">
+      <c r="G29" s="363">
         <f>F29/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="H29" s="361">
+      <c r="H29" s="364">
         <f>G29/D29</f>
         <v/>
       </c>
-      <c r="I29" s="362" t="inlineStr">
+      <c r="I29" s="365" t="inlineStr">
         <is>
           <t>تاهو/باترول صغير</t>
         </is>
@@ -7467,30 +7931,30 @@
         </is>
       </c>
       <c r="B30" s="287" t="n"/>
-      <c r="C30" s="356" t="n">
+      <c r="C30" s="359" t="n">
         <v>2500</v>
       </c>
-      <c r="D30" s="357">
+      <c r="D30" s="360">
         <f>C30*12</f>
         <v/>
       </c>
-      <c r="E30" s="358">
+      <c r="E30" s="361">
         <f>IF(D30&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(D30&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="F30" s="359">
+      <c r="F30" s="362">
         <f>D30*IF(E30="🤍 أبيض",السيناريوهات!$C$7,IF(E30="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="G30" s="360">
+      <c r="G30" s="363">
         <f>F30/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="H30" s="361">
+      <c r="H30" s="364">
         <f>G30/D30</f>
         <v/>
       </c>
-      <c r="I30" s="362" t="inlineStr">
+      <c r="I30" s="365" t="inlineStr">
         <is>
           <t>عائلة نشطة · سيارتين</t>
         </is>
@@ -7504,30 +7968,30 @@
         </is>
       </c>
       <c r="B31" s="287" t="n"/>
-      <c r="C31" s="356" t="n">
+      <c r="C31" s="359" t="n">
         <v>4000</v>
       </c>
-      <c r="D31" s="357">
+      <c r="D31" s="360">
         <f>C31*12</f>
         <v/>
       </c>
-      <c r="E31" s="358">
+      <c r="E31" s="361">
         <f>IF(D31&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(D31&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="F31" s="359">
+      <c r="F31" s="362">
         <f>D31*IF(E31="🤍 أبيض",السيناريوهات!$C$7,IF(E31="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="G31" s="360">
+      <c r="G31" s="363">
         <f>F31/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="H31" s="361">
+      <c r="H31" s="364">
         <f>G31/D31</f>
         <v/>
       </c>
-      <c r="I31" s="362" t="inlineStr">
+      <c r="I31" s="365" t="inlineStr">
         <is>
           <t>أبو خالد · 3-4 سيارات</t>
         </is>
@@ -7541,30 +8005,30 @@
         </is>
       </c>
       <c r="B32" s="287" t="n"/>
-      <c r="C32" s="356" t="n">
+      <c r="C32" s="359" t="n">
         <v>8000</v>
       </c>
-      <c r="D32" s="357">
+      <c r="D32" s="360">
         <f>C32*12</f>
         <v/>
       </c>
-      <c r="E32" s="358">
+      <c r="E32" s="361">
         <f>IF(D32&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(D32&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="F32" s="359">
+      <c r="F32" s="362">
         <f>D32*IF(E32="🤍 أبيض",السيناريوهات!$C$7,IF(E32="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="G32" s="360">
+      <c r="G32" s="363">
         <f>F32/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="H32" s="361">
+      <c r="H32" s="364">
         <f>G32/D32</f>
         <v/>
       </c>
-      <c r="I32" s="362" t="inlineStr">
+      <c r="I32" s="365" t="inlineStr">
         <is>
           <t>شركة صغيرة · 4-5 سيارات</t>
         </is>
@@ -7702,7 +8166,7 @@
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1" s="260">
-      <c r="A2" s="319" t="inlineStr">
+      <c r="A2" s="322" t="inlineStr">
         <is>
           <t xml:space="preserve">  من إطلاق الوقود فقط إلى منظومة مكافآت شاملة · 18 شهراً</t>
         </is>
@@ -7717,35 +8181,35 @@
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" s="260">
-      <c r="A5" s="327" t="inlineStr">
+      <c r="A5" s="330" t="inlineStr">
         <is>
           <t>المرحلة</t>
         </is>
       </c>
-      <c r="B5" s="327" t="inlineStr">
+      <c r="B5" s="330" t="inlineStr">
         <is>
           <t>الفترة</t>
         </is>
       </c>
-      <c r="C5" s="327" t="inlineStr">
+      <c r="C5" s="330" t="inlineStr">
         <is>
           <t>العنوان</t>
         </is>
       </c>
-      <c r="D5" s="327" t="inlineStr">
+      <c r="D5" s="330" t="inlineStr">
         <is>
           <t>الهدف الرئيسي</t>
         </is>
       </c>
       <c r="E5" s="293" t="n"/>
       <c r="F5" s="287" t="n"/>
-      <c r="G5" s="327" t="inlineStr">
+      <c r="G5" s="330" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
       </c>
       <c r="H5" s="287" t="n"/>
-      <c r="I5" s="327" t="inlineStr">
+      <c r="I5" s="330" t="inlineStr">
         <is>
           <t>التكلفة المتوقعة</t>
         </is>
@@ -7753,22 +8217,22 @@
       <c r="J5" s="287" t="n"/>
     </row>
     <row r="6" ht="42" customHeight="1" s="260">
-      <c r="A6" s="363" t="inlineStr">
+      <c r="A6" s="366" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="B6" s="364" t="inlineStr">
+      <c r="B6" s="367" t="inlineStr">
         <is>
           <t>شهر 1-3</t>
         </is>
       </c>
-      <c r="C6" s="365" t="inlineStr">
+      <c r="C6" s="368" t="inlineStr">
         <is>
           <t>إطلاق الوقود</t>
         </is>
       </c>
-      <c r="D6" s="366" t="inlineStr">
+      <c r="D6" s="369" t="inlineStr">
         <is>
           <t>بناء قاعدة 50K مستخدم بالوقود فقط</t>
         </is>
@@ -7781,7 +8245,7 @@
         </is>
       </c>
       <c r="H6" s="287" t="n"/>
-      <c r="I6" s="367" t="inlineStr">
+      <c r="I6" s="370" t="inlineStr">
         <is>
           <t>2.3 مليون ر/سنة</t>
         </is>
@@ -7789,22 +8253,22 @@
       <c r="J6" s="287" t="n"/>
     </row>
     <row r="7" ht="42" customHeight="1" s="260">
-      <c r="A7" s="368" t="inlineStr">
+      <c r="A7" s="371" t="inlineStr">
         <is>
           <t>🔵</t>
         </is>
       </c>
-      <c r="B7" s="340" t="inlineStr">
+      <c r="B7" s="343" t="inlineStr">
         <is>
           <t>شهر 3-6</t>
         </is>
       </c>
-      <c r="C7" s="369" t="inlineStr">
+      <c r="C7" s="372" t="inlineStr">
         <is>
           <t>تفاوض المستأجرين</t>
         </is>
       </c>
-      <c r="D7" s="366" t="inlineStr">
+      <c r="D7" s="369" t="inlineStr">
         <is>
           <t>توقيع 3-5 عقود + Pilot كافيه واحد</t>
         </is>
@@ -7817,7 +8281,7 @@
         </is>
       </c>
       <c r="H7" s="287" t="n"/>
-      <c r="I7" s="367" t="inlineStr">
+      <c r="I7" s="370" t="inlineStr">
         <is>
           <t>+ تكاليف تكامل</t>
         </is>
@@ -7825,22 +8289,22 @@
       <c r="J7" s="287" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" s="260">
-      <c r="A8" s="370" t="inlineStr">
+      <c r="A8" s="373" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="B8" s="339" t="inlineStr">
+      <c r="B8" s="342" t="inlineStr">
         <is>
           <t>شهر 6-12</t>
         </is>
       </c>
-      <c r="C8" s="371" t="inlineStr">
+      <c r="C8" s="374" t="inlineStr">
         <is>
           <t>التوسع التدريجي</t>
         </is>
       </c>
-      <c r="D8" s="366" t="inlineStr">
+      <c r="D8" s="369" t="inlineStr">
         <is>
           <t>5+ أقسام نشطة + 100K مستخدم</t>
         </is>
@@ -7853,7 +8317,7 @@
         </is>
       </c>
       <c r="H8" s="287" t="n"/>
-      <c r="I8" s="367" t="inlineStr">
+      <c r="I8" s="370" t="inlineStr">
         <is>
           <t>3.5 مليون ر/سنة</t>
         </is>
@@ -7861,22 +8325,22 @@
       <c r="J8" s="287" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" s="260">
-      <c r="A9" s="372" t="inlineStr">
+      <c r="A9" s="375" t="inlineStr">
         <is>
           <t>🟠</t>
         </is>
       </c>
-      <c r="B9" s="373" t="inlineStr">
+      <c r="B9" s="376" t="inlineStr">
         <is>
           <t>شهر 12-18</t>
         </is>
       </c>
-      <c r="C9" s="374" t="inlineStr">
+      <c r="C9" s="377" t="inlineStr">
         <is>
           <t>النضج الكامل</t>
         </is>
       </c>
-      <c r="D9" s="366" t="inlineStr">
+      <c r="D9" s="369" t="inlineStr">
         <is>
           <t>200K مستخدم + 7+ أقسام + بطاقات مشتركة</t>
         </is>
@@ -7889,7 +8353,7 @@
         </is>
       </c>
       <c r="H9" s="287" t="n"/>
-      <c r="I9" s="367" t="inlineStr">
+      <c r="I9" s="370" t="inlineStr">
         <is>
           <t>5+ مليون ر/سنة</t>
         </is>
@@ -7905,26 +8369,26 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" s="260">
-      <c r="A12" s="327" t="inlineStr">
+      <c r="A12" s="330" t="inlineStr">
         <is>
           <t>المرحلة</t>
         </is>
       </c>
-      <c r="B12" s="327" t="inlineStr">
+      <c r="B12" s="330" t="inlineStr">
         <is>
           <t>الأنشطة الرئيسية</t>
         </is>
       </c>
       <c r="C12" s="293" t="n"/>
       <c r="D12" s="287" t="n"/>
-      <c r="E12" s="327" t="inlineStr">
+      <c r="E12" s="330" t="inlineStr">
         <is>
           <t>المخرجات المتوقعة</t>
         </is>
       </c>
       <c r="F12" s="293" t="n"/>
       <c r="G12" s="287" t="n"/>
-      <c r="H12" s="327" t="inlineStr">
+      <c r="H12" s="330" t="inlineStr">
         <is>
           <t>المخاطر والتحديات</t>
         </is>
@@ -7933,7 +8397,7 @@
       <c r="J12" s="287" t="n"/>
     </row>
     <row r="13" ht="109.5" customHeight="1" s="260">
-      <c r="A13" s="375" t="inlineStr">
+      <c r="A13" s="378" t="inlineStr">
         <is>
           <t>🟢
 المرحلة 1
@@ -7941,7 +8405,7 @@
 إطلاق الوقود</t>
         </is>
       </c>
-      <c r="B13" s="366" t="inlineStr">
+      <c r="B13" s="369" t="inlineStr">
         <is>
           <t>• إطلاق التطبيق رسمياً
 • حملة تسويقية كبرى
@@ -7951,7 +8415,7 @@
       </c>
       <c r="C13" s="293" t="n"/>
       <c r="D13" s="287" t="n"/>
-      <c r="E13" s="376" t="inlineStr">
+      <c r="E13" s="379" t="inlineStr">
         <is>
           <t>• 50,000+ مستخدم
 • 65% نسبة تنشيط
@@ -7961,7 +8425,7 @@
       </c>
       <c r="F13" s="293" t="n"/>
       <c r="G13" s="287" t="n"/>
-      <c r="H13" s="377" t="inlineStr">
+      <c r="H13" s="380" t="inlineStr">
         <is>
           <t>• مشاكل تقنية
 • ضعف التسويق
@@ -7973,7 +8437,7 @@
       <c r="J13" s="287" t="n"/>
     </row>
     <row r="14" ht="109.5" customHeight="1" s="260">
-      <c r="A14" s="378" t="inlineStr">
+      <c r="A14" s="381" t="inlineStr">
         <is>
           <t>🔵
 المرحلة 2
@@ -7981,7 +8445,7 @@
 تفاوض المستأجرين</t>
         </is>
       </c>
-      <c r="B14" s="366" t="inlineStr">
+      <c r="B14" s="369" t="inlineStr">
         <is>
           <t>• إعداد حقيبة عرض
 • اجتماعات مستأجرين
@@ -7991,7 +8455,7 @@
       </c>
       <c r="C14" s="293" t="n"/>
       <c r="D14" s="287" t="n"/>
-      <c r="E14" s="376" t="inlineStr">
+      <c r="E14" s="379" t="inlineStr">
         <is>
           <t>• 3-5 عقود موقعة
 • Pilot ناجح للكافيه
@@ -8001,7 +8465,7 @@
       </c>
       <c r="F14" s="293" t="n"/>
       <c r="G14" s="287" t="n"/>
-      <c r="H14" s="377" t="inlineStr">
+      <c r="H14" s="380" t="inlineStr">
         <is>
           <t>• رفض المستأجرين
 • شروط مالية صعبة
@@ -8013,7 +8477,7 @@
       <c r="J14" s="287" t="n"/>
     </row>
     <row r="15" ht="109.5" customHeight="1" s="260">
-      <c r="A15" s="379" t="inlineStr">
+      <c r="A15" s="382" t="inlineStr">
         <is>
           <t>🟣
 المرحلة 3
@@ -8021,7 +8485,7 @@
 التوسع التدريجي</t>
         </is>
       </c>
-      <c r="B15" s="366" t="inlineStr">
+      <c r="B15" s="369" t="inlineStr">
         <is>
           <t>• إطلاق قسم شهرياً
 • حملات حصرية
@@ -8031,7 +8495,7 @@
       </c>
       <c r="C15" s="293" t="n"/>
       <c r="D15" s="287" t="n"/>
-      <c r="E15" s="376" t="inlineStr">
+      <c r="E15" s="379" t="inlineStr">
         <is>
           <t>• 5+ أقسام نشطة
 • 100,000+ مستخدم
@@ -8041,7 +8505,7 @@
       </c>
       <c r="F15" s="293" t="n"/>
       <c r="G15" s="287" t="n"/>
-      <c r="H15" s="377" t="inlineStr">
+      <c r="H15" s="380" t="inlineStr">
         <is>
           <t>• فشل بعض الأقسام
 • تعقيد المضاعفات
@@ -8053,7 +8517,7 @@
       <c r="J15" s="287" t="n"/>
     </row>
     <row r="16" ht="109.5" customHeight="1" s="260">
-      <c r="A16" s="380" t="inlineStr">
+      <c r="A16" s="383" t="inlineStr">
         <is>
           <t>🟠
 المرحلة 4
@@ -8061,7 +8525,7 @@
 النضج الكامل</t>
         </is>
       </c>
-      <c r="B16" s="366" t="inlineStr">
+      <c r="B16" s="369" t="inlineStr">
         <is>
           <t>• حملات موسمية
 • بطاقات مشتركة
@@ -8071,7 +8535,7 @@
       </c>
       <c r="C16" s="293" t="n"/>
       <c r="D16" s="287" t="n"/>
-      <c r="E16" s="376" t="inlineStr">
+      <c r="E16" s="379" t="inlineStr">
         <is>
           <t>• 200,000+ مستخدم
 • 7+ أقسام
@@ -8081,7 +8545,7 @@
       </c>
       <c r="F16" s="293" t="n"/>
       <c r="G16" s="287" t="n"/>
-      <c r="H16" s="377" t="inlineStr">
+      <c r="H16" s="380" t="inlineStr">
         <is>
           <t>• زيادة التكاليف
 • منافسة ساسكو
@@ -8101,42 +8565,42 @@
       </c>
     </row>
     <row r="19" ht="39.75" customHeight="1" s="260">
-      <c r="A19" s="327" t="inlineStr">
+      <c r="A19" s="330" t="inlineStr">
         <is>
           <t>النشاط</t>
         </is>
       </c>
-      <c r="B19" s="375" t="inlineStr">
+      <c r="B19" s="378" t="inlineStr">
         <is>
           <t>Q1
 شهر 1-3</t>
         </is>
       </c>
-      <c r="C19" s="378" t="inlineStr">
+      <c r="C19" s="381" t="inlineStr">
         <is>
           <t>Q2
 شهر 4-6</t>
         </is>
       </c>
-      <c r="D19" s="379" t="inlineStr">
+      <c r="D19" s="382" t="inlineStr">
         <is>
           <t>Q3
 شهر 7-9</t>
         </is>
       </c>
-      <c r="E19" s="379" t="inlineStr">
+      <c r="E19" s="382" t="inlineStr">
         <is>
           <t>Q4
 شهر 10-12</t>
         </is>
       </c>
-      <c r="F19" s="380" t="inlineStr">
+      <c r="F19" s="383" t="inlineStr">
         <is>
           <t>Q5
 شهر 13-15</t>
         </is>
       </c>
-      <c r="G19" s="380" t="inlineStr">
+      <c r="G19" s="383" t="inlineStr">
         <is>
           <t>Q6
 شهر 16-18</t>
@@ -8151,7 +8615,7 @@
       <c r="J19" s="287" t="n"/>
     </row>
     <row r="20" ht="25.5" customHeight="1" s="260">
-      <c r="A20" s="381" t="inlineStr">
+      <c r="A20" s="384" t="inlineStr">
         <is>
           <t>إطلاق الوقود</t>
         </is>
@@ -8174,7 +8638,7 @@
       <c r="E20" s="284" t="n"/>
       <c r="F20" s="284" t="n"/>
       <c r="G20" s="284" t="n"/>
-      <c r="H20" s="382" t="inlineStr">
+      <c r="H20" s="385" t="inlineStr">
         <is>
           <t>50K مستخدم Q1 · المنتج الأساسي</t>
         </is>
@@ -8183,7 +8647,7 @@
       <c r="J20" s="287" t="n"/>
     </row>
     <row r="21" ht="25.5" customHeight="1" s="260">
-      <c r="A21" s="381" t="inlineStr">
+      <c r="A21" s="384" t="inlineStr">
         <is>
           <t>التسويق الكبير</t>
         </is>
@@ -8218,7 +8682,7 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="H21" s="382" t="inlineStr">
+      <c r="H21" s="385" t="inlineStr">
         <is>
           <t>حملة إطلاق كبرى ثم متابعة</t>
         </is>
@@ -8227,7 +8691,7 @@
       <c r="J21" s="287" t="n"/>
     </row>
     <row r="22" ht="25.5" customHeight="1" s="260">
-      <c r="A22" s="381" t="inlineStr">
+      <c r="A22" s="384" t="inlineStr">
         <is>
           <t>تفاوض المستأجرين</t>
         </is>
@@ -8250,7 +8714,7 @@
       </c>
       <c r="F22" s="284" t="n"/>
       <c r="G22" s="284" t="n"/>
-      <c r="H22" s="382" t="inlineStr">
+      <c r="H22" s="385" t="inlineStr">
         <is>
           <t>5+ عقود بنهاية Q3</t>
         </is>
@@ -8259,7 +8723,7 @@
       <c r="J22" s="287" t="n"/>
     </row>
     <row r="23" ht="25.5" customHeight="1" s="260">
-      <c r="A23" s="381" t="inlineStr">
+      <c r="A23" s="384" t="inlineStr">
         <is>
           <t>Pilot الكافيه</t>
         </is>
@@ -8278,7 +8742,7 @@
       </c>
       <c r="F23" s="284" t="n"/>
       <c r="G23" s="284" t="n"/>
-      <c r="H23" s="382" t="inlineStr">
+      <c r="H23" s="385" t="inlineStr">
         <is>
           <t>محطة واحدة كتجربة</t>
         </is>
@@ -8287,7 +8751,7 @@
       <c r="J23" s="287" t="n"/>
     </row>
     <row r="24" ht="25.5" customHeight="1" s="260">
-      <c r="A24" s="381" t="inlineStr">
+      <c r="A24" s="384" t="inlineStr">
         <is>
           <t>إضافة المغسلة</t>
         </is>
@@ -8310,7 +8774,7 @@
           <t>🟣</t>
         </is>
       </c>
-      <c r="H24" s="382" t="inlineStr">
+      <c r="H24" s="385" t="inlineStr">
         <is>
           <t>بعد نجاح الكافيه</t>
         </is>
@@ -8319,7 +8783,7 @@
       <c r="J24" s="287" t="n"/>
     </row>
     <row r="25" ht="25.5" customHeight="1" s="260">
-      <c r="A25" s="381" t="inlineStr">
+      <c r="A25" s="384" t="inlineStr">
         <is>
           <t>إضافة الزيوت/سوبرماركت</t>
         </is>
@@ -8338,7 +8802,7 @@
           <t>🟣🟣 Launch</t>
         </is>
       </c>
-      <c r="H25" s="382" t="inlineStr">
+      <c r="H25" s="385" t="inlineStr">
         <is>
           <t>أقسام سهلة الإضافة</t>
         </is>
@@ -8347,7 +8811,7 @@
       <c r="J25" s="287" t="n"/>
     </row>
     <row r="26" ht="25.5" customHeight="1" s="260">
-      <c r="A26" s="381" t="inlineStr">
+      <c r="A26" s="384" t="inlineStr">
         <is>
           <t>حملات موسمية</t>
         </is>
@@ -8378,7 +8842,7 @@
           <t>🟢 صيف</t>
         </is>
       </c>
-      <c r="H26" s="382" t="inlineStr">
+      <c r="H26" s="385" t="inlineStr">
         <is>
           <t>حملات حصرية كل ربع</t>
         </is>
@@ -8387,7 +8851,7 @@
       <c r="J26" s="287" t="n"/>
     </row>
     <row r="27" ht="25.5" customHeight="1" s="260">
-      <c r="A27" s="381" t="inlineStr">
+      <c r="A27" s="384" t="inlineStr">
         <is>
           <t>بطاقات مشتركة</t>
         </is>
@@ -8406,7 +8870,7 @@
           <t>🟠🟠 إطلاق</t>
         </is>
       </c>
-      <c r="H27" s="382" t="inlineStr">
+      <c r="H27" s="385" t="inlineStr">
         <is>
           <t>تعاون مع بنك سعودي</t>
         </is>
@@ -8505,7 +8969,7 @@
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1" s="260">
-      <c r="A2" s="319" t="inlineStr">
+      <c r="A2" s="322" t="inlineStr">
         <is>
           <t xml:space="preserve">  قاعدة بيانات المستأجرين · بنود التفاوض · النموذج المالي لكل سيناريو</t>
         </is>
@@ -8585,41 +9049,41 @@
       <c r="A6" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="383" t="inlineStr">
+      <c r="B6" s="386" t="inlineStr">
         <is>
           <t>سلسلة كافيه (مثال: ستاربكس)</t>
         </is>
       </c>
-      <c r="C6" s="384" t="inlineStr">
+      <c r="C6" s="387" t="inlineStr">
         <is>
           <t>كافيه</t>
         </is>
       </c>
-      <c r="D6" s="384" t="n">
+      <c r="D6" s="387" t="n">
         <v>30</v>
       </c>
-      <c r="E6" s="385" t="n">
+      <c r="E6" s="388" t="n">
         <v>150000</v>
       </c>
-      <c r="F6" s="386" t="n">
+      <c r="F6" s="389" t="n">
         <v>0.65</v>
       </c>
-      <c r="G6" s="384" t="inlineStr">
+      <c r="G6" s="387" t="inlineStr">
         <is>
           <t>مشاركة 50/50</t>
         </is>
       </c>
-      <c r="H6" s="387" t="n">
+      <c r="H6" s="390" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="384" t="inlineStr">
+      <c r="I6" s="387" t="inlineStr">
         <is>
           <t>لم نتواصل</t>
         </is>
       </c>
-      <c r="J6" s="388" t="n"/>
-      <c r="K6" s="388" t="n"/>
-      <c r="L6" s="389" t="inlineStr">
+      <c r="J6" s="391" t="n"/>
+      <c r="K6" s="391" t="n"/>
+      <c r="L6" s="392" t="inlineStr">
         <is>
           <t>هدف استراتيجي · حضور قوي</t>
         </is>
@@ -8629,41 +9093,41 @@
       <c r="A7" s="303" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="383" t="inlineStr">
+      <c r="B7" s="386" t="inlineStr">
         <is>
           <t>كافيه محلي (دانكن/تيم هورتنز)</t>
         </is>
       </c>
-      <c r="C7" s="384" t="inlineStr">
+      <c r="C7" s="387" t="inlineStr">
         <is>
           <t>كافيه</t>
         </is>
       </c>
-      <c r="D7" s="384" t="n">
+      <c r="D7" s="387" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="385" t="n">
+      <c r="E7" s="388" t="n">
         <v>100000</v>
       </c>
-      <c r="F7" s="386" t="n">
+      <c r="F7" s="389" t="n">
         <v>0.55</v>
       </c>
-      <c r="G7" s="384" t="inlineStr">
+      <c r="G7" s="387" t="inlineStr">
         <is>
           <t>مشاركة 70/30 (المستأجر)</t>
         </is>
       </c>
-      <c r="H7" s="387" t="n">
+      <c r="H7" s="390" t="n">
         <v>1.5</v>
       </c>
-      <c r="I7" s="384" t="inlineStr">
+      <c r="I7" s="387" t="inlineStr">
         <is>
           <t>لم نتواصل</t>
         </is>
       </c>
-      <c r="J7" s="388" t="n"/>
-      <c r="K7" s="388" t="n"/>
-      <c r="L7" s="389" t="inlineStr">
+      <c r="J7" s="391" t="n"/>
+      <c r="K7" s="391" t="n"/>
+      <c r="L7" s="392" t="inlineStr">
         <is>
           <t>مرونة أعلى من العالمية</t>
         </is>
@@ -8673,41 +9137,41 @@
       <c r="A8" s="303" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="383" t="inlineStr">
+      <c r="B8" s="386" t="inlineStr">
         <is>
           <t>سلسلة سوبرماركت (مثال: العثيم)</t>
         </is>
       </c>
-      <c r="C8" s="384" t="inlineStr">
+      <c r="C8" s="387" t="inlineStr">
         <is>
           <t>سوبرماركت</t>
         </is>
       </c>
-      <c r="D8" s="384" t="n">
+      <c r="D8" s="387" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="385" t="n">
+      <c r="E8" s="388" t="n">
         <v>500000</v>
       </c>
-      <c r="F8" s="386" t="n">
+      <c r="F8" s="389" t="n">
         <v>0.2</v>
       </c>
-      <c r="G8" s="384" t="inlineStr">
+      <c r="G8" s="387" t="inlineStr">
         <is>
           <t>مشاركة 30/70 (درب)</t>
         </is>
       </c>
-      <c r="H8" s="387" t="n">
+      <c r="H8" s="390" t="n">
         <v>0.5</v>
       </c>
-      <c r="I8" s="384" t="inlineStr">
+      <c r="I8" s="387" t="inlineStr">
         <is>
           <t>لم نتواصل</t>
         </is>
       </c>
-      <c r="J8" s="388" t="n"/>
-      <c r="K8" s="388" t="n"/>
-      <c r="L8" s="389" t="inlineStr">
+      <c r="J8" s="391" t="n"/>
+      <c r="K8" s="391" t="n"/>
+      <c r="L8" s="392" t="inlineStr">
         <is>
           <t>حجم كبير · هامش منخفض</t>
         </is>
@@ -8717,41 +9181,41 @@
       <c r="A9" s="303" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="383" t="inlineStr">
+      <c r="B9" s="386" t="inlineStr">
         <is>
           <t>مغسلة (مثال: Magic Wash)</t>
         </is>
       </c>
-      <c r="C9" s="384" t="inlineStr">
+      <c r="C9" s="387" t="inlineStr">
         <is>
           <t>مغسلة</t>
         </is>
       </c>
-      <c r="D9" s="384" t="n">
+      <c r="D9" s="387" t="n">
         <v>50</v>
       </c>
-      <c r="E9" s="385" t="n">
+      <c r="E9" s="388" t="n">
         <v>80000</v>
       </c>
-      <c r="F9" s="386" t="n">
+      <c r="F9" s="389" t="n">
         <v>0.7</v>
       </c>
-      <c r="G9" s="384" t="inlineStr">
+      <c r="G9" s="387" t="inlineStr">
         <is>
           <t>المستأجر يدفع 100%</t>
         </is>
       </c>
-      <c r="H9" s="387" t="n">
+      <c r="H9" s="390" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="384" t="inlineStr">
+      <c r="I9" s="387" t="inlineStr">
         <is>
           <t>لم نتواصل</t>
         </is>
       </c>
-      <c r="J9" s="388" t="n"/>
-      <c r="K9" s="388" t="n"/>
-      <c r="L9" s="389" t="inlineStr">
+      <c r="J9" s="391" t="n"/>
+      <c r="K9" s="391" t="n"/>
+      <c r="L9" s="392" t="inlineStr">
         <is>
           <t>خدمة درب الخاصة</t>
         </is>
@@ -8761,41 +9225,41 @@
       <c r="A10" s="303" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="383" t="inlineStr">
+      <c r="B10" s="386" t="inlineStr">
         <is>
           <t>مطعم سريع (مثال: البيك/كودو)</t>
         </is>
       </c>
-      <c r="C10" s="384" t="inlineStr">
+      <c r="C10" s="387" t="inlineStr">
         <is>
           <t>مطعم</t>
         </is>
       </c>
-      <c r="D10" s="384" t="n">
+      <c r="D10" s="387" t="n">
         <v>35</v>
       </c>
-      <c r="E10" s="385" t="n">
+      <c r="E10" s="388" t="n">
         <v>200000</v>
       </c>
-      <c r="F10" s="386" t="n">
+      <c r="F10" s="389" t="n">
         <v>0.45</v>
       </c>
-      <c r="G10" s="384" t="inlineStr">
+      <c r="G10" s="387" t="inlineStr">
         <is>
           <t>مشاركة 50/50</t>
         </is>
       </c>
-      <c r="H10" s="387" t="n">
+      <c r="H10" s="390" t="n">
         <v>1.5</v>
       </c>
-      <c r="I10" s="384" t="inlineStr">
+      <c r="I10" s="387" t="inlineStr">
         <is>
           <t>لم نتواصل</t>
         </is>
       </c>
-      <c r="J10" s="388" t="n"/>
-      <c r="K10" s="388" t="n"/>
-      <c r="L10" s="389" t="inlineStr">
+      <c r="J10" s="391" t="n"/>
+      <c r="K10" s="391" t="n"/>
+      <c r="L10" s="392" t="inlineStr">
         <is>
           <t>حركة عالية · فرص ممتازة</t>
         </is>
@@ -8805,267 +9269,267 @@
       <c r="A11" s="303" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="390" t="n"/>
-      <c r="C11" s="391" t="n"/>
-      <c r="D11" s="391" t="n"/>
-      <c r="E11" s="392" t="n"/>
-      <c r="F11" s="393" t="n"/>
-      <c r="G11" s="391" t="n"/>
-      <c r="H11" s="394" t="n"/>
-      <c r="I11" s="391" t="n"/>
-      <c r="J11" s="395" t="n"/>
-      <c r="K11" s="395" t="n"/>
-      <c r="L11" s="390" t="n"/>
+      <c r="B11" s="393" t="n"/>
+      <c r="C11" s="394" t="n"/>
+      <c r="D11" s="394" t="n"/>
+      <c r="E11" s="395" t="n"/>
+      <c r="F11" s="396" t="n"/>
+      <c r="G11" s="394" t="n"/>
+      <c r="H11" s="397" t="n"/>
+      <c r="I11" s="394" t="n"/>
+      <c r="J11" s="398" t="n"/>
+      <c r="K11" s="398" t="n"/>
+      <c r="L11" s="393" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="260">
       <c r="A12" s="303" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="390" t="n"/>
-      <c r="C12" s="391" t="n"/>
-      <c r="D12" s="391" t="n"/>
-      <c r="E12" s="392" t="n"/>
-      <c r="F12" s="393" t="n"/>
-      <c r="G12" s="391" t="n"/>
-      <c r="H12" s="394" t="n"/>
-      <c r="I12" s="391" t="n"/>
-      <c r="J12" s="395" t="n"/>
-      <c r="K12" s="395" t="n"/>
-      <c r="L12" s="390" t="n"/>
+      <c r="B12" s="393" t="n"/>
+      <c r="C12" s="394" t="n"/>
+      <c r="D12" s="394" t="n"/>
+      <c r="E12" s="395" t="n"/>
+      <c r="F12" s="396" t="n"/>
+      <c r="G12" s="394" t="n"/>
+      <c r="H12" s="397" t="n"/>
+      <c r="I12" s="394" t="n"/>
+      <c r="J12" s="398" t="n"/>
+      <c r="K12" s="398" t="n"/>
+      <c r="L12" s="393" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1" s="260">
       <c r="A13" s="303" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="390" t="n"/>
-      <c r="C13" s="391" t="n"/>
-      <c r="D13" s="391" t="n"/>
-      <c r="E13" s="392" t="n"/>
-      <c r="F13" s="393" t="n"/>
-      <c r="G13" s="391" t="n"/>
-      <c r="H13" s="394" t="n"/>
-      <c r="I13" s="391" t="n"/>
-      <c r="J13" s="395" t="n"/>
-      <c r="K13" s="395" t="n"/>
-      <c r="L13" s="390" t="n"/>
+      <c r="B13" s="393" t="n"/>
+      <c r="C13" s="394" t="n"/>
+      <c r="D13" s="394" t="n"/>
+      <c r="E13" s="395" t="n"/>
+      <c r="F13" s="396" t="n"/>
+      <c r="G13" s="394" t="n"/>
+      <c r="H13" s="397" t="n"/>
+      <c r="I13" s="394" t="n"/>
+      <c r="J13" s="398" t="n"/>
+      <c r="K13" s="398" t="n"/>
+      <c r="L13" s="393" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1" s="260">
       <c r="A14" s="303" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="390" t="n"/>
-      <c r="C14" s="391" t="n"/>
-      <c r="D14" s="391" t="n"/>
-      <c r="E14" s="392" t="n"/>
-      <c r="F14" s="393" t="n"/>
-      <c r="G14" s="391" t="n"/>
-      <c r="H14" s="394" t="n"/>
-      <c r="I14" s="391" t="n"/>
-      <c r="J14" s="395" t="n"/>
-      <c r="K14" s="395" t="n"/>
-      <c r="L14" s="390" t="n"/>
+      <c r="B14" s="393" t="n"/>
+      <c r="C14" s="394" t="n"/>
+      <c r="D14" s="394" t="n"/>
+      <c r="E14" s="395" t="n"/>
+      <c r="F14" s="396" t="n"/>
+      <c r="G14" s="394" t="n"/>
+      <c r="H14" s="397" t="n"/>
+      <c r="I14" s="394" t="n"/>
+      <c r="J14" s="398" t="n"/>
+      <c r="K14" s="398" t="n"/>
+      <c r="L14" s="393" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1" s="260">
       <c r="A15" s="303" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="390" t="n"/>
-      <c r="C15" s="391" t="n"/>
-      <c r="D15" s="391" t="n"/>
-      <c r="E15" s="392" t="n"/>
-      <c r="F15" s="393" t="n"/>
-      <c r="G15" s="391" t="n"/>
-      <c r="H15" s="394" t="n"/>
-      <c r="I15" s="391" t="n"/>
-      <c r="J15" s="395" t="n"/>
-      <c r="K15" s="395" t="n"/>
-      <c r="L15" s="390" t="n"/>
+      <c r="B15" s="393" t="n"/>
+      <c r="C15" s="394" t="n"/>
+      <c r="D15" s="394" t="n"/>
+      <c r="E15" s="395" t="n"/>
+      <c r="F15" s="396" t="n"/>
+      <c r="G15" s="394" t="n"/>
+      <c r="H15" s="397" t="n"/>
+      <c r="I15" s="394" t="n"/>
+      <c r="J15" s="398" t="n"/>
+      <c r="K15" s="398" t="n"/>
+      <c r="L15" s="393" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1" s="260">
       <c r="A16" s="303" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="390" t="n"/>
-      <c r="C16" s="391" t="n"/>
-      <c r="D16" s="391" t="n"/>
-      <c r="E16" s="392" t="n"/>
-      <c r="F16" s="393" t="n"/>
-      <c r="G16" s="391" t="n"/>
-      <c r="H16" s="394" t="n"/>
-      <c r="I16" s="391" t="n"/>
-      <c r="J16" s="395" t="n"/>
-      <c r="K16" s="395" t="n"/>
-      <c r="L16" s="390" t="n"/>
+      <c r="B16" s="393" t="n"/>
+      <c r="C16" s="394" t="n"/>
+      <c r="D16" s="394" t="n"/>
+      <c r="E16" s="395" t="n"/>
+      <c r="F16" s="396" t="n"/>
+      <c r="G16" s="394" t="n"/>
+      <c r="H16" s="397" t="n"/>
+      <c r="I16" s="394" t="n"/>
+      <c r="J16" s="398" t="n"/>
+      <c r="K16" s="398" t="n"/>
+      <c r="L16" s="393" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="260">
       <c r="A17" s="303" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="390" t="n"/>
-      <c r="C17" s="391" t="n"/>
-      <c r="D17" s="391" t="n"/>
-      <c r="E17" s="392" t="n"/>
-      <c r="F17" s="393" t="n"/>
-      <c r="G17" s="391" t="n"/>
-      <c r="H17" s="394" t="n"/>
-      <c r="I17" s="391" t="n"/>
-      <c r="J17" s="395" t="n"/>
-      <c r="K17" s="395" t="n"/>
-      <c r="L17" s="390" t="n"/>
+      <c r="B17" s="393" t="n"/>
+      <c r="C17" s="394" t="n"/>
+      <c r="D17" s="394" t="n"/>
+      <c r="E17" s="395" t="n"/>
+      <c r="F17" s="396" t="n"/>
+      <c r="G17" s="394" t="n"/>
+      <c r="H17" s="397" t="n"/>
+      <c r="I17" s="394" t="n"/>
+      <c r="J17" s="398" t="n"/>
+      <c r="K17" s="398" t="n"/>
+      <c r="L17" s="393" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="260">
       <c r="A18" s="303" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="390" t="n"/>
-      <c r="C18" s="391" t="n"/>
-      <c r="D18" s="391" t="n"/>
-      <c r="E18" s="392" t="n"/>
-      <c r="F18" s="393" t="n"/>
-      <c r="G18" s="391" t="n"/>
-      <c r="H18" s="394" t="n"/>
-      <c r="I18" s="391" t="n"/>
-      <c r="J18" s="395" t="n"/>
-      <c r="K18" s="395" t="n"/>
-      <c r="L18" s="390" t="n"/>
+      <c r="B18" s="393" t="n"/>
+      <c r="C18" s="394" t="n"/>
+      <c r="D18" s="394" t="n"/>
+      <c r="E18" s="395" t="n"/>
+      <c r="F18" s="396" t="n"/>
+      <c r="G18" s="394" t="n"/>
+      <c r="H18" s="397" t="n"/>
+      <c r="I18" s="394" t="n"/>
+      <c r="J18" s="398" t="n"/>
+      <c r="K18" s="398" t="n"/>
+      <c r="L18" s="393" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="260">
       <c r="A19" s="303" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="390" t="n"/>
-      <c r="C19" s="391" t="n"/>
-      <c r="D19" s="391" t="n"/>
-      <c r="E19" s="392" t="n"/>
-      <c r="F19" s="393" t="n"/>
-      <c r="G19" s="391" t="n"/>
-      <c r="H19" s="394" t="n"/>
-      <c r="I19" s="391" t="n"/>
-      <c r="J19" s="395" t="n"/>
-      <c r="K19" s="395" t="n"/>
-      <c r="L19" s="390" t="n"/>
+      <c r="B19" s="393" t="n"/>
+      <c r="C19" s="394" t="n"/>
+      <c r="D19" s="394" t="n"/>
+      <c r="E19" s="395" t="n"/>
+      <c r="F19" s="396" t="n"/>
+      <c r="G19" s="394" t="n"/>
+      <c r="H19" s="397" t="n"/>
+      <c r="I19" s="394" t="n"/>
+      <c r="J19" s="398" t="n"/>
+      <c r="K19" s="398" t="n"/>
+      <c r="L19" s="393" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="260">
       <c r="A20" s="303" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="390" t="n"/>
-      <c r="C20" s="391" t="n"/>
-      <c r="D20" s="391" t="n"/>
-      <c r="E20" s="392" t="n"/>
-      <c r="F20" s="393" t="n"/>
-      <c r="G20" s="391" t="n"/>
-      <c r="H20" s="394" t="n"/>
-      <c r="I20" s="391" t="n"/>
-      <c r="J20" s="395" t="n"/>
-      <c r="K20" s="395" t="n"/>
-      <c r="L20" s="390" t="n"/>
+      <c r="B20" s="393" t="n"/>
+      <c r="C20" s="394" t="n"/>
+      <c r="D20" s="394" t="n"/>
+      <c r="E20" s="395" t="n"/>
+      <c r="F20" s="396" t="n"/>
+      <c r="G20" s="394" t="n"/>
+      <c r="H20" s="397" t="n"/>
+      <c r="I20" s="394" t="n"/>
+      <c r="J20" s="398" t="n"/>
+      <c r="K20" s="398" t="n"/>
+      <c r="L20" s="393" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1" s="260">
       <c r="A21" s="303" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="390" t="n"/>
-      <c r="C21" s="391" t="n"/>
-      <c r="D21" s="391" t="n"/>
-      <c r="E21" s="392" t="n"/>
-      <c r="F21" s="393" t="n"/>
-      <c r="G21" s="391" t="n"/>
-      <c r="H21" s="394" t="n"/>
-      <c r="I21" s="391" t="n"/>
-      <c r="J21" s="395" t="n"/>
-      <c r="K21" s="395" t="n"/>
-      <c r="L21" s="390" t="n"/>
+      <c r="B21" s="393" t="n"/>
+      <c r="C21" s="394" t="n"/>
+      <c r="D21" s="394" t="n"/>
+      <c r="E21" s="395" t="n"/>
+      <c r="F21" s="396" t="n"/>
+      <c r="G21" s="394" t="n"/>
+      <c r="H21" s="397" t="n"/>
+      <c r="I21" s="394" t="n"/>
+      <c r="J21" s="398" t="n"/>
+      <c r="K21" s="398" t="n"/>
+      <c r="L21" s="393" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1" s="260">
       <c r="A22" s="303" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="390" t="n"/>
-      <c r="C22" s="391" t="n"/>
-      <c r="D22" s="391" t="n"/>
-      <c r="E22" s="392" t="n"/>
-      <c r="F22" s="393" t="n"/>
-      <c r="G22" s="391" t="n"/>
-      <c r="H22" s="394" t="n"/>
-      <c r="I22" s="391" t="n"/>
-      <c r="J22" s="395" t="n"/>
-      <c r="K22" s="395" t="n"/>
-      <c r="L22" s="390" t="n"/>
+      <c r="B22" s="393" t="n"/>
+      <c r="C22" s="394" t="n"/>
+      <c r="D22" s="394" t="n"/>
+      <c r="E22" s="395" t="n"/>
+      <c r="F22" s="396" t="n"/>
+      <c r="G22" s="394" t="n"/>
+      <c r="H22" s="397" t="n"/>
+      <c r="I22" s="394" t="n"/>
+      <c r="J22" s="398" t="n"/>
+      <c r="K22" s="398" t="n"/>
+      <c r="L22" s="393" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1" s="260">
       <c r="A23" s="303" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="390" t="n"/>
-      <c r="C23" s="391" t="n"/>
-      <c r="D23" s="391" t="n"/>
-      <c r="E23" s="392" t="n"/>
-      <c r="F23" s="393" t="n"/>
-      <c r="G23" s="391" t="n"/>
-      <c r="H23" s="394" t="n"/>
-      <c r="I23" s="391" t="n"/>
-      <c r="J23" s="395" t="n"/>
-      <c r="K23" s="395" t="n"/>
-      <c r="L23" s="390" t="n"/>
+      <c r="B23" s="393" t="n"/>
+      <c r="C23" s="394" t="n"/>
+      <c r="D23" s="394" t="n"/>
+      <c r="E23" s="395" t="n"/>
+      <c r="F23" s="396" t="n"/>
+      <c r="G23" s="394" t="n"/>
+      <c r="H23" s="397" t="n"/>
+      <c r="I23" s="394" t="n"/>
+      <c r="J23" s="398" t="n"/>
+      <c r="K23" s="398" t="n"/>
+      <c r="L23" s="393" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="260">
       <c r="A24" s="303" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="390" t="n"/>
-      <c r="C24" s="391" t="n"/>
-      <c r="D24" s="391" t="n"/>
-      <c r="E24" s="392" t="n"/>
-      <c r="F24" s="393" t="n"/>
-      <c r="G24" s="391" t="n"/>
-      <c r="H24" s="394" t="n"/>
-      <c r="I24" s="391" t="n"/>
-      <c r="J24" s="395" t="n"/>
-      <c r="K24" s="395" t="n"/>
-      <c r="L24" s="390" t="n"/>
+      <c r="B24" s="393" t="n"/>
+      <c r="C24" s="394" t="n"/>
+      <c r="D24" s="394" t="n"/>
+      <c r="E24" s="395" t="n"/>
+      <c r="F24" s="396" t="n"/>
+      <c r="G24" s="394" t="n"/>
+      <c r="H24" s="397" t="n"/>
+      <c r="I24" s="394" t="n"/>
+      <c r="J24" s="398" t="n"/>
+      <c r="K24" s="398" t="n"/>
+      <c r="L24" s="393" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1" s="260">
       <c r="A25" s="303" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="390" t="n"/>
-      <c r="C25" s="391" t="n"/>
-      <c r="D25" s="391" t="n"/>
-      <c r="E25" s="392" t="n"/>
-      <c r="F25" s="393" t="n"/>
-      <c r="G25" s="391" t="n"/>
-      <c r="H25" s="394" t="n"/>
-      <c r="I25" s="391" t="n"/>
-      <c r="J25" s="395" t="n"/>
-      <c r="K25" s="395" t="n"/>
-      <c r="L25" s="390" t="n"/>
+      <c r="B25" s="393" t="n"/>
+      <c r="C25" s="394" t="n"/>
+      <c r="D25" s="394" t="n"/>
+      <c r="E25" s="395" t="n"/>
+      <c r="F25" s="396" t="n"/>
+      <c r="G25" s="394" t="n"/>
+      <c r="H25" s="397" t="n"/>
+      <c r="I25" s="394" t="n"/>
+      <c r="J25" s="398" t="n"/>
+      <c r="K25" s="398" t="n"/>
+      <c r="L25" s="393" t="n"/>
     </row>
     <row r="26" ht="13.5" customHeight="1" s="260"/>
     <row r="27" ht="30" customHeight="1" s="260">
-      <c r="A27" s="326" t="inlineStr">
+      <c r="A27" s="329" t="inlineStr">
         <is>
           <t>🤝 نماذج التفاوض الأربعة · أيها يناسب كل مستأجر</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" s="260">
-      <c r="A28" s="327" t="inlineStr">
+      <c r="A28" s="330" t="inlineStr">
         <is>
           <t>النموذج</t>
         </is>
       </c>
-      <c r="B28" s="327" t="inlineStr">
+      <c r="B28" s="330" t="inlineStr">
         <is>
           <t>مساهمة المستأجر</t>
         </is>
       </c>
-      <c r="C28" s="327" t="inlineStr">
+      <c r="C28" s="330" t="inlineStr">
         <is>
           <t>مساهمة درب</t>
         </is>
       </c>
-      <c r="D28" s="327" t="inlineStr">
+      <c r="D28" s="330" t="inlineStr">
         <is>
           <t>مناسب لمن؟</t>
         </is>
@@ -9073,7 +9537,7 @@
       <c r="E28" s="293" t="n"/>
       <c r="F28" s="293" t="n"/>
       <c r="G28" s="287" t="n"/>
-      <c r="H28" s="327" t="inlineStr">
+      <c r="H28" s="330" t="inlineStr">
         <is>
           <t>حجة التفاوض</t>
         </is>
@@ -9081,7 +9545,7 @@
       <c r="I28" s="293" t="n"/>
       <c r="J28" s="293" t="n"/>
       <c r="K28" s="287" t="n"/>
-      <c r="L28" s="327" t="inlineStr">
+      <c r="L28" s="330" t="inlineStr">
         <is>
           <t>التقييم</t>
         </is>
@@ -9093,17 +9557,17 @@
           <t>🟢 المستأجر 100%</t>
         </is>
       </c>
-      <c r="B29" s="396" t="inlineStr">
+      <c r="B29" s="399" t="inlineStr">
         <is>
           <t>2 هللة/ريال</t>
         </is>
       </c>
-      <c r="C29" s="367" t="inlineStr">
+      <c r="C29" s="370" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D29" s="366" t="inlineStr">
+      <c r="D29" s="369" t="inlineStr">
         <is>
           <t>هامش عالي (&gt;60%) · المستأجر الذي يحتاج عملاء درب أكثر مما تحتاجه درب · مغاسل/كافيهات صغيرة محلية</t>
         </is>
@@ -9111,7 +9575,7 @@
       <c r="E29" s="293" t="n"/>
       <c r="F29" s="293" t="n"/>
       <c r="G29" s="287" t="n"/>
-      <c r="H29" s="397" t="inlineStr">
+      <c r="H29" s="400" t="inlineStr">
         <is>
           <t>العميل يأتيك من تطبيق درب مجاناً · أنت تربح من المبيعات الإضافية · المقابل بسيط: 2 هللة من كل ريال (أقل من 1% من إيرادك)</t>
         </is>
@@ -9131,17 +9595,17 @@
           <t>🔵 مشاركة 70/30 (المستأجر)</t>
         </is>
       </c>
-      <c r="B30" s="396" t="inlineStr">
+      <c r="B30" s="399" t="inlineStr">
         <is>
           <t>1.5 هللة/ريال</t>
         </is>
       </c>
-      <c r="C30" s="367" t="inlineStr">
+      <c r="C30" s="370" t="inlineStr">
         <is>
           <t>0.5 هللة/ريال</t>
         </is>
       </c>
-      <c r="D30" s="366" t="inlineStr">
+      <c r="D30" s="369" t="inlineStr">
         <is>
           <t>هامش متوسط (40-60%) · مستأجر متوسط الحجم · مطاعم متوسطة · سلاسل صغيرة محلية</t>
         </is>
@@ -9149,7 +9613,7 @@
       <c r="E30" s="293" t="n"/>
       <c r="F30" s="293" t="n"/>
       <c r="G30" s="287" t="n"/>
-      <c r="H30" s="397" t="inlineStr">
+      <c r="H30" s="400" t="inlineStr">
         <is>
           <t>أنت تتحمل 70% فقط · درب تشارك معك 30% · في المقابل تحصل على بيانات العملاء + تسويق مجاني داخل التطبيق</t>
         </is>
@@ -9164,22 +9628,22 @@
       </c>
     </row>
     <row r="31" ht="79.5" customHeight="1" s="260">
-      <c r="A31" s="398" t="inlineStr">
+      <c r="A31" s="401" t="inlineStr">
         <is>
           <t>🟡 مشاركة 50/50</t>
         </is>
       </c>
-      <c r="B31" s="396" t="inlineStr">
+      <c r="B31" s="399" t="inlineStr">
         <is>
           <t>1 هللة/ريال</t>
         </is>
       </c>
-      <c r="C31" s="367" t="inlineStr">
+      <c r="C31" s="370" t="inlineStr">
         <is>
           <t>1 هللة/ريال</t>
         </is>
       </c>
-      <c r="D31" s="366" t="inlineStr">
+      <c r="D31" s="369" t="inlineStr">
         <is>
           <t>هامش متوسط · مستأجر كبير له ثقل تفاوضي · سلاسل عالمية · شركاء استراتيجيون</t>
         </is>
@@ -9187,7 +9651,7 @@
       <c r="E31" s="293" t="n"/>
       <c r="F31" s="293" t="n"/>
       <c r="G31" s="287" t="n"/>
-      <c r="H31" s="397" t="inlineStr">
+      <c r="H31" s="400" t="inlineStr">
         <is>
           <t>شراكة عادلة 50/50 · كلانا يستفيد · درب توفر تسويق وقاعدة بيانات · أنت توفر الخدمة والخصومات</t>
         </is>
@@ -9195,29 +9659,29 @@
       <c r="I31" s="293" t="n"/>
       <c r="J31" s="293" t="n"/>
       <c r="K31" s="287" t="n"/>
-      <c r="L31" s="399" t="inlineStr">
+      <c r="L31" s="402" t="inlineStr">
         <is>
           <t>⭐⭐⭐ متوازن</t>
         </is>
       </c>
     </row>
     <row r="32" ht="79.5" customHeight="1" s="260">
-      <c r="A32" s="400" t="inlineStr">
+      <c r="A32" s="403" t="inlineStr">
         <is>
           <t>🟠 مشاركة 30/70 (درب)</t>
         </is>
       </c>
-      <c r="B32" s="396" t="inlineStr">
+      <c r="B32" s="399" t="inlineStr">
         <is>
           <t>0.5 هللة/ريال</t>
         </is>
       </c>
-      <c r="C32" s="367" t="inlineStr">
+      <c r="C32" s="370" t="inlineStr">
         <is>
           <t>1.5 هللة/ريال</t>
         </is>
       </c>
-      <c r="D32" s="366" t="inlineStr">
+      <c r="D32" s="369" t="inlineStr">
         <is>
           <t>هامش منخفض (&lt;25%) · سوبرماركت · مستأجر استراتيجي مهم لكن صعب الإقناع · حالات خاصة</t>
         </is>
@@ -9225,7 +9689,7 @@
       <c r="E32" s="293" t="n"/>
       <c r="F32" s="293" t="n"/>
       <c r="G32" s="287" t="n"/>
-      <c r="H32" s="397" t="inlineStr">
+      <c r="H32" s="400" t="inlineStr">
         <is>
           <t>درب تتحمل 70% · أنت 30% فقط · هذا لأننا نقدّر هامشك الضعيف · لكنك تساعدنا في تكامل المنظومة</t>
         </is>
@@ -9233,7 +9697,7 @@
       <c r="I32" s="293" t="n"/>
       <c r="J32" s="293" t="n"/>
       <c r="K32" s="287" t="n"/>
-      <c r="L32" s="399" t="inlineStr">
+      <c r="L32" s="402" t="inlineStr">
         <is>
           <t>⭐⭐ مكلف لدرب</t>
         </is>
@@ -9241,14 +9705,14 @@
     </row>
     <row r="33" ht="13.5" customHeight="1" s="260"/>
     <row r="34" ht="30" customHeight="1" s="260">
-      <c r="A34" s="333" t="inlineStr">
+      <c r="A34" s="336" t="inlineStr">
         <is>
           <t>💰 حاسبة الأثر المالي لكل مستأجر</t>
         </is>
       </c>
     </row>
     <row r="35" ht="27.75" customHeight="1" s="260">
-      <c r="A35" s="401" t="inlineStr">
+      <c r="A35" s="404" t="inlineStr">
         <is>
           <t>📝 أدخل بيانات المستأجر</t>
         </is>
@@ -9272,13 +9736,13 @@
         </is>
       </c>
       <c r="B36" s="287" t="n"/>
-      <c r="C36" s="402" t="inlineStr">
+      <c r="C36" s="405" t="inlineStr">
         <is>
           <t>سلسلة كافيه افتراضية</t>
         </is>
       </c>
       <c r="D36" s="287" t="n"/>
-      <c r="E36" s="362" t="inlineStr">
+      <c r="E36" s="365" t="inlineStr">
         <is>
           <t>← اسم الشركة المحتمل</t>
         </is>
@@ -9298,11 +9762,11 @@
         </is>
       </c>
       <c r="B37" s="287" t="n"/>
-      <c r="C37" s="403" t="n">
+      <c r="C37" s="406" t="n">
         <v>150000</v>
       </c>
       <c r="D37" s="287" t="n"/>
-      <c r="E37" s="362" t="inlineStr">
+      <c r="E37" s="365" t="inlineStr">
         <is>
           <t>← متوسط مبيعاتها داخل محطات درب</t>
         </is>
@@ -9322,11 +9786,11 @@
         </is>
       </c>
       <c r="B38" s="287" t="n"/>
-      <c r="C38" s="404" t="n">
+      <c r="C38" s="407" t="n">
         <v>0.65</v>
       </c>
       <c r="D38" s="287" t="n"/>
-      <c r="E38" s="362" t="inlineStr">
+      <c r="E38" s="365" t="inlineStr">
         <is>
           <t>← هامش الربح الإجمالي</t>
         </is>
@@ -9346,11 +9810,11 @@
         </is>
       </c>
       <c r="B39" s="287" t="n"/>
-      <c r="C39" s="405" t="n">
+      <c r="C39" s="408" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="287" t="n"/>
-      <c r="E39" s="362" t="inlineStr">
+      <c r="E39" s="365" t="inlineStr">
         <is>
           <t>← كم تدفع لدرب من كل ريال</t>
         </is>
@@ -9365,7 +9829,7 @@
     </row>
     <row r="40" ht="13.5" customHeight="1" s="260"/>
     <row r="41" ht="30" customHeight="1" s="260">
-      <c r="A41" s="406" t="inlineStr">
+      <c r="A41" s="409" t="inlineStr">
         <is>
           <t>📊 النتائج المحسوبة تلقائياً</t>
         </is>
@@ -9383,27 +9847,27 @@
       <c r="L41" s="287" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1" s="260">
-      <c r="A42" s="338" t="inlineStr">
+      <c r="A42" s="341" t="inlineStr">
         <is>
           <t>📅 الإيرادات السنوية</t>
         </is>
       </c>
       <c r="B42" s="293" t="n"/>
       <c r="C42" s="287" t="n"/>
-      <c r="D42" s="407">
+      <c r="D42" s="410">
         <f>C37*12</f>
         <v/>
       </c>
       <c r="E42" s="293" t="n"/>
       <c r="F42" s="287" t="n"/>
-      <c r="G42" s="338" t="inlineStr">
+      <c r="G42" s="341" t="inlineStr">
         <is>
           <t>💰 الربح السنوي للمستأجر</t>
         </is>
       </c>
       <c r="H42" s="293" t="n"/>
       <c r="I42" s="287" t="n"/>
-      <c r="J42" s="408">
+      <c r="J42" s="411">
         <f>D42*C38</f>
         <v/>
       </c>
@@ -9411,27 +9875,27 @@
       <c r="L42" s="287" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1" s="260">
-      <c r="A43" s="338" t="inlineStr">
+      <c r="A43" s="341" t="inlineStr">
         <is>
           <t>💸 تكلفة النقاط على المستأجر/سنة</t>
         </is>
       </c>
       <c r="B43" s="293" t="n"/>
       <c r="C43" s="287" t="n"/>
-      <c r="D43" s="409">
+      <c r="D43" s="412">
         <f>D42*C39/100</f>
         <v/>
       </c>
       <c r="E43" s="293" t="n"/>
       <c r="F43" s="287" t="n"/>
-      <c r="G43" s="338" t="inlineStr">
+      <c r="G43" s="341" t="inlineStr">
         <is>
           <t>📊 % من ربح المستأجر</t>
         </is>
       </c>
       <c r="H43" s="293" t="n"/>
       <c r="I43" s="287" t="n"/>
-      <c r="J43" s="410">
+      <c r="J43" s="413">
         <f>D43/J42</f>
         <v/>
       </c>
@@ -9439,27 +9903,27 @@
       <c r="L43" s="287" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1" s="260">
-      <c r="A44" s="338" t="inlineStr">
+      <c r="A44" s="341" t="inlineStr">
         <is>
           <t>📈 الزيادة المتوقعة (15%)</t>
         </is>
       </c>
       <c r="B44" s="293" t="n"/>
       <c r="C44" s="287" t="n"/>
-      <c r="D44" s="411">
+      <c r="D44" s="414">
         <f>D42*0.15</f>
         <v/>
       </c>
       <c r="E44" s="293" t="n"/>
       <c r="F44" s="287" t="n"/>
-      <c r="G44" s="338" t="inlineStr">
+      <c r="G44" s="341" t="inlineStr">
         <is>
           <t>💎 الربح الإضافي المتوقع</t>
         </is>
       </c>
       <c r="H44" s="293" t="n"/>
       <c r="I44" s="287" t="n"/>
-      <c r="J44" s="411">
+      <c r="J44" s="414">
         <f>D44*C38</f>
         <v/>
       </c>
@@ -9467,27 +9931,27 @@
       <c r="L44" s="287" t="n"/>
     </row>
     <row r="45" ht="43.5" customHeight="1" s="260">
-      <c r="A45" s="412" t="inlineStr">
+      <c r="A45" s="415" t="inlineStr">
         <is>
           <t>✅ صافي العائد للمستأجر</t>
         </is>
       </c>
       <c r="B45" s="293" t="n"/>
       <c r="C45" s="287" t="n"/>
-      <c r="D45" s="413">
+      <c r="D45" s="416">
         <f>J44-D43</f>
         <v/>
       </c>
       <c r="E45" s="293" t="n"/>
       <c r="F45" s="287" t="n"/>
-      <c r="G45" s="412" t="inlineStr">
+      <c r="G45" s="415" t="inlineStr">
         <is>
           <t>🎯 ROI للمستأجر</t>
         </is>
       </c>
       <c r="H45" s="293" t="n"/>
       <c r="I45" s="287" t="n"/>
-      <c r="J45" s="414">
+      <c r="J45" s="417">
         <f>D45/D43</f>
         <v/>
       </c>
@@ -9496,7 +9960,7 @@
     </row>
     <row r="46" ht="13.5" customHeight="1" s="260"/>
     <row r="47" ht="31.5" customHeight="1" s="260">
-      <c r="A47" s="355" t="inlineStr">
+      <c r="A47" s="358" t="inlineStr">
         <is>
           <t>💡 جرّب · غيّر القيم في الخلايا الصفراء وشوف كيف تتغير النتائج لحظياً · ROI &gt; 100% يعني المستأجر سيوافق بالتأكيد</t>
         </is>
@@ -9560,27 +10024,27 @@
       <c r="L50" s="287" t="n"/>
     </row>
     <row r="51" ht="109.5" customHeight="1" s="260">
-      <c r="A51" s="415" t="inlineStr">
+      <c r="A51" s="418" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B51" s="401" t="inlineStr">
+      <c r="B51" s="404" t="inlineStr">
         <is>
           <t>الافتتاح</t>
         </is>
       </c>
-      <c r="C51" s="353" t="inlineStr">
+      <c r="C51" s="356" t="inlineStr">
         <is>
           <t>5 دقائق</t>
         </is>
       </c>
-      <c r="D51" s="416" t="inlineStr">
+      <c r="D51" s="419" t="inlineStr">
         <is>
           <t>بناء الثقة وتحديد السياق</t>
         </is>
       </c>
-      <c r="E51" s="366" t="inlineStr">
+      <c r="E51" s="369" t="inlineStr">
         <is>
           <t>«شكراً لاستضافتنا. درب اليوم 173 محطة وننمو بسرعة. أطلقنا برنامج تانكي للمكافآت وفي يومه الأول وصلنا 50K مستخدم نشط. اليوم نريد نتحدث كيف نوسّع التجربة لتشمل [اسم المستأجر].»</t>
         </is>
@@ -9589,7 +10053,7 @@
       <c r="G51" s="293" t="n"/>
       <c r="H51" s="293" t="n"/>
       <c r="I51" s="287" t="n"/>
-      <c r="J51" s="417" t="inlineStr">
+      <c r="J51" s="420" t="inlineStr">
         <is>
           <t>لا تتكلم عن المال في البداية · ابدأ بأرقام درب القوية</t>
         </is>
@@ -9598,27 +10062,27 @@
       <c r="L51" s="287" t="n"/>
     </row>
     <row r="52" ht="109.5" customHeight="1" s="260">
-      <c r="A52" s="415" t="inlineStr">
+      <c r="A52" s="418" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B52" s="401" t="inlineStr">
+      <c r="B52" s="404" t="inlineStr">
         <is>
           <t>عرض القيمة</t>
         </is>
       </c>
-      <c r="C52" s="353" t="inlineStr">
+      <c r="C52" s="356" t="inlineStr">
         <is>
           <t>10 دقائق</t>
         </is>
       </c>
-      <c r="D52" s="416" t="inlineStr">
+      <c r="D52" s="419" t="inlineStr">
         <is>
           <t>إظهار الفائدة قبل التكلفة</t>
         </is>
       </c>
-      <c r="E52" s="366" t="inlineStr">
+      <c r="E52" s="369" t="inlineStr">
         <is>
           <t>«قاعدة عملاء درب الـ 50K هي عملاؤك المحتملون. عندنا بيانات تظهر أن العميل الذي يدخل المحطة للوقود يصرف +30% إذا وجد خدمات إضافية. لو دخل تطبيقنا ورأى عرضكم، سيدخل عندكم.»</t>
         </is>
@@ -9627,7 +10091,7 @@
       <c r="G52" s="293" t="n"/>
       <c r="H52" s="293" t="n"/>
       <c r="I52" s="287" t="n"/>
-      <c r="J52" s="417" t="inlineStr">
+      <c r="J52" s="420" t="inlineStr">
         <is>
           <t>استخدم أرقاماً واقعية · اعرض شاشة التطبيق إن أمكن</t>
         </is>
@@ -9636,27 +10100,27 @@
       <c r="L52" s="287" t="n"/>
     </row>
     <row r="53" ht="109.5" customHeight="1" s="260">
-      <c r="A53" s="415" t="inlineStr">
+      <c r="A53" s="418" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B53" s="401" t="inlineStr">
+      <c r="B53" s="404" t="inlineStr">
         <is>
           <t>عرض النموذج</t>
         </is>
       </c>
-      <c r="C53" s="353" t="inlineStr">
+      <c r="C53" s="356" t="inlineStr">
         <is>
           <t>10 دقائق</t>
         </is>
       </c>
-      <c r="D53" s="416" t="inlineStr">
+      <c r="D53" s="419" t="inlineStr">
         <is>
           <t>تقديم الخيار الأنسب</t>
         </is>
       </c>
-      <c r="E53" s="366" t="inlineStr">
+      <c r="E53" s="369" t="inlineStr">
         <is>
           <t>«اقتراحنا بسيط: عملاء درب يحصلون على نقاط عند الشراء منكم. مقابل ذلك، أنتم تساهمون بـ [حسب النموذج: 2 هللة / 1.5 / 1 / 0.5] من كل ريال مبيعات. هذا [أقل من 1% من إيراداتكم].»</t>
         </is>
@@ -9665,7 +10129,7 @@
       <c r="G53" s="293" t="n"/>
       <c r="H53" s="293" t="n"/>
       <c r="I53" s="287" t="n"/>
-      <c r="J53" s="417" t="inlineStr">
+      <c r="J53" s="420" t="inlineStr">
         <is>
           <t>اختر النموذج حسب حجمهم وهامش ربحهم</t>
         </is>
@@ -9674,27 +10138,27 @@
       <c r="L53" s="287" t="n"/>
     </row>
     <row r="54" ht="109.5" customHeight="1" s="260">
-      <c r="A54" s="415" t="inlineStr">
+      <c r="A54" s="418" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B54" s="401" t="inlineStr">
+      <c r="B54" s="404" t="inlineStr">
         <is>
           <t>الرد على الاعتراضات</t>
         </is>
       </c>
-      <c r="C54" s="353" t="inlineStr">
+      <c r="C54" s="356" t="inlineStr">
         <is>
           <t>15 دقيقة</t>
         </is>
       </c>
-      <c r="D54" s="416" t="inlineStr">
+      <c r="D54" s="419" t="inlineStr">
         <is>
           <t>إزالة المخاوف</t>
         </is>
       </c>
-      <c r="E54" s="366" t="inlineStr">
+      <c r="E54" s="369" t="inlineStr">
         <is>
           <t>⚠️ إعتراض شائع: «هذا ضغط على هامشي»
 → ردك: «لكنك تكسب +15% مبيعات على الأقل = +X ريال صافي بعد التكاليف»
@@ -9706,7 +10170,7 @@
       <c r="G54" s="293" t="n"/>
       <c r="H54" s="293" t="n"/>
       <c r="I54" s="287" t="n"/>
-      <c r="J54" s="417" t="inlineStr">
+      <c r="J54" s="420" t="inlineStr">
         <is>
           <t>تحضّر للاعتراضات مسبقاً · لا تتفاجأ</t>
         </is>
@@ -9715,27 +10179,27 @@
       <c r="L54" s="287" t="n"/>
     </row>
     <row r="55" ht="109.5" customHeight="1" s="260">
-      <c r="A55" s="415" t="inlineStr">
+      <c r="A55" s="418" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B55" s="401" t="inlineStr">
+      <c r="B55" s="404" t="inlineStr">
         <is>
           <t>التفاوض على التفاصيل</t>
         </is>
       </c>
-      <c r="C55" s="353" t="inlineStr">
+      <c r="C55" s="356" t="inlineStr">
         <is>
           <t>15 دقيقة</t>
         </is>
       </c>
-      <c r="D55" s="416" t="inlineStr">
+      <c r="D55" s="419" t="inlineStr">
         <is>
           <t>الوصول لاتفاق</t>
         </is>
       </c>
-      <c r="E55" s="366" t="inlineStr">
+      <c r="E55" s="369" t="inlineStr">
         <is>
           <t>«لنبدأ بـ Pilot 3 شهور في محطة واحدة. لو حقق نتائج، نوسّع للجميع. خلال هذي الفترة، لا توجد التزامات طويلة المدى. ما رأيكم؟»</t>
         </is>
@@ -9744,7 +10208,7 @@
       <c r="G55" s="293" t="n"/>
       <c r="H55" s="293" t="n"/>
       <c r="I55" s="287" t="n"/>
-      <c r="J55" s="417" t="inlineStr">
+      <c r="J55" s="420" t="inlineStr">
         <is>
           <t>Pilot يخفض المقاومة بنسبة 70% · ابدأ صغير</t>
         </is>
@@ -9753,27 +10217,27 @@
       <c r="L55" s="287" t="n"/>
     </row>
     <row r="56" ht="109.5" customHeight="1" s="260">
-      <c r="A56" s="415" t="inlineStr">
+      <c r="A56" s="418" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B56" s="401" t="inlineStr">
+      <c r="B56" s="404" t="inlineStr">
         <is>
           <t>الإغلاق</t>
         </is>
       </c>
-      <c r="C56" s="353" t="inlineStr">
+      <c r="C56" s="356" t="inlineStr">
         <is>
           <t>5 دقائق</t>
         </is>
       </c>
-      <c r="D56" s="416" t="inlineStr">
+      <c r="D56" s="419" t="inlineStr">
         <is>
           <t>تحديد الخطوة التالية</t>
         </is>
       </c>
-      <c r="E56" s="366" t="inlineStr">
+      <c r="E56" s="369" t="inlineStr">
         <is>
           <t>«ممتاز. سأرسل لكم اتفاقية الـ Pilot خلال 3 أيام. أقترح اجتماع متابعة الأسبوع القادم لمراجعة الوثائق. هل يوم [التاريخ] مناسب؟»</t>
         </is>
@@ -9782,7 +10246,7 @@
       <c r="G56" s="293" t="n"/>
       <c r="H56" s="293" t="n"/>
       <c r="I56" s="287" t="n"/>
-      <c r="J56" s="417" t="inlineStr">
+      <c r="J56" s="420" t="inlineStr">
         <is>
           <t>لا تخرج من الاجتماع بدون موعد محدد للخطوة التالية</t>
         </is>
@@ -9792,14 +10256,14 @@
     </row>
     <row r="57" ht="13.5" customHeight="1" s="260"/>
     <row r="58" ht="30" customHeight="1" s="260">
-      <c r="A58" s="418" t="inlineStr">
+      <c r="A58" s="421" t="inlineStr">
         <is>
           <t>⚠️ الاعتراضات الشائعة وكيف تردّ عليها</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1" s="260">
-      <c r="A59" s="327" t="inlineStr">
+      <c r="A59" s="330" t="inlineStr">
         <is>
           <t>الاعتراض</t>
         </is>
@@ -9807,7 +10271,7 @@
       <c r="B59" s="293" t="n"/>
       <c r="C59" s="293" t="n"/>
       <c r="D59" s="287" t="n"/>
-      <c r="E59" s="327" t="inlineStr">
+      <c r="E59" s="330" t="inlineStr">
         <is>
           <t>ردك الذكي</t>
         </is>
@@ -9816,7 +10280,7 @@
       <c r="G59" s="293" t="n"/>
       <c r="H59" s="293" t="n"/>
       <c r="I59" s="287" t="n"/>
-      <c r="J59" s="327" t="inlineStr">
+      <c r="J59" s="330" t="inlineStr">
         <is>
           <t>دعم بالأرقام</t>
         </is>
@@ -9825,7 +10289,7 @@
       <c r="L59" s="287" t="n"/>
     </row>
     <row r="60" ht="79.5" customHeight="1" s="260">
-      <c r="A60" s="419" t="inlineStr">
+      <c r="A60" s="422" t="inlineStr">
         <is>
           <t>🔴 «التكلفة عالية ولا نقدر»</t>
         </is>
@@ -9833,7 +10297,7 @@
       <c r="B60" s="293" t="n"/>
       <c r="C60" s="293" t="n"/>
       <c r="D60" s="287" t="n"/>
-      <c r="E60" s="376" t="inlineStr">
+      <c r="E60" s="379" t="inlineStr">
         <is>
           <t>«التكلفة الفعلية أقل مما تتوقع. أنت تدفع فقط من المبيعات التي تأتيك من تطبيق درب. لو لم يأتك عميل، لا تدفع شيئاً.»</t>
         </is>
@@ -9842,7 +10306,7 @@
       <c r="G60" s="293" t="n"/>
       <c r="H60" s="293" t="n"/>
       <c r="I60" s="287" t="n"/>
-      <c r="J60" s="420" t="inlineStr">
+      <c r="J60" s="423" t="inlineStr">
         <is>
           <t>تكلفة = 1% من المبيعات
 العائد = +15% مبيعات
@@ -9853,7 +10317,7 @@
       <c r="L60" s="287" t="n"/>
     </row>
     <row r="61" ht="79.5" customHeight="1" s="260">
-      <c r="A61" s="419" t="inlineStr">
+      <c r="A61" s="422" t="inlineStr">
         <is>
           <t>🔴 «التكامل التقني معقد»</t>
         </is>
@@ -9861,7 +10325,7 @@
       <c r="B61" s="293" t="n"/>
       <c r="C61" s="293" t="n"/>
       <c r="D61" s="287" t="n"/>
-      <c r="E61" s="376" t="inlineStr">
+      <c r="E61" s="379" t="inlineStr">
         <is>
           <t>«نوفر API بسيط جداً. فريقنا التقني يدعمك في الإعداد مجاناً. التكامل يأخذ أسبوع واحد فقط. عندنا 15 شريك مدمج بنجاح.»</t>
         </is>
@@ -9870,7 +10334,7 @@
       <c r="G61" s="293" t="n"/>
       <c r="H61" s="293" t="n"/>
       <c r="I61" s="287" t="n"/>
-      <c r="J61" s="420" t="inlineStr">
+      <c r="J61" s="423" t="inlineStr">
         <is>
           <t>مدة التكامل: 5-7 أيام
 الدعم: مجاني
@@ -9881,7 +10345,7 @@
       <c r="L61" s="287" t="n"/>
     </row>
     <row r="62" ht="79.5" customHeight="1" s="260">
-      <c r="A62" s="419" t="inlineStr">
+      <c r="A62" s="422" t="inlineStr">
         <is>
           <t>🔴 «عندنا برامج ولاء خاصة بنا»</t>
         </is>
@@ -9889,7 +10353,7 @@
       <c r="B62" s="293" t="n"/>
       <c r="C62" s="293" t="n"/>
       <c r="D62" s="287" t="n"/>
-      <c r="E62" s="376" t="inlineStr">
+      <c r="E62" s="379" t="inlineStr">
         <is>
           <t>«ممتاز! تانكي لا يحل محلها. هو يضيف طبقة إضافية. العميل يكسب نقاطك ونقاط تانكي معاً = ضعف الجاذبية.»</t>
         </is>
@@ -9898,7 +10362,7 @@
       <c r="G62" s="293" t="n"/>
       <c r="H62" s="293" t="n"/>
       <c r="I62" s="287" t="n"/>
-      <c r="J62" s="420" t="inlineStr">
+      <c r="J62" s="423" t="inlineStr">
         <is>
           <t>برامج موازية = نمو 30%
 بدلاً من 15% منفصلة</t>
@@ -9908,7 +10372,7 @@
       <c r="L62" s="287" t="n"/>
     </row>
     <row r="63" ht="79.5" customHeight="1" s="260">
-      <c r="A63" s="419" t="inlineStr">
+      <c r="A63" s="422" t="inlineStr">
         <is>
           <t>🔴 «نريد ضمانات على زيادة المبيعات»</t>
         </is>
@@ -9916,7 +10380,7 @@
       <c r="B63" s="293" t="n"/>
       <c r="C63" s="293" t="n"/>
       <c r="D63" s="287" t="n"/>
-      <c r="E63" s="376" t="inlineStr">
+      <c r="E63" s="379" t="inlineStr">
         <is>
           <t>«نقدّم لك Pilot لمدة 3 شهور بدون التزامات. لو لم تحقق زيادة 10% على الأقل، تنسحب بدون أي رسوم.»</t>
         </is>
@@ -9925,7 +10389,7 @@
       <c r="G63" s="293" t="n"/>
       <c r="H63" s="293" t="n"/>
       <c r="I63" s="287" t="n"/>
-      <c r="J63" s="420" t="inlineStr">
+      <c r="J63" s="423" t="inlineStr">
         <is>
           <t>Pilot = 3 شهور
 Low risk
@@ -9936,7 +10400,7 @@
       <c r="L63" s="287" t="n"/>
     </row>
     <row r="64" ht="79.5" customHeight="1" s="260">
-      <c r="A64" s="419" t="inlineStr">
+      <c r="A64" s="422" t="inlineStr">
         <is>
           <t>🔴 «نريد نسبة أقل (نصف ما تطلبه)»</t>
         </is>
@@ -9944,7 +10408,7 @@
       <c r="B64" s="293" t="n"/>
       <c r="C64" s="293" t="n"/>
       <c r="D64" s="287" t="n"/>
-      <c r="E64" s="376" t="inlineStr">
+      <c r="E64" s="379" t="inlineStr">
         <is>
           <t>«النسبة الحالية مدروسة بناءً على هامش ربحك. لكن ما رأيك بهيكلة مختلفة: نسبة منخفضة + رسم اشتراك سنوي ثابت؟»</t>
         </is>
@@ -9953,7 +10417,7 @@
       <c r="G64" s="293" t="n"/>
       <c r="H64" s="293" t="n"/>
       <c r="I64" s="287" t="n"/>
-      <c r="J64" s="420" t="inlineStr">
+      <c r="J64" s="423" t="inlineStr">
         <is>
           <t>مرونة في النموذج
 بدائل متعددة
@@ -9964,7 +10428,7 @@
       <c r="L64" s="287" t="n"/>
     </row>
     <row r="65" ht="79.5" customHeight="1" s="260">
-      <c r="A65" s="419" t="inlineStr">
+      <c r="A65" s="422" t="inlineStr">
         <is>
           <t>🔴 «لا نثق في حماية بياناتنا»</t>
         </is>
@@ -9972,7 +10436,7 @@
       <c r="B65" s="293" t="n"/>
       <c r="C65" s="293" t="n"/>
       <c r="D65" s="287" t="n"/>
-      <c r="E65" s="376" t="inlineStr">
+      <c r="E65" s="379" t="inlineStr">
         <is>
           <t>«درب ملتزمة بنظام حماية البيانات السعودي (PDPL). لن نشارك أي بيانات حساسة لك مع أحد. تستطيع مراجعة العقد قبل التوقيع.»</t>
         </is>
@@ -9981,7 +10445,7 @@
       <c r="G65" s="293" t="n"/>
       <c r="H65" s="293" t="n"/>
       <c r="I65" s="287" t="n"/>
-      <c r="J65" s="420" t="inlineStr">
+      <c r="J65" s="423" t="inlineStr">
         <is>
           <t>PDPL Compliant
 عقد قانوني
@@ -10158,7 +10622,7 @@
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1" s="260">
-      <c r="A2" s="319" t="inlineStr">
+      <c r="A2" s="322" t="inlineStr">
         <is>
           <t xml:space="preserve">  هل يستحق برنامج تانكي الاستثمار؟ حساب شامل للعائد على درب</t>
         </is>
@@ -10166,7 +10630,7 @@
     </row>
     <row r="3" ht="12" customHeight="1" s="260"/>
     <row r="4" ht="30" customHeight="1" s="260">
-      <c r="A4" s="418" t="inlineStr">
+      <c r="A4" s="421" t="inlineStr">
         <is>
           <t>💸 الاستثمار · التكاليف السنوية على درب</t>
         </is>
@@ -10225,31 +10689,31 @@
           <t>💻 تطوير التطبيق</t>
         </is>
       </c>
-      <c r="B6" s="421" t="inlineStr">
+      <c r="B6" s="424" t="inlineStr">
         <is>
           <t>استثمار أولي</t>
         </is>
       </c>
-      <c r="C6" s="422" t="n">
+      <c r="C6" s="425" t="n">
         <v>800000</v>
       </c>
-      <c r="D6" s="422" t="n">
+      <c r="D6" s="425" t="n">
         <v>200000</v>
       </c>
-      <c r="E6" s="422" t="n">
+      <c r="E6" s="425" t="n">
         <v>150000</v>
       </c>
-      <c r="F6" s="422" t="n">
+      <c r="F6" s="425" t="n">
         <v>150000</v>
       </c>
-      <c r="G6" s="422" t="n">
+      <c r="G6" s="425" t="n">
         <v>150000</v>
       </c>
-      <c r="H6" s="423">
+      <c r="H6" s="426">
         <f>SUM(C6:G6)</f>
         <v/>
       </c>
-      <c r="I6" s="424">
+      <c r="I6" s="427">
         <f>H6/H13</f>
         <v/>
       </c>
@@ -10260,31 +10724,31 @@
           <t>🤝 شراكة Dsquares</t>
         </is>
       </c>
-      <c r="B7" s="421" t="inlineStr">
+      <c r="B7" s="424" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C7" s="422" t="n">
+      <c r="C7" s="425" t="n">
         <v>1370000</v>
       </c>
-      <c r="D7" s="422" t="n">
+      <c r="D7" s="425" t="n">
         <v>850000</v>
       </c>
-      <c r="E7" s="422" t="n">
+      <c r="E7" s="425" t="n">
         <v>870000</v>
       </c>
-      <c r="F7" s="422" t="n">
+      <c r="F7" s="425" t="n">
         <v>890000</v>
       </c>
-      <c r="G7" s="422" t="n">
+      <c r="G7" s="425" t="n">
         <v>920000</v>
       </c>
-      <c r="H7" s="423">
+      <c r="H7" s="426">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
-      <c r="I7" s="424">
+      <c r="I7" s="427">
         <f>H7/H13</f>
         <v/>
       </c>
@@ -10295,31 +10759,31 @@
           <t>📣 التسويق والإعلانات</t>
         </is>
       </c>
-      <c r="B8" s="425" t="inlineStr">
+      <c r="B8" s="428" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C8" s="422" t="n">
+      <c r="C8" s="425" t="n">
         <v>1500000</v>
       </c>
-      <c r="D8" s="422" t="n">
+      <c r="D8" s="425" t="n">
         <v>1200000</v>
       </c>
-      <c r="E8" s="422" t="n">
+      <c r="E8" s="425" t="n">
         <v>1000000</v>
       </c>
-      <c r="F8" s="422" t="n">
+      <c r="F8" s="425" t="n">
         <v>1000000</v>
       </c>
-      <c r="G8" s="422" t="n">
+      <c r="G8" s="425" t="n">
         <v>1000000</v>
       </c>
-      <c r="H8" s="423">
+      <c r="H8" s="426">
         <f>SUM(C8:G8)</f>
         <v/>
       </c>
-      <c r="I8" s="424">
+      <c r="I8" s="427">
         <f>H8/H13</f>
         <v/>
       </c>
@@ -10330,31 +10794,31 @@
           <t>👥 فريق الولاء</t>
         </is>
       </c>
-      <c r="B9" s="425" t="inlineStr">
+      <c r="B9" s="428" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C9" s="422" t="n">
+      <c r="C9" s="425" t="n">
         <v>2780000</v>
       </c>
-      <c r="D9" s="422" t="n">
+      <c r="D9" s="425" t="n">
         <v>3500000</v>
       </c>
-      <c r="E9" s="422" t="n">
+      <c r="E9" s="425" t="n">
         <v>4000000</v>
       </c>
-      <c r="F9" s="422" t="n">
+      <c r="F9" s="425" t="n">
         <v>4500000</v>
       </c>
-      <c r="G9" s="422" t="n">
+      <c r="G9" s="425" t="n">
         <v>5000000</v>
       </c>
-      <c r="H9" s="423">
+      <c r="H9" s="426">
         <f>SUM(C9:G9)</f>
         <v/>
       </c>
-      <c r="I9" s="424">
+      <c r="I9" s="427">
         <f>H9/H13</f>
         <v/>
       </c>
@@ -10365,31 +10829,31 @@
           <t>🎁 كلفة النقاط للعملاء</t>
         </is>
       </c>
-      <c r="B10" s="425" t="inlineStr">
+      <c r="B10" s="428" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C10" s="422" t="n">
+      <c r="C10" s="425" t="n">
         <v>2270000</v>
       </c>
-      <c r="D10" s="422" t="n">
+      <c r="D10" s="425" t="n">
         <v>2680000</v>
       </c>
-      <c r="E10" s="422" t="n">
+      <c r="E10" s="425" t="n">
         <v>3100000</v>
       </c>
-      <c r="F10" s="422" t="n">
+      <c r="F10" s="425" t="n">
         <v>3520000</v>
       </c>
-      <c r="G10" s="422" t="n">
+      <c r="G10" s="425" t="n">
         <v>3930000</v>
       </c>
-      <c r="H10" s="423">
+      <c r="H10" s="426">
         <f>SUM(C10:G10)</f>
         <v/>
       </c>
-      <c r="I10" s="424">
+      <c r="I10" s="427">
         <f>H10/H13</f>
         <v/>
       </c>
@@ -10400,31 +10864,31 @@
           <t>🛠️ التكامل مع المستأجرين</t>
         </is>
       </c>
-      <c r="B11" s="425" t="inlineStr">
+      <c r="B11" s="428" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C11" s="422" t="n">
+      <c r="C11" s="425" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="422" t="n">
+      <c r="D11" s="425" t="n">
         <v>500000</v>
       </c>
-      <c r="E11" s="422" t="n">
+      <c r="E11" s="425" t="n">
         <v>750000</v>
       </c>
-      <c r="F11" s="422" t="n">
+      <c r="F11" s="425" t="n">
         <v>1000000</v>
       </c>
-      <c r="G11" s="422" t="n">
+      <c r="G11" s="425" t="n">
         <v>1200000</v>
       </c>
-      <c r="H11" s="423">
+      <c r="H11" s="426">
         <f>SUM(C11:G11)</f>
         <v/>
       </c>
-      <c r="I11" s="424">
+      <c r="I11" s="427">
         <f>H11/H13</f>
         <v/>
       </c>
@@ -10435,67 +10899,67 @@
           <t>🔧 الصيانة والدعم</t>
         </is>
       </c>
-      <c r="B12" s="425" t="inlineStr">
+      <c r="B12" s="428" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C12" s="422" t="n">
+      <c r="C12" s="425" t="n">
         <v>200000</v>
       </c>
-      <c r="D12" s="422" t="n">
+      <c r="D12" s="425" t="n">
         <v>400000</v>
       </c>
-      <c r="E12" s="422" t="n">
+      <c r="E12" s="425" t="n">
         <v>600000</v>
       </c>
-      <c r="F12" s="422" t="n">
+      <c r="F12" s="425" t="n">
         <v>800000</v>
       </c>
-      <c r="G12" s="422" t="n">
+      <c r="G12" s="425" t="n">
         <v>1000000</v>
       </c>
-      <c r="H12" s="423">
+      <c r="H12" s="426">
         <f>SUM(C12:G12)</f>
         <v/>
       </c>
-      <c r="I12" s="424">
+      <c r="I12" s="427">
         <f>H12/H13</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="37.5" customHeight="1" s="260">
-      <c r="A13" s="426" t="inlineStr">
+      <c r="A13" s="429" t="inlineStr">
         <is>
           <t>📊 إجمالي التكاليف</t>
         </is>
       </c>
-      <c r="B13" s="427" t="n"/>
-      <c r="C13" s="428">
+      <c r="B13" s="430" t="n"/>
+      <c r="C13" s="431">
         <f>SUM(C6:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="428">
+      <c r="D13" s="431">
         <f>SUM(D6:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="428">
+      <c r="E13" s="431">
         <f>SUM(E6:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="428">
+      <c r="F13" s="431">
         <f>SUM(F6:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="428">
+      <c r="G13" s="431">
         <f>SUM(G6:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="429">
+      <c r="H13" s="432">
         <f>SUM(C13:G13)</f>
         <v/>
       </c>
-      <c r="I13" s="427" t="inlineStr">
+      <c r="I13" s="430" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10503,7 +10967,7 @@
     </row>
     <row r="14" ht="13.5" customHeight="1" s="260"/>
     <row r="15" ht="30" customHeight="1" s="260">
-      <c r="A15" s="430" t="inlineStr">
+      <c r="A15" s="433" t="inlineStr">
         <is>
           <t>💰 العائد · الإيرادات الإضافية المتوقعة</t>
         </is>
@@ -10562,31 +11026,31 @@
           <t>⛽ زيادة مبيعات الوقود (+8%)</t>
         </is>
       </c>
-      <c r="B17" s="431" t="inlineStr">
+      <c r="B17" s="434" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C17" s="422" t="n">
+      <c r="C17" s="425" t="n">
         <v>8000000</v>
       </c>
-      <c r="D17" s="422" t="n">
+      <c r="D17" s="425" t="n">
         <v>12000000</v>
       </c>
-      <c r="E17" s="422" t="n">
+      <c r="E17" s="425" t="n">
         <v>16000000</v>
       </c>
-      <c r="F17" s="422" t="n">
+      <c r="F17" s="425" t="n">
         <v>20000000</v>
       </c>
-      <c r="G17" s="422" t="n">
+      <c r="G17" s="425" t="n">
         <v>24000000</v>
       </c>
-      <c r="H17" s="432">
+      <c r="H17" s="435">
         <f>SUM(C17:G17)</f>
         <v/>
       </c>
-      <c r="I17" s="424">
+      <c r="I17" s="427">
         <f>H17/H23</f>
         <v/>
       </c>
@@ -10597,31 +11061,31 @@
           <t>🤝 عمولة من المستأجرين</t>
         </is>
       </c>
-      <c r="B18" s="431" t="inlineStr">
+      <c r="B18" s="434" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C18" s="422" t="n">
+      <c r="C18" s="425" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="422" t="n">
+      <c r="D18" s="425" t="n">
         <v>1200000</v>
       </c>
-      <c r="E18" s="422" t="n">
+      <c r="E18" s="425" t="n">
         <v>2500000</v>
       </c>
-      <c r="F18" s="422" t="n">
+      <c r="F18" s="425" t="n">
         <v>4000000</v>
       </c>
-      <c r="G18" s="422" t="n">
+      <c r="G18" s="425" t="n">
         <v>6000000</v>
       </c>
-      <c r="H18" s="432">
+      <c r="H18" s="435">
         <f>SUM(C18:G18)</f>
         <v/>
       </c>
-      <c r="I18" s="424">
+      <c r="I18" s="427">
         <f>H18/H23</f>
         <v/>
       </c>
@@ -10632,31 +11096,31 @@
           <t>🎯 جذب عملاء جدد</t>
         </is>
       </c>
-      <c r="B19" s="431" t="inlineStr">
+      <c r="B19" s="434" t="inlineStr">
         <is>
           <t>تشغيلي</t>
         </is>
       </c>
-      <c r="C19" s="422" t="n">
+      <c r="C19" s="425" t="n">
         <v>1500000</v>
       </c>
-      <c r="D19" s="422" t="n">
+      <c r="D19" s="425" t="n">
         <v>3000000</v>
       </c>
-      <c r="E19" s="422" t="n">
+      <c r="E19" s="425" t="n">
         <v>4500000</v>
       </c>
-      <c r="F19" s="422" t="n">
+      <c r="F19" s="425" t="n">
         <v>6000000</v>
       </c>
-      <c r="G19" s="422" t="n">
+      <c r="G19" s="425" t="n">
         <v>7500000</v>
       </c>
-      <c r="H19" s="432">
+      <c r="H19" s="435">
         <f>SUM(C19:G19)</f>
         <v/>
       </c>
-      <c r="I19" s="424">
+      <c r="I19" s="427">
         <f>H19/H23</f>
         <v/>
       </c>
@@ -10667,31 +11131,31 @@
           <t>📊 توفير في التسويق التقليدي</t>
         </is>
       </c>
-      <c r="B20" s="431" t="inlineStr">
+      <c r="B20" s="434" t="inlineStr">
         <is>
           <t>توفير</t>
         </is>
       </c>
-      <c r="C20" s="422" t="n">
+      <c r="C20" s="425" t="n">
         <v>800000</v>
       </c>
-      <c r="D20" s="422" t="n">
+      <c r="D20" s="425" t="n">
         <v>1500000</v>
       </c>
-      <c r="E20" s="422" t="n">
+      <c r="E20" s="425" t="n">
         <v>2000000</v>
       </c>
-      <c r="F20" s="422" t="n">
+      <c r="F20" s="425" t="n">
         <v>2500000</v>
       </c>
-      <c r="G20" s="422" t="n">
+      <c r="G20" s="425" t="n">
         <v>3000000</v>
       </c>
-      <c r="H20" s="432">
+      <c r="H20" s="435">
         <f>SUM(C20:G20)</f>
         <v/>
       </c>
-      <c r="I20" s="424">
+      <c r="I20" s="427">
         <f>H20/H23</f>
         <v/>
       </c>
@@ -10702,31 +11166,31 @@
           <t>🚀 نمو المحطات (انتشار العلامة)</t>
         </is>
       </c>
-      <c r="B21" s="431" t="inlineStr">
+      <c r="B21" s="434" t="inlineStr">
         <is>
           <t>استراتيجي</t>
         </is>
       </c>
-      <c r="C21" s="422" t="n">
+      <c r="C21" s="425" t="n">
         <v>500000</v>
       </c>
-      <c r="D21" s="422" t="n">
+      <c r="D21" s="425" t="n">
         <v>1500000</v>
       </c>
-      <c r="E21" s="422" t="n">
+      <c r="E21" s="425" t="n">
         <v>3000000</v>
       </c>
-      <c r="F21" s="422" t="n">
+      <c r="F21" s="425" t="n">
         <v>5000000</v>
       </c>
-      <c r="G21" s="422" t="n">
+      <c r="G21" s="425" t="n">
         <v>8000000</v>
       </c>
-      <c r="H21" s="432">
+      <c r="H21" s="435">
         <f>SUM(C21:G21)</f>
         <v/>
       </c>
-      <c r="I21" s="424">
+      <c r="I21" s="427">
         <f>H21/H23</f>
         <v/>
       </c>
@@ -10737,67 +11201,67 @@
           <t>💎 بيع البيانات والتحليلات</t>
         </is>
       </c>
-      <c r="B22" s="431" t="inlineStr">
+      <c r="B22" s="434" t="inlineStr">
         <is>
           <t>إضافي</t>
         </is>
       </c>
-      <c r="C22" s="422" t="n">
+      <c r="C22" s="425" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="422" t="n">
+      <c r="D22" s="425" t="n">
         <v>200000</v>
       </c>
-      <c r="E22" s="422" t="n">
+      <c r="E22" s="425" t="n">
         <v>500000</v>
       </c>
-      <c r="F22" s="422" t="n">
+      <c r="F22" s="425" t="n">
         <v>1000000</v>
       </c>
-      <c r="G22" s="422" t="n">
+      <c r="G22" s="425" t="n">
         <v>1500000</v>
       </c>
-      <c r="H22" s="432">
+      <c r="H22" s="435">
         <f>SUM(C22:G22)</f>
         <v/>
       </c>
-      <c r="I22" s="424">
+      <c r="I22" s="427">
         <f>H22/H23</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="37.5" customHeight="1" s="260">
-      <c r="A23" s="433" t="inlineStr">
+      <c r="A23" s="436" t="inlineStr">
         <is>
           <t>📊 إجمالي الإيرادات</t>
         </is>
       </c>
-      <c r="B23" s="434" t="n"/>
-      <c r="C23" s="435">
+      <c r="B23" s="437" t="n"/>
+      <c r="C23" s="438">
         <f>SUM(C17:C22)</f>
         <v/>
       </c>
-      <c r="D23" s="435">
+      <c r="D23" s="438">
         <f>SUM(D17:D22)</f>
         <v/>
       </c>
-      <c r="E23" s="435">
+      <c r="E23" s="438">
         <f>SUM(E17:E22)</f>
         <v/>
       </c>
-      <c r="F23" s="435">
+      <c r="F23" s="438">
         <f>SUM(F17:F22)</f>
         <v/>
       </c>
-      <c r="G23" s="435">
+      <c r="G23" s="438">
         <f>SUM(G17:G22)</f>
         <v/>
       </c>
-      <c r="H23" s="436">
+      <c r="H23" s="439">
         <f>SUM(C23:G23)</f>
         <v/>
       </c>
-      <c r="I23" s="434" t="inlineStr">
+      <c r="I23" s="437" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10859,148 +11323,148 @@
       </c>
     </row>
     <row r="27" ht="31.5" customHeight="1" s="260">
-      <c r="A27" s="437" t="inlineStr">
+      <c r="A27" s="440" t="inlineStr">
         <is>
           <t>💰 إجمالي الإيرادات</t>
         </is>
       </c>
-      <c r="B27" s="438" t="n"/>
-      <c r="C27" s="439">
+      <c r="B27" s="441" t="n"/>
+      <c r="C27" s="442">
         <f>C23</f>
         <v/>
       </c>
-      <c r="D27" s="439">
+      <c r="D27" s="442">
         <f>D23</f>
         <v/>
       </c>
-      <c r="E27" s="439">
+      <c r="E27" s="442">
         <f>E23</f>
         <v/>
       </c>
-      <c r="F27" s="439">
+      <c r="F27" s="442">
         <f>F23</f>
         <v/>
       </c>
-      <c r="G27" s="439">
+      <c r="G27" s="442">
         <f>G23</f>
         <v/>
       </c>
-      <c r="H27" s="435">
+      <c r="H27" s="438">
         <f>SUM(C27:G27)</f>
         <v/>
       </c>
-      <c r="I27" s="440" t="inlineStr">
+      <c r="I27" s="443" t="inlineStr">
         <is>
           <t>إيرادات</t>
         </is>
       </c>
     </row>
     <row r="28" ht="31.5" customHeight="1" s="260">
-      <c r="A28" s="441" t="inlineStr">
+      <c r="A28" s="444" t="inlineStr">
         <is>
           <t>💸 إجمالي التكاليف</t>
         </is>
       </c>
-      <c r="B28" s="442" t="n"/>
-      <c r="C28" s="443">
+      <c r="B28" s="445" t="n"/>
+      <c r="C28" s="446">
         <f>C13</f>
         <v/>
       </c>
-      <c r="D28" s="443">
+      <c r="D28" s="446">
         <f>D13</f>
         <v/>
       </c>
-      <c r="E28" s="443">
+      <c r="E28" s="446">
         <f>E13</f>
         <v/>
       </c>
-      <c r="F28" s="443">
+      <c r="F28" s="446">
         <f>F13</f>
         <v/>
       </c>
-      <c r="G28" s="443">
+      <c r="G28" s="446">
         <f>G13</f>
         <v/>
       </c>
-      <c r="H28" s="428">
+      <c r="H28" s="431">
         <f>SUM(C28:G28)</f>
         <v/>
       </c>
-      <c r="I28" s="444" t="inlineStr">
+      <c r="I28" s="447" t="inlineStr">
         <is>
           <t>تكاليف</t>
         </is>
       </c>
     </row>
     <row r="29" ht="37.5" customHeight="1" s="260">
-      <c r="A29" s="445" t="inlineStr">
+      <c r="A29" s="448" t="inlineStr">
         <is>
           <t>💎 صافي الربح</t>
         </is>
       </c>
-      <c r="B29" s="446" t="n"/>
-      <c r="C29" s="447">
+      <c r="B29" s="449" t="n"/>
+      <c r="C29" s="450">
         <f>C27-C28</f>
         <v/>
       </c>
-      <c r="D29" s="447">
+      <c r="D29" s="450">
         <f>D27-D28</f>
         <v/>
       </c>
-      <c r="E29" s="447">
+      <c r="E29" s="450">
         <f>E27-E28</f>
         <v/>
       </c>
-      <c r="F29" s="447">
+      <c r="F29" s="450">
         <f>F27-F28</f>
         <v/>
       </c>
-      <c r="G29" s="447">
+      <c r="G29" s="450">
         <f>G27-G28</f>
         <v/>
       </c>
-      <c r="H29" s="448">
+      <c r="H29" s="451">
         <f>SUM(C29:G29)</f>
         <v/>
       </c>
-      <c r="I29" s="449" t="inlineStr">
+      <c r="I29" s="452" t="inlineStr">
         <is>
           <t>ربح</t>
         </is>
       </c>
     </row>
     <row r="30" ht="43.5" customHeight="1" s="260">
-      <c r="A30" s="450" t="inlineStr">
+      <c r="A30" s="453" t="inlineStr">
         <is>
           <t>🎯 ROI %</t>
         </is>
       </c>
-      <c r="B30" s="451" t="n"/>
-      <c r="C30" s="452">
+      <c r="B30" s="454" t="n"/>
+      <c r="C30" s="455">
         <f>IFERROR(C29/C28, 0)</f>
         <v/>
       </c>
-      <c r="D30" s="452">
+      <c r="D30" s="455">
         <f>IFERROR(D29/D28, 0)</f>
         <v/>
       </c>
-      <c r="E30" s="452">
+      <c r="E30" s="455">
         <f>IFERROR(E29/E28, 0)</f>
         <v/>
       </c>
-      <c r="F30" s="452">
+      <c r="F30" s="455">
         <f>IFERROR(F29/F28, 0)</f>
         <v/>
       </c>
-      <c r="G30" s="452">
+      <c r="G30" s="455">
         <f>IFERROR(G29/G28, 0)</f>
         <v/>
       </c>
-      <c r="H30" s="453">
+      <c r="H30" s="456">
         <f>H29/H28</f>
         <v/>
       </c>
-      <c r="I30" s="449" t="inlineStr">
+      <c r="I30" s="452" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
@@ -11008,34 +11472,34 @@
     </row>
     <row r="31" ht="13.5" customHeight="1" s="260"/>
     <row r="32" ht="30" customHeight="1" s="260">
-      <c r="A32" s="326" t="inlineStr">
+      <c r="A32" s="329" t="inlineStr">
         <is>
           <t>⚖️ نقطة التعادل والتقييم النهائي</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="260">
-      <c r="A33" s="454" t="inlineStr">
+      <c r="A33" s="457" t="inlineStr">
         <is>
           <t>🎯 ROI الإجمالي (5 سنوات)</t>
         </is>
       </c>
       <c r="B33" s="287" t="n"/>
-      <c r="C33" s="364" t="inlineStr">
+      <c r="C33" s="367" t="inlineStr">
         <is>
           <t>💰 صافي الربح (5 سنوات)</t>
         </is>
       </c>
       <c r="D33" s="293" t="n"/>
       <c r="E33" s="287" t="n"/>
-      <c r="F33" s="340" t="inlineStr">
+      <c r="F33" s="343" t="inlineStr">
         <is>
           <t>⚖️ نقطة التعادل</t>
         </is>
       </c>
       <c r="G33" s="293" t="n"/>
       <c r="H33" s="287" t="n"/>
-      <c r="I33" s="339" t="inlineStr">
+      <c r="I33" s="342" t="inlineStr">
         <is>
           <t>✅ التوصية</t>
         </is>
@@ -11043,24 +11507,24 @@
       <c r="J33" s="287" t="n"/>
     </row>
     <row r="34" ht="69.75" customHeight="1" s="260">
-      <c r="A34" s="455">
+      <c r="A34" s="458">
         <f>H30</f>
         <v/>
       </c>
       <c r="B34" s="287" t="n"/>
-      <c r="C34" s="456">
+      <c r="C34" s="459">
         <f>H29</f>
         <v/>
       </c>
       <c r="D34" s="293" t="n"/>
       <c r="E34" s="287" t="n"/>
-      <c r="F34" s="457">
+      <c r="F34" s="460">
         <f>IF(C29&gt;=0,"السنة 1",IF(SUM(C29:D29)&gt;=0,"السنة 2",IF(SUM(C29:E29)&gt;=0,"السنة 3",IF(SUM(C29:F29)&gt;=0,"السنة 4",IF(SUM(C29:G29)&gt;=0,"السنة 5","بعد 5 سنوات")))))</f>
         <v/>
       </c>
       <c r="G34" s="293" t="n"/>
       <c r="H34" s="287" t="n"/>
-      <c r="I34" s="458">
+      <c r="I34" s="461">
         <f>IF(H30&gt;1,"⭐ مشروع ممتاز",IF(H30&gt;0.5,"✅ مربح",IF(H30&gt;0,"🟡 مقبول","🔴 إعادة نظر")))</f>
         <v/>
       </c>
@@ -11068,14 +11532,14 @@
     </row>
     <row r="35" ht="13.5" customHeight="1" s="260"/>
     <row r="36" ht="27.75" customHeight="1" s="260">
-      <c r="A36" s="459" t="inlineStr">
+      <c r="A36" s="462" t="inlineStr">
         <is>
           <t>📝 ملاحظات وافتراضات</t>
         </is>
       </c>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="260">
-      <c r="A37" s="355" t="inlineStr">
+      <c r="A37" s="358" t="inlineStr">
         <is>
           <t>💡 زيادة مبيعات الوقود +8% بناءً على دراسات عالمية لبرامج الولاء (شل · BP · Caltex)</t>
         </is>
@@ -11091,7 +11555,7 @@
       <c r="J37" s="287" t="n"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="260">
-      <c r="A38" s="355" t="inlineStr">
+      <c r="A38" s="358" t="inlineStr">
         <is>
           <t>💡 تكلفة فريق الولاء تشمل: لويالتي ليد + 3 مطورين + PM + 2 شراكات + محلل بيانات</t>
         </is>
@@ -11107,7 +11571,7 @@
       <c r="J38" s="287" t="n"/>
     </row>
     <row r="39" ht="27.75" customHeight="1" s="260">
-      <c r="A39" s="355" t="inlineStr">
+      <c r="A39" s="358" t="inlineStr">
         <is>
           <t>💡 عمولة المستأجرين تبدأ من السنة 2 (مع إطلاق المرحلة 2 من خطة التوسع)</t>
         </is>
@@ -11123,7 +11587,7 @@
       <c r="J39" s="287" t="n"/>
     </row>
     <row r="40" ht="27.75" customHeight="1" s="260">
-      <c r="A40" s="355" t="inlineStr">
+      <c r="A40" s="358" t="inlineStr">
         <is>
           <t>💡 توفير التسويق التقليدي: انتقال 30% من الميزانية للقنوات الرقمية بفعالية أعلى</t>
         </is>
@@ -11139,7 +11603,7 @@
       <c r="J40" s="287" t="n"/>
     </row>
     <row r="41" ht="27.75" customHeight="1" s="260">
-      <c r="A41" s="355" t="inlineStr">
+      <c r="A41" s="358" t="inlineStr">
         <is>
           <t>💡 جذب عملاء جدد: 5% من عملاء المنافسين خلال 5 سنوات (تحفظي)</t>
         </is>
@@ -11155,7 +11619,7 @@
       <c r="J41" s="287" t="n"/>
     </row>
     <row r="42" ht="27.75" customHeight="1" s="260">
-      <c r="A42" s="355" t="inlineStr">
+      <c r="A42" s="358" t="inlineStr">
         <is>
           <t>💡 الأرقام لا تشمل القيمة الاستراتيجية غير المباشرة (تحسين العلامة التجارية، البيانات الكبيرة، إلخ)</t>
         </is>
@@ -11326,23 +11790,23 @@
           <t>قيمة النقطة</t>
         </is>
       </c>
-      <c r="B6" s="460" t="n">
+      <c r="B6" s="463" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="461" t="n">
+      <c r="C6" s="464" t="n">
         <v>20000</v>
       </c>
-      <c r="D6" s="462">
+      <c r="D6" s="465">
         <f>السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="E6" s="461" t="n">
+      <c r="E6" s="464" t="n">
         <v>10000</v>
       </c>
-      <c r="F6" s="461" t="n">
+      <c r="F6" s="464" t="n">
         <v>10000</v>
       </c>
-      <c r="G6" s="461" t="n">
+      <c r="G6" s="464" t="n">
         <v>10000</v>
       </c>
       <c r="H6" s="306">
@@ -11357,23 +11821,23 @@
           <t>معدل كسب الأبيض</t>
         </is>
       </c>
-      <c r="B7" s="422" t="n">
+      <c r="B7" s="425" t="n">
         <v>0.43</v>
       </c>
-      <c r="C7" s="422" t="n">
+      <c r="C7" s="425" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="447">
+      <c r="D7" s="450">
         <f>السيناريوهات!C7</f>
         <v/>
       </c>
-      <c r="E7" s="422" t="n">
+      <c r="E7" s="425" t="n">
         <v>100</v>
       </c>
-      <c r="F7" s="422" t="n">
+      <c r="F7" s="425" t="n">
         <v>150</v>
       </c>
-      <c r="G7" s="422" t="n">
+      <c r="G7" s="425" t="n">
         <v>200</v>
       </c>
       <c r="H7" s="306">
@@ -11388,23 +11852,23 @@
           <t>معدل كسب الفضي</t>
         </is>
       </c>
-      <c r="B8" s="422" t="n">
+      <c r="B8" s="425" t="n">
         <v>0.43</v>
       </c>
-      <c r="C8" s="422" t="n">
+      <c r="C8" s="425" t="n">
         <v>75</v>
       </c>
-      <c r="D8" s="447">
+      <c r="D8" s="450">
         <f>السيناريوهات!C8</f>
         <v/>
       </c>
-      <c r="E8" s="422" t="n">
+      <c r="E8" s="425" t="n">
         <v>150</v>
       </c>
-      <c r="F8" s="422" t="n">
+      <c r="F8" s="425" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="422" t="n">
+      <c r="G8" s="425" t="n">
         <v>250</v>
       </c>
       <c r="H8" s="306">
@@ -11419,23 +11883,23 @@
           <t>معدل كسب البرتقالي</t>
         </is>
       </c>
-      <c r="B9" s="422" t="n">
+      <c r="B9" s="425" t="n">
         <v>0.43</v>
       </c>
-      <c r="C9" s="422" t="n">
+      <c r="C9" s="425" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="447">
+      <c r="D9" s="450">
         <f>السيناريوهات!C9</f>
         <v/>
       </c>
-      <c r="E9" s="422" t="n">
+      <c r="E9" s="425" t="n">
         <v>200</v>
       </c>
-      <c r="F9" s="422" t="n">
+      <c r="F9" s="425" t="n">
         <v>250</v>
       </c>
-      <c r="G9" s="422" t="n">
+      <c r="G9" s="425" t="n">
         <v>300</v>
       </c>
       <c r="H9" s="306">
@@ -11450,23 +11914,23 @@
           <t>كاش باك الأبيض %</t>
         </is>
       </c>
-      <c r="B10" s="463" t="n">
+      <c r="B10" s="466" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C10" s="463" t="n">
+      <c r="C10" s="466" t="n">
         <v>0.0025</v>
       </c>
-      <c r="D10" s="464">
+      <c r="D10" s="467">
         <f>السيناريوهات!C7/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="E10" s="463" t="n">
+      <c r="E10" s="466" t="n">
         <v>0.01</v>
       </c>
-      <c r="F10" s="463" t="n">
+      <c r="F10" s="466" t="n">
         <v>0.015</v>
       </c>
-      <c r="G10" s="463" t="n">
+      <c r="G10" s="466" t="n">
         <v>0.02</v>
       </c>
       <c r="H10" s="306">
@@ -11481,23 +11945,23 @@
           <t>كاش باك الفضي %</t>
         </is>
       </c>
-      <c r="B11" s="463" t="n">
+      <c r="B11" s="466" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C11" s="463" t="n">
+      <c r="C11" s="466" t="n">
         <v>0.00375</v>
       </c>
-      <c r="D11" s="464">
+      <c r="D11" s="467">
         <f>السيناريوهات!C8/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="E11" s="463" t="n">
+      <c r="E11" s="466" t="n">
         <v>0.015</v>
       </c>
-      <c r="F11" s="463" t="n">
+      <c r="F11" s="466" t="n">
         <v>0.02</v>
       </c>
-      <c r="G11" s="463" t="n">
+      <c r="G11" s="466" t="n">
         <v>0.025</v>
       </c>
       <c r="H11" s="306">
@@ -11512,23 +11976,23 @@
           <t>كاش باك البرتقالي %</t>
         </is>
       </c>
-      <c r="B12" s="463" t="n">
+      <c r="B12" s="466" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C12" s="463" t="n">
+      <c r="C12" s="466" t="n">
         <v>0.005</v>
       </c>
-      <c r="D12" s="464">
+      <c r="D12" s="467">
         <f>السيناريوهات!C9/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="E12" s="463" t="n">
+      <c r="E12" s="466" t="n">
         <v>0.02</v>
       </c>
-      <c r="F12" s="463" t="n">
+      <c r="F12" s="466" t="n">
         <v>0.025</v>
       </c>
-      <c r="G12" s="463" t="n">
+      <c r="G12" s="466" t="n">
         <v>0.03</v>
       </c>
       <c r="H12" s="306">
@@ -11543,23 +12007,23 @@
           <t>تكلفة درب (هللة/ريال)</t>
         </is>
       </c>
-      <c r="B13" s="465" t="n">
+      <c r="B13" s="468" t="n">
         <v>0.43</v>
       </c>
-      <c r="C13" s="465" t="n">
+      <c r="C13" s="468" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" s="466">
+      <c r="D13" s="469">
         <f>السيناريوهات!C10</f>
         <v/>
       </c>
-      <c r="E13" s="465" t="n">
+      <c r="E13" s="468" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="465" t="n">
+      <c r="F13" s="468" t="n">
         <v>1.5</v>
       </c>
-      <c r="G13" s="465" t="n">
+      <c r="G13" s="468" t="n">
         <v>2</v>
       </c>
       <c r="H13" s="306">
@@ -11570,46 +12034,46 @@
     </row>
     <row r="14" ht="13.5" customHeight="1" s="260"/>
     <row r="15" ht="37.5" customHeight="1" s="260">
-      <c r="A15" s="467" t="inlineStr">
+      <c r="A15" s="470" t="inlineStr">
         <is>
           <t>🎯 التقييم الإجمالي</t>
         </is>
       </c>
-      <c r="B15" s="367" t="inlineStr">
+      <c r="B15" s="370" t="inlineStr">
         <is>
           <t>ضعيف</t>
         </is>
       </c>
-      <c r="C15" s="367" t="inlineStr">
+      <c r="C15" s="370" t="inlineStr">
         <is>
           <t>آمن</t>
         </is>
       </c>
-      <c r="D15" s="468">
+      <c r="D15" s="471">
         <f>IF(D10&gt;=0.008,IF(D10&lt;=0.012,"⭐ مثالي",IF(D10&lt;=0.018,"جيد","مكلف")),"ضعيف")</f>
         <v/>
       </c>
-      <c r="E15" s="367" t="inlineStr">
+      <c r="E15" s="370" t="inlineStr">
         <is>
           <t>متوازن</t>
         </is>
       </c>
-      <c r="F15" s="367" t="inlineStr">
+      <c r="F15" s="370" t="inlineStr">
         <is>
           <t>سخي</t>
         </is>
       </c>
-      <c r="G15" s="367" t="inlineStr">
+      <c r="G15" s="370" t="inlineStr">
         <is>
           <t>مكلف جداً</t>
         </is>
       </c>
-      <c r="H15" s="469" t="n"/>
+      <c r="H15" s="472" t="n"/>
       <c r="I15" s="287" t="n"/>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="260"/>
     <row r="17" ht="30" customHeight="1" s="260">
-      <c r="A17" s="326" t="inlineStr">
+      <c r="A17" s="329" t="inlineStr">
         <is>
           <t>💰 الأثر المالي السنوي على درب (مليون ريال) - افتراض 230 محطة × 80,000 لتر × 12</t>
         </is>
@@ -11664,31 +12128,31 @@
           <t>تكلفة سنوية (الأبيض)</t>
         </is>
       </c>
-      <c r="B19" s="470">
+      <c r="B19" s="473">
         <f>B10*514.5*0.7</f>
         <v/>
       </c>
-      <c r="C19" s="470">
+      <c r="C19" s="473">
         <f>C10*514.5*0.7</f>
         <v/>
       </c>
-      <c r="D19" s="471">
+      <c r="D19" s="474">
         <f>D10*514.5*0.7</f>
         <v/>
       </c>
-      <c r="E19" s="470">
+      <c r="E19" s="473">
         <f>E10*514.5*0.7</f>
         <v/>
       </c>
-      <c r="F19" s="470">
+      <c r="F19" s="473">
         <f>F10*514.5*0.7</f>
         <v/>
       </c>
-      <c r="G19" s="470">
+      <c r="G19" s="473">
         <f>G10*514.5*0.7</f>
         <v/>
       </c>
-      <c r="H19" s="472">
+      <c r="H19" s="475">
         <f>G19-D19</f>
         <v/>
       </c>
@@ -11696,7 +12160,7 @@
     </row>
     <row r="20" ht="13.5" customHeight="1" s="260"/>
     <row r="21" ht="36" customHeight="1" s="260">
-      <c r="A21" s="355" t="inlineStr">
+      <c r="A21" s="358" t="inlineStr">
         <is>
           <t>💡 العمود ⭐ الحالي يعكس قيم شيت السيناريوهات وقت فتح الملف · غيّر القيم في السيناريوهات وارجع هنا لتشوف الفرق</t>
         </is>
@@ -11918,7 +12382,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" s="260">
-      <c r="A1" s="473" t="inlineStr">
+      <c r="A1" s="476" t="inlineStr">
         <is>
           <t xml:space="preserve">  درب · حساب قيمة النقطة بالتفصيل</t>
         </is>
@@ -11967,16 +12431,16 @@
           <t>قيمة 1 نقطة (ريال)</t>
         </is>
       </c>
-      <c r="B6" s="474" t="inlineStr">
+      <c r="B6" s="477" t="inlineStr">
         <is>
           <t>1 / 10,000</t>
         </is>
       </c>
-      <c r="C6" s="475">
+      <c r="C6" s="478">
         <f>1/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="D6" s="353" t="inlineStr">
+      <c r="D6" s="356" t="inlineStr">
         <is>
           <t>ريال</t>
         </is>
@@ -11988,16 +12452,16 @@
           <t>قيمة 1 نقطة (هللة)</t>
         </is>
       </c>
-      <c r="B7" s="474" t="inlineStr">
+      <c r="B7" s="477" t="inlineStr">
         <is>
           <t>(1/10K)×100</t>
         </is>
       </c>
-      <c r="C7" s="476">
+      <c r="C7" s="479">
         <f>(1/السيناريوهات!C6)*100</f>
         <v/>
       </c>
-      <c r="D7" s="353" t="inlineStr">
+      <c r="D7" s="356" t="inlineStr">
         <is>
           <t>هللة</t>
         </is>
@@ -12009,16 +12473,16 @@
           <t>نقاط ساسكو لكل ريال</t>
         </is>
       </c>
-      <c r="B8" s="474" t="inlineStr">
+      <c r="B8" s="477" t="inlineStr">
         <is>
           <t>لتر/ريال</t>
         </is>
       </c>
-      <c r="C8" s="476">
+      <c r="C8" s="479">
         <f>1/السيناريوهات!C11</f>
         <v/>
       </c>
-      <c r="D8" s="353" t="inlineStr">
+      <c r="D8" s="356" t="inlineStr">
         <is>
           <t>نقطة</t>
         </is>
@@ -12030,7 +12494,7 @@
           <t>نقاط درب الأبيض/ريال</t>
         </is>
       </c>
-      <c r="B9" s="474" t="inlineStr">
+      <c r="B9" s="477" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -12039,7 +12503,7 @@
         <f>السيناريوهات!C7</f>
         <v/>
       </c>
-      <c r="D9" s="353" t="inlineStr">
+      <c r="D9" s="356" t="inlineStr">
         <is>
           <t>نقطة</t>
         </is>
@@ -12051,7 +12515,7 @@
           <t>نقاط درب الفضي/ريال</t>
         </is>
       </c>
-      <c r="B10" s="474" t="inlineStr">
+      <c r="B10" s="477" t="inlineStr">
         <is>
           <t>150</t>
         </is>
@@ -12060,7 +12524,7 @@
         <f>السيناريوهات!C8</f>
         <v/>
       </c>
-      <c r="D10" s="353" t="inlineStr">
+      <c r="D10" s="356" t="inlineStr">
         <is>
           <t>نقطة</t>
         </is>
@@ -12072,7 +12536,7 @@
           <t>نقاط درب البرتقالي/ريال</t>
         </is>
       </c>
-      <c r="B11" s="474" t="inlineStr">
+      <c r="B11" s="477" t="inlineStr">
         <is>
           <t>200</t>
         </is>
@@ -12081,7 +12545,7 @@
         <f>السيناريوهات!C9</f>
         <v/>
       </c>
-      <c r="D11" s="353" t="inlineStr">
+      <c r="D11" s="356" t="inlineStr">
         <is>
           <t>نقطة</t>
         </is>
@@ -12093,16 +12557,16 @@
           <t>الكاش باك الأبيض</t>
         </is>
       </c>
-      <c r="B12" s="474" t="inlineStr">
+      <c r="B12" s="477" t="inlineStr">
         <is>
           <t>100÷10K</t>
         </is>
       </c>
-      <c r="C12" s="477">
+      <c r="C12" s="480">
         <f>السيناريوهات!C7/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="D12" s="353" t="inlineStr">
+      <c r="D12" s="356" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -12114,16 +12578,16 @@
           <t>الكاش باك الفضي</t>
         </is>
       </c>
-      <c r="B13" s="474" t="inlineStr">
+      <c r="B13" s="477" t="inlineStr">
         <is>
           <t>150÷10K</t>
         </is>
       </c>
-      <c r="C13" s="477">
+      <c r="C13" s="480">
         <f>السيناريوهات!C8/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="D13" s="353" t="inlineStr">
+      <c r="D13" s="356" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -12135,16 +12599,16 @@
           <t>الكاش باك البرتقالي</t>
         </is>
       </c>
-      <c r="B14" s="474" t="inlineStr">
+      <c r="B14" s="477" t="inlineStr">
         <is>
           <t>200÷10K</t>
         </is>
       </c>
-      <c r="C14" s="477">
+      <c r="C14" s="480">
         <f>السيناريوهات!C9/السيناريوهات!C6</f>
         <v/>
       </c>
-      <c r="D14" s="353" t="inlineStr">
+      <c r="D14" s="356" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -12152,7 +12616,7 @@
     </row>
     <row r="15" ht="9.75" customHeight="1" s="260"/>
     <row r="16" ht="30" customHeight="1" s="260">
-      <c r="A16" s="326" t="inlineStr">
+      <c r="A16" s="329" t="inlineStr">
         <is>
           <t>📊 أمثلة عملية للعملاء</t>
         </is>
@@ -12209,7 +12673,7 @@
       <c r="B18" s="277" t="n">
         <v>500</v>
       </c>
-      <c r="C18" s="357">
+      <c r="C18" s="360">
         <f>B18*12</f>
         <v/>
       </c>
@@ -12217,19 +12681,19 @@
         <f>IF(C18&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(C18&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="E18" s="478">
+      <c r="E18" s="481">
         <f>C18*IF(D18="🤍 أبيض",السيناريوهات!$C$7,IF(D18="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="F18" s="479">
+      <c r="F18" s="482">
         <f>E18/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="G18" s="361">
+      <c r="G18" s="364">
         <f>F18/C18</f>
         <v/>
       </c>
-      <c r="H18" s="480">
+      <c r="H18" s="483">
         <f>G18/0.0043</f>
         <v/>
       </c>
@@ -12243,7 +12707,7 @@
       <c r="B19" s="277" t="n">
         <v>1500</v>
       </c>
-      <c r="C19" s="357">
+      <c r="C19" s="360">
         <f>B19*12</f>
         <v/>
       </c>
@@ -12251,19 +12715,19 @@
         <f>IF(C19&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(C19&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="E19" s="478">
+      <c r="E19" s="481">
         <f>C19*IF(D19="🤍 أبيض",السيناريوهات!$C$7,IF(D19="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="F19" s="479">
+      <c r="F19" s="482">
         <f>E19/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="G19" s="361">
+      <c r="G19" s="364">
         <f>F19/C19</f>
         <v/>
       </c>
-      <c r="H19" s="480">
+      <c r="H19" s="483">
         <f>G19/0.0043</f>
         <v/>
       </c>
@@ -12277,7 +12741,7 @@
       <c r="B20" s="277" t="n">
         <v>2500</v>
       </c>
-      <c r="C20" s="357">
+      <c r="C20" s="360">
         <f>B20*12</f>
         <v/>
       </c>
@@ -12285,19 +12749,19 @@
         <f>IF(C20&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(C20&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="E20" s="478">
+      <c r="E20" s="481">
         <f>C20*IF(D20="🤍 أبيض",السيناريوهات!$C$7,IF(D20="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="F20" s="479">
+      <c r="F20" s="482">
         <f>E20/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="G20" s="361">
+      <c r="G20" s="364">
         <f>F20/C20</f>
         <v/>
       </c>
-      <c r="H20" s="480">
+      <c r="H20" s="483">
         <f>G20/0.0043</f>
         <v/>
       </c>
@@ -12311,7 +12775,7 @@
       <c r="B21" s="277" t="n">
         <v>5000</v>
       </c>
-      <c r="C21" s="357">
+      <c r="C21" s="360">
         <f>B21*12</f>
         <v/>
       </c>
@@ -12319,19 +12783,19 @@
         <f>IF(C21&lt;السيناريوهات!$C$16,"🤍 أبيض",IF(C21&lt;السيناريوهات!$C$17,"🩶 فضي","🟠 برتقالي"))</f>
         <v/>
       </c>
-      <c r="E21" s="478">
+      <c r="E21" s="481">
         <f>C21*IF(D21="🤍 أبيض",السيناريوهات!$C$7,IF(D21="🩶 فضي",السيناريوهات!$C$8,السيناريوهات!$C$9))</f>
         <v/>
       </c>
-      <c r="F21" s="479">
+      <c r="F21" s="482">
         <f>E21/السيناريوهات!$C$6</f>
         <v/>
       </c>
-      <c r="G21" s="361">
+      <c r="G21" s="364">
         <f>F21/C21</f>
         <v/>
       </c>
-      <c r="H21" s="480">
+      <c r="H21" s="483">
         <f>G21/0.0043</f>
         <v/>
       </c>

--- a/tanki_financial_model_v5.xlsx
+++ b/tanki_financial_model_v5.xlsx
@@ -21,6 +21,7 @@
     <sheet name="التحصيل من الامتياز" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="التوقعات السنوية" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="الاقتصاد الموسّع" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="قنوات الاستبدال" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1126,7 +1127,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="529">
+  <cellXfs count="534">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2698,6 +2699,21 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="10" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="101" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="102" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="4" fontId="102" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -5675,6 +5691,240 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" style="260" min="1" max="1"/>
+    <col width="22" customWidth="1" style="260" min="2" max="2"/>
+    <col width="12" customWidth="1" style="260" min="3" max="3"/>
+    <col width="16" customWidth="1" style="260" min="4" max="4"/>
+    <col width="18" customWidth="1" style="260" min="5" max="5"/>
+    <col width="16" customWidth="1" style="260" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="524" t="inlineStr">
+        <is>
+          <t>درب · قنوات استبدال النقاط — التكلفة على درب لكل قناة (معادلات حيّة)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="525" t="inlineStr">
+        <is>
+          <t>إجمالي القيمة المستبدلة سنوياً (ريال)</t>
+        </is>
+      </c>
+      <c r="C3" s="529" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="526" t="inlineStr">
+        <is>
+          <t>القناة</t>
+        </is>
+      </c>
+      <c r="B5" s="526" t="inlineStr">
+        <is>
+          <t>من يموّلها</t>
+        </is>
+      </c>
+      <c r="C5" s="526" t="inlineStr">
+        <is>
+          <t>النسبة %</t>
+        </is>
+      </c>
+      <c r="D5" s="526" t="inlineStr">
+        <is>
+          <t>تكلفة درب/ريال %</t>
+        </is>
+      </c>
+      <c r="E5" s="526" t="inlineStr">
+        <is>
+          <t>القيمة المستبدلة</t>
+        </is>
+      </c>
+      <c r="F5" s="526" t="inlineStr">
+        <is>
+          <t>تكلفة درب</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="525" t="inlineStr">
+        <is>
+          <t>⛽ خصم بنزين</t>
+        </is>
+      </c>
+      <c r="B6" s="525" t="inlineStr">
+        <is>
+          <t>درب</t>
+        </is>
+      </c>
+      <c r="C6" s="530" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="530" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="531">
+        <f>$C$3*C6</f>
+        <v/>
+      </c>
+      <c r="F6" s="527">
+        <f>E6*D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="525" t="inlineStr">
+        <is>
+          <t>🛍️ عروض المستأجرين</t>
+        </is>
+      </c>
+      <c r="B7" s="525" t="inlineStr">
+        <is>
+          <t>المستأجر</t>
+        </is>
+      </c>
+      <c r="C7" s="530" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D7" s="530" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="531">
+        <f>$C$3*C7</f>
+        <v/>
+      </c>
+      <c r="F7" s="527">
+        <f>E7*D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="525" t="inlineStr">
+        <is>
+          <t>🎁 شركات خارجية (جرير/أمازون/الفرسان)</t>
+        </is>
+      </c>
+      <c r="B8" s="525" t="inlineStr">
+        <is>
+          <t>درب (خصم جملة)</t>
+        </is>
+      </c>
+      <c r="C8" s="530" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="530" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E8" s="531">
+        <f>$C$3*C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="527">
+        <f>E8*D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="525" t="inlineStr">
+        <is>
+          <t>📱 كرت شحن</t>
+        </is>
+      </c>
+      <c r="B9" s="525" t="inlineStr">
+        <is>
+          <t>درب (عمولة المشغّل)</t>
+        </is>
+      </c>
+      <c r="C9" s="530" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D9" s="530" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E9" s="531">
+        <f>$C$3*C9</f>
+        <v/>
+      </c>
+      <c r="F9" s="527">
+        <f>E9*D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="524" t="inlineStr">
+        <is>
+          <t>📊 الإجمالي</t>
+        </is>
+      </c>
+      <c r="C10" s="532">
+        <f>SUM(C6:C9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="527">
+        <f>SUM(E6:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="527">
+        <f>SUM(F6:F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="525" t="inlineStr">
+        <is>
+          <t>متوسط تكلفة الريال المستبدل</t>
+        </is>
+      </c>
+      <c r="C12" s="533">
+        <f>F10/E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="525" t="inlineStr">
+        <is>
+          <t>التوفير مقابل الكل-بنزين</t>
+        </is>
+      </c>
+      <c r="C13" s="527">
+        <f>$C$3-F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="525" t="inlineStr">
+        <is>
+          <t>تحقق مجموع النسب</t>
+        </is>
+      </c>
+      <c r="C14" s="524">
+        <f>IF(C10=1,"✅ 100%","⚠️ راجع النسب")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="525" t="inlineStr">
+        <is>
+          <t>💡 وجّه الاستبدال نحو عروض المستأجرين (تكلفتها صفر) بدل خصم البنزين</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/tanki_financial_model_v5.xlsx
+++ b/tanki_financial_model_v5.xlsx
@@ -3434,22 +3434,22 @@
       </c>
       <c r="D16" s="289" t="inlineStr">
         <is>
-          <t>50 نقطة</t>
+          <t>5 نقطة</t>
         </is>
       </c>
       <c r="E16" s="290" t="inlineStr">
         <is>
-          <t>75 نقطة</t>
+          <t>7.5 نقطة</t>
         </is>
       </c>
       <c r="F16" s="291" t="inlineStr">
         <is>
-          <t>100 نقطة</t>
+          <t>10 نقطة</t>
         </is>
       </c>
       <c r="G16" s="292" t="inlineStr">
         <is>
-          <t>116x - 232x</t>
+          <t>12x - 23x</t>
         </is>
       </c>
       <c r="H16" s="293" t="n"/>
@@ -3539,17 +3539,17 @@
       </c>
       <c r="D19" s="289" t="inlineStr">
         <is>
-          <t>5,000 نقطة</t>
+          <t>500 نقطة</t>
         </is>
       </c>
       <c r="E19" s="290" t="inlineStr">
         <is>
-          <t>7,500 نقطة</t>
+          <t>750 نقطة</t>
         </is>
       </c>
       <c r="F19" s="291" t="inlineStr">
         <is>
-          <t>10,000 نقطة</t>
+          <t>1,000 نقطة</t>
         </is>
       </c>
       <c r="G19" s="292" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="23" ht="27.75" customHeight="1" s="260">
       <c r="A23" s="296" t="inlineStr">
         <is>
-          <t>1. اعتمد النموذج المُضخّم (100 نقطة/ريال + 10,000 نقطة = ريال) للإحساس بالثراء</t>
+          <t>1. اعتمد نقاطاً أكبر من ساسكو (5 نقطة/ريال + 1,000 نقطة = ريال) دون مبالغة تكشف ضعف القيمة</t>
         </is>
       </c>
       <c r="B23" s="293" t="n"/>
@@ -3636,7 +3636,7 @@
     <row r="25" ht="27.75" customHeight="1" s="260">
       <c r="A25" s="296" t="inlineStr">
         <is>
-          <t>3. هدية ترحيب 5,000 نقطة (تكلف 50 هللة فقط لكن إحساسها بـ 5 آلاف!)</t>
+          <t>3. هدية ترحيب 5,000 نقطة = 5 ريال · إحساس كبير وتكلفة بسيطة</t>
         </is>
       </c>
       <c r="B25" s="293" t="n"/>
@@ -3651,7 +3651,7 @@
     <row r="26" ht="27.75" customHeight="1" s="260">
       <c r="A26" s="296" t="inlineStr">
         <is>
-          <t>4. التسويق: 'احصل على نقاط أضعاف ساسكو · 100 نقطة لكل ريال'</t>
+          <t>4. التسويق: 'احصل على نقاط أضعاف ساسكو · 5 نقاط لكل ريال'</t>
         </is>
       </c>
       <c r="B26" s="293" t="n"/>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="C6" s="304" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="305" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="C7" s="304" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D7" s="305" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="C8" s="304" t="n">
-        <v>75</v>
+        <v>7.5</v>
       </c>
       <c r="D8" s="305" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="C9" s="304" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D9" s="305" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
     <row r="33" ht="31.5" customHeight="1" s="260">
       <c r="A33" s="318" t="inlineStr">
         <is>
-          <t>💡 الفلسفة · نقاط مُضخّمة 116x–232x من ساسكو لإحساس بالثراء + قيمة استبدال واضحة (10,000 نقطة = ريال)</t>
+          <t>💡 الفلسفة · نقاط أكبر من ساسكو 12x–23x + قيمة استبدال واضحة (1,000 نقطة = ريال) دون تضخيم يكشف ضعف القيمة</t>
         </is>
       </c>
       <c r="B33" s="299" t="n"/>
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="C38" s="321" t="n">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="D38" s="320" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C39" s="321" t="n">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="D39" s="320" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C41" s="321" t="n">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="D41" s="320">
         <f> 5 ريال تكلفة فعلية</f>

--- a/tanki_financial_model_v5.xlsx
+++ b/tanki_financial_model_v5.xlsx
@@ -22,6 +22,7 @@
     <sheet name="التوقعات السنوية" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="الاقتصاد الموسّع" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="قنوات الاستبدال" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="نموذج المحفظة" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1127,7 +1128,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="534">
+  <cellXfs count="540">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2714,6 +2715,24 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="167" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="102" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="166" fontId="102" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="4" fontId="102" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="2" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="102" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -5925,6 +5944,286 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="260" min="1" max="1"/>
+    <col width="16" customWidth="1" style="260" min="2" max="2"/>
+    <col width="16" customWidth="1" style="260" min="3" max="3"/>
+    <col width="14" customWidth="1" style="260" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="524" t="inlineStr">
+        <is>
+          <t>درب · نموذج المحفظة المموّلة بالكامل (Escrow) — معادلات حيّة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="525" t="inlineStr">
+        <is>
+          <t>كل مُصدِر يودع نسبته على مبيعاته هو · النقاط واجهة فوق محفظة بالريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="526" t="inlineStr">
+        <is>
+          <t>📥 تغذية المحفظة</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="526" t="inlineStr">
+        <is>
+          <t>المصدر</t>
+        </is>
+      </c>
+      <c r="B5" s="526" t="inlineStr">
+        <is>
+          <t>قيمة الشراء (﷼)</t>
+        </is>
+      </c>
+      <c r="C5" s="526" t="inlineStr">
+        <is>
+          <t>نسبة الإيداع %</t>
+        </is>
+      </c>
+      <c r="D5" s="526" t="inlineStr">
+        <is>
+          <t>المودَع (﷼)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="525" t="inlineStr">
+        <is>
+          <t>⛽ بنزين (درب)</t>
+        </is>
+      </c>
+      <c r="B6" s="534" t="n">
+        <v>600</v>
+      </c>
+      <c r="C6" s="535" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="527">
+        <f>B6*C6/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="525" t="inlineStr">
+        <is>
+          <t>☕ كافيه</t>
+        </is>
+      </c>
+      <c r="B7" s="534" t="n">
+        <v>200</v>
+      </c>
+      <c r="C7" s="535" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="527">
+        <f>B7*C7/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="525" t="inlineStr">
+        <is>
+          <t>🍔 مطعم</t>
+        </is>
+      </c>
+      <c r="B8" s="534" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="535" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="527">
+        <f>B8*C8/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="525" t="inlineStr">
+        <is>
+          <t>🛒 سوبرماركت</t>
+        </is>
+      </c>
+      <c r="B9" s="534" t="n">
+        <v>400</v>
+      </c>
+      <c r="C9" s="535" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="527">
+        <f>B9*C9/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="524" t="inlineStr">
+        <is>
+          <t>📊 إجمالي التغذية</t>
+        </is>
+      </c>
+      <c r="D10" s="527">
+        <f>SUM(D6:D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="524" t="inlineStr">
+        <is>
+          <t>رصيد المحفظة (﷼)</t>
+        </is>
+      </c>
+      <c r="C12" s="527">
+        <f>D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="525" t="inlineStr">
+        <is>
+          <t>يُعرض للعميل كنقاط</t>
+        </is>
+      </c>
+      <c r="C13" s="536">
+        <f>C12*السيناريوهات!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="526" t="inlineStr">
+        <is>
+          <t>🔁 محاكاة استبدال</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="525" t="inlineStr">
+        <is>
+          <t>يُسحب من المحفظة (﷼)</t>
+        </is>
+      </c>
+      <c r="C16" s="537" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="525" t="inlineStr">
+        <is>
+          <t>يضيف التاجر تنافساً (﷼)</t>
+        </is>
+      </c>
+      <c r="C17" s="537" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="525" t="inlineStr">
+        <is>
+          <t>يحصل العميل (﷼)</t>
+        </is>
+      </c>
+      <c r="C18" s="527">
+        <f>C16+C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="525" t="inlineStr">
+        <is>
+          <t>القيمة لكل ريال مسحوب</t>
+        </is>
+      </c>
+      <c r="C19" s="538">
+        <f>C18/C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="525" t="inlineStr">
+        <is>
+          <t>الرصيد بعد الاستبدال (﷼)</t>
+        </is>
+      </c>
+      <c r="C20" s="527">
+        <f>C12-C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="526" t="inlineStr">
+        <is>
+          <t>🕳️ الأموال الخاملة (Breakage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="525" t="inlineStr">
+        <is>
+          <t>نسبة الخمول %</t>
+        </is>
+      </c>
+      <c r="C23" s="539" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="525" t="inlineStr">
+        <is>
+          <t>مدة الصلاحية (شهر)</t>
+        </is>
+      </c>
+      <c r="C24" s="539" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="525" t="inlineStr">
+        <is>
+          <t>المتوقع خامل (﷼)</t>
+        </is>
+      </c>
+      <c r="C25" s="527">
+        <f>C12*C23/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="525" t="inlineStr">
+        <is>
+          <t>المتوقع استبداله فعلاً (﷼)</t>
+        </is>
+      </c>
+      <c r="C26" s="527">
+        <f>C12-C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="525" t="inlineStr">
+        <is>
+          <t>🔒 النظام لا يخسر: كل ريال يُستبدل كان مودَعاً مسبقاً · لا أحد يموّل وعود غيره</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/tanki_financial_model_v5.xlsx
+++ b/tanki_financial_model_v5.xlsx
@@ -3217,17 +3217,17 @@
     <row r="6" ht="24" customHeight="1" s="260">
       <c r="A6" s="269" t="inlineStr">
         <is>
-          <t>0.5% من كل ريال إنفاق</t>
+          <t>1% من كل ريال إنفاق</t>
         </is>
       </c>
       <c r="D6" s="270" t="inlineStr">
         <is>
-          <t>0.75% للأعضاء النشطين</t>
+          <t>1% + منافع للأعضاء النشطين</t>
         </is>
       </c>
       <c r="G6" s="271" t="inlineStr">
         <is>
-          <t>1% للأعضاء المميزين</t>
+          <t>1% + منافع VIP</t>
         </is>
       </c>
     </row>
@@ -3453,22 +3453,22 @@
       </c>
       <c r="D16" s="289" t="inlineStr">
         <is>
-          <t>5 نقطة</t>
+          <t>1 نقطة</t>
         </is>
       </c>
       <c r="E16" s="290" t="inlineStr">
         <is>
-          <t>7.5 نقطة</t>
+          <t>1 نقطة</t>
         </is>
       </c>
       <c r="F16" s="291" t="inlineStr">
         <is>
-          <t>10 نقطة</t>
+          <t>1 نقطة</t>
         </is>
       </c>
       <c r="G16" s="292" t="inlineStr">
         <is>
-          <t>12x - 23x</t>
+          <t>2.3x</t>
         </is>
       </c>
       <c r="H16" s="293" t="n"/>
@@ -3523,12 +3523,12 @@
       </c>
       <c r="D18" s="289" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="E18" s="290" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="F18" s="291" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="G18" s="292" t="inlineStr">
         <is>
-          <t>1.2x - 2.3x</t>
+          <t>2.3x</t>
         </is>
       </c>
       <c r="H18" s="293" t="n"/>
@@ -3558,17 +3558,17 @@
       </c>
       <c r="D19" s="289" t="inlineStr">
         <is>
-          <t>500 نقطة</t>
+          <t>100 نقطة</t>
         </is>
       </c>
       <c r="E19" s="290" t="inlineStr">
         <is>
-          <t>750 نقطة</t>
+          <t>100 نقطة</t>
         </is>
       </c>
       <c r="F19" s="291" t="inlineStr">
         <is>
-          <t>1,000 نقطة</t>
+          <t>100 نقطة</t>
         </is>
       </c>
       <c r="G19" s="292" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="23" ht="27.75" customHeight="1" s="260">
       <c r="A23" s="296" t="inlineStr">
         <is>
-          <t>1. اعتمد نقاطاً أكبر من ساسكو (5 نقطة/ريال + 1,000 نقطة = ريال) دون مبالغة تكشف ضعف القيمة</t>
+          <t>1. اعتمد النموذج الشفّاف: كل ريال = نقطة · 100 نقطة = ريال (1%) — ثقة كاملة بلا تضخيم</t>
         </is>
       </c>
       <c r="B23" s="293" t="n"/>
@@ -3655,7 +3655,7 @@
     <row r="25" ht="27.75" customHeight="1" s="260">
       <c r="A25" s="296" t="inlineStr">
         <is>
-          <t>3. هدية ترحيب 5,000 نقطة = 5 ريال · إحساس كبير وتكلفة بسيطة</t>
+          <t>3. هدية ترحيب 500 نقطة = 5 ريال · ترحيب بسيط وواضح</t>
         </is>
       </c>
       <c r="B25" s="293" t="n"/>
@@ -3670,7 +3670,7 @@
     <row r="26" ht="27.75" customHeight="1" s="260">
       <c r="A26" s="296" t="inlineStr">
         <is>
-          <t>4. التسويق: 'احصل على نقاط أضعاف ساسكو · 5 نقاط لكل ريال'</t>
+          <t>4. التسويق: 'كل ريال نقطة · ضعف ساسكو كاش باك'</t>
         </is>
       </c>
       <c r="B26" s="293" t="n"/>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="C6" s="304" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D6" s="305" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="C7" s="304" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="305" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="C8" s="304" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="D8" s="305" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="C9" s="304" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D9" s="305" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
     <row r="33" ht="31.5" customHeight="1" s="260">
       <c r="A33" s="318" t="inlineStr">
         <is>
-          <t>💡 الفلسفة · نقاط أكبر من ساسكو 12x–23x + قيمة استبدال واضحة (1,000 نقطة = ريال) دون تضخيم يكشف ضعف القيمة</t>
+          <t>💡 الفلسفة · نموذج شفّاف: كل ريال = نقطة · 100 نقطة = ريال (1% كاش باك) بلا تضخيم · ثقة كاملة كمنهج TotalEnergies</t>
         </is>
       </c>
       <c r="B33" s="299" t="n"/>
@@ -6929,11 +6929,11 @@
         </is>
       </c>
       <c r="C38" s="321" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="D38" s="320" t="inlineStr">
         <is>
-          <t>كاش باك 0.25%</t>
+          <t>كاش باك 0.5% (هامش ضعيف)</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="C39" s="321" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D39" s="320" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="C41" s="321" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="D41" s="320">
         <f> 5 ريال تكلفة فعلية</f>

--- a/tanki_financial_model_v5.xlsx
+++ b/tanki_financial_model_v5.xlsx
@@ -3217,17 +3217,17 @@
     <row r="6" ht="24" customHeight="1" s="260">
       <c r="A6" s="269" t="inlineStr">
         <is>
-          <t>1% من كل ريال إنفاق</t>
+          <t>0.5% من كل ريال إنفاق</t>
         </is>
       </c>
       <c r="D6" s="270" t="inlineStr">
         <is>
-          <t>1% + منافع للأعضاء النشطين</t>
+          <t>0.5% + منافع للأعضاء النشطين</t>
         </is>
       </c>
       <c r="G6" s="271" t="inlineStr">
         <is>
-          <t>1% + منافع VIP</t>
+          <t>0.5% + منافع VIP</t>
         </is>
       </c>
     </row>
@@ -3488,22 +3488,22 @@
       </c>
       <c r="D17" s="289" t="inlineStr">
         <is>
-          <t>10K = ريال</t>
+          <t>200 = ريال</t>
         </is>
       </c>
       <c r="E17" s="290" t="inlineStr">
         <is>
-          <t>10K = ريال</t>
+          <t>200 = ريال</t>
         </is>
       </c>
       <c r="F17" s="291" t="inlineStr">
         <is>
-          <t>10K = ريال</t>
+          <t>200 = ريال</t>
         </is>
       </c>
       <c r="G17" s="292" t="inlineStr">
         <is>
-          <t>مضخّمة 100x</t>
+          <t>نقطة = نص هللة</t>
         </is>
       </c>
       <c r="H17" s="293" t="n"/>
@@ -3523,22 +3523,22 @@
       </c>
       <c r="D18" s="289" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="E18" s="290" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="F18" s="291" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="G18" s="292" t="inlineStr">
         <is>
-          <t>2.3x</t>
+          <t>1.2x</t>
         </is>
       </c>
       <c r="H18" s="293" t="n"/>
@@ -3625,7 +3625,7 @@
     <row r="23" ht="27.75" customHeight="1" s="260">
       <c r="A23" s="296" t="inlineStr">
         <is>
-          <t>1. اعتمد النموذج الشفّاف: كل ريال = نقطة · 100 نقطة = ريال (1%) — ثقة كاملة بلا تضخيم</t>
+          <t>1. اعتمد النموذج الشفّاف: كل ريال = نقطة · النقطة = نص هللة (200 نقطة = ريال) = 0.5%</t>
         </is>
       </c>
       <c r="B23" s="293" t="n"/>
@@ -3655,7 +3655,7 @@
     <row r="25" ht="27.75" customHeight="1" s="260">
       <c r="A25" s="296" t="inlineStr">
         <is>
-          <t>3. هدية ترحيب 500 نقطة = 5 ريال · ترحيب بسيط وواضح</t>
+          <t>3. هدية ترحيب 1,000 نقطة = 5 ريال · ترحيب بسيط وواضح</t>
         </is>
       </c>
       <c r="B25" s="293" t="n"/>
@@ -3670,7 +3670,7 @@
     <row r="26" ht="27.75" customHeight="1" s="260">
       <c r="A26" s="296" t="inlineStr">
         <is>
-          <t>4. التسويق: 'كل ريال نقطة · ضعف ساسكو كاش باك'</t>
+          <t>4. التسويق: 'كل ريال نقطة · أكثر كاش باك من ساسكو'</t>
         </is>
       </c>
       <c r="B26" s="293" t="n"/>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="C6" s="304" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D6" s="305" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="C10" s="307" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="305" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
     <row r="33" ht="31.5" customHeight="1" s="260">
       <c r="A33" s="318" t="inlineStr">
         <is>
-          <t>💡 الفلسفة · نموذج شفّاف: كل ريال = نقطة · 100 نقطة = ريال (1% كاش باك) بلا تضخيم · ثقة كاملة كمنهج TotalEnergies</t>
+          <t>💡 الفلسفة · نموذج شفّاف: كل ريال = نقطة · النقطة = نص هللة (200 نقطة = ريال) = 0.5% · موحّد مع المتاجر · بلا تضخيم</t>
         </is>
       </c>
       <c r="B33" s="299" t="n"/>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D38" s="320" t="inlineStr">
         <is>
-          <t>كاش باك 0.5% (هامش ضعيف)</t>
+          <t>كاش باك 0.25% (هامش ضعيف)</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="C39" s="321" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D39" s="320" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="C41" s="321" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D41" s="320">
         <f> 5 ريال تكلفة فعلية</f>

--- a/tanki_financial_model_v5.xlsx
+++ b/tanki_financial_model_v5.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="الملخص التنفيذي" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="السيناريوهات" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="كيف يعمل النظام" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="محاكي العميل" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="خطة التوسع" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="محرر المستأجرين" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="حاسبة ROI" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="مقارنة السيناريوهات" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="قيمة النقطة" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="المستويات الثلاثة" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="تكلفة المحطات" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="التحصيل من الامتياز" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="التوقعات السنوية" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="الاقتصاد الموسّع" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="قنوات الاستبدال" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="نموذج المحفظة" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص التنفيذي" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="السيناريوهات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="كيف يعمل النظام" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="محاكي العميل" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="خطة التوسع" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="محرر المستأجرين" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="حاسبة ROI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مقارنة السيناريوهات" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قيمة النقطة" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المستويات الثلاثة" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تكلفة المحطات" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التحصيل من الامتياز" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التوقعات السنوية" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الاقتصاد الموسّع" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قنوات الاستبدال" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نموذج المحفظة" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نموذج التاجر" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1128,7 +1129,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="540">
+  <cellXfs count="541">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2733,6 +2734,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="1" fontId="102" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -6224,6 +6228,191 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" style="260" min="1" max="1"/>
+    <col width="16" customWidth="1" style="260" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="524" t="inlineStr">
+        <is>
+          <t>درب · نموذج التاجر — اقتصاد الـ3% (1% عميل + 2% درب) · معادلات حيّة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="526" t="inlineStr">
+        <is>
+          <t>المدخلات (خلايا صفراء)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="525" t="inlineStr">
+        <is>
+          <t>مبيعات التاجر الشهرية (فواتير عملاء البرنامج)</t>
+        </is>
+      </c>
+      <c r="C3" s="534" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="525" t="inlineStr">
+        <is>
+          <t>هامش التاجر (%)</t>
+        </is>
+      </c>
+      <c r="C4" s="539" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="525" t="inlineStr">
+        <is>
+          <t>النسبة الكلية من الفاتورة (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="535" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="525" t="inlineStr">
+        <is>
+          <t>حصة العميل · نقاط (%)</t>
+        </is>
+      </c>
+      <c r="C6" s="535" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="526" t="inlineStr">
+        <is>
+          <t>النتائج (معادلات)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="525" t="inlineStr">
+        <is>
+          <t>حصة درب (%)</t>
+        </is>
+      </c>
+      <c r="C9" s="540">
+        <f>C5-C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="525" t="inlineStr">
+        <is>
+          <t>تكلفة التاجر/شهر (﷼)</t>
+        </is>
+      </c>
+      <c r="C10" s="527">
+        <f>C3*C5/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="525" t="inlineStr">
+        <is>
+          <t>نقاط العميل/شهر</t>
+        </is>
+      </c>
+      <c r="C11" s="536">
+        <f>C3*C6/100*السيناريوهات!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="525" t="inlineStr">
+        <is>
+          <t>إيراد درب/شهر (﷼)</t>
+        </is>
+      </c>
+      <c r="C12" s="527">
+        <f>C3*(C5-C6)/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="525" t="inlineStr">
+        <is>
+          <t>إيراد درب/سنة (﷼)</t>
+        </is>
+      </c>
+      <c r="C13" s="536">
+        <f>C3*(C5-C6)/100*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="525" t="inlineStr">
+        <is>
+          <t>نقطة التعادل للتاجر (% نمو)</t>
+        </is>
+      </c>
+      <c r="C14" s="540">
+        <f>C5*100/C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="525" t="inlineStr">
+        <is>
+          <t>ربح إضافي عند نمو 15% (﷼)</t>
+        </is>
+      </c>
+      <c r="C15" s="527">
+        <f>C3*0.15*C4/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="525" t="inlineStr">
+        <is>
+          <t>صافي ربح التاجر/شهر (﷼)</t>
+        </is>
+      </c>
+      <c r="C16" s="527">
+        <f>C3*0.15*C4/100-C3*C5/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="525" t="inlineStr">
+        <is>
+          <t>ROI للتاجر</t>
+        </is>
+      </c>
+      <c r="C17" s="532">
+        <f>(C3*0.15*C4/100-C3*C5/100)/(C3*C5/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="525" t="inlineStr">
+        <is>
+          <t>💡 التعادل = النسبة ÷ الهامش (~5%). الولاء يعطي 15-30% → التاجر رابح. الاستدامة: التسعير على النمو فوق الأساس.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
